--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Pos. 005 · 006 · 007 (EP) · 008 · Erd-/Fassadenleitung (A05/A06) · Anschlussleitung Inneneinheit (Pos. 103 aus A13) · Dachzentralen-Leitungen (Pos. 139/140 aus D05, Pos. 141 aus D03) · Heizkreise (H01) · Wärmemengenzähler: Pos. 096 × Anzahl (H09)</t>
+          <t>Pos. 005 · 006 · 007 (EP) · 008 · Fassadenleitung (A06) · Anschlussleitung Inneneinheit (Pos. 103 aus A13) · Dachzentralen-Leitungen (Pos. 139/140 aus D05, Pos. 141 aus D03) · Heizkreise (H01) · Wärmemengenzähler: Pos. 096 × Anzahl (H09)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Pos. 010 oder 132 · ggf. 133 · ggf. 135 (EP)</t>
+          <t>Pos. 010 oder 132 · ggf. 133 · ggf. 135 (EP) · Erdleitung: Pos. 102 (A05, zur Fundament-/Konsolen-Position)</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -5708,15 +5708,19 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>50 l / 100 l / 200 l</t>
+          <t>100 l / 200 l</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Artikel: Z15 / Z16 / Z17 ×1</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr"/>
+          <t>Artikel: Z16 / Z17 ×1</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>50 l: KEIN Artikel – der 50-l-Puffer (BST 50 Ehp) ist Bestandteil aller 3800er-Pakete 045–054 (v11, AN-C-261082)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -7841,7 +7845,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>WP-Paket lt. Paketmatrix · Puffer (N06) · ggf. Pos. 065 · Pos. 003 · Serie CS8800i: 030 / 031 · 055 / 056 (N07/N08) · 067 · Solar-Übernahme: 069</t>
+          <t>Serie CS8800i: 030 / 031 · 055 / 056 (N07/N08) · WP-Paket lt. Paketmatrix · Puffer (N06) · ggf. Pos. 065 · Pos. 003 · 067 · Solar-Übernahme: 069</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -2275,7 +2275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2292,24 +2292,6 @@
       <c r="C1" t="inlineStr">
         <is>
           <t>Platzierung</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Vermerk zur Heizungsumverlegung
-Im Rahmen des vorliegenden Angebots ist vorgesehen, die bestehende Heizungsanlage aus dem Dachgeschoss in das Kellergeschoss zu verlegen. Die finale Ausführung kann erst im Zuge der detaillierten Feinplanung verbindlich festgelegt werden. Voraussetzung hierfür ist die eindeutige Klärung der hydraulischen Anbindung im Kellergeschoss. Insbesondere müssen geeignete Anschlusspunkte für Heizungs-Vorlauf und -Rücklauf sowie für die Warmwasserversorgung und eine gegebenenfalls erforderliche Zirkulationsleitung vorhanden sein. Für die Kalkulation dieses Angebots wird davon ausgegangen, dass entsprechende Übergabepunkte im Kellergeschoss selbst oder alternativ im direkt darüberliegenden Geschoss vorhanden sind und für die Anbindung genutzt werden können. Die erforderlichen baulichen Maßnahmen zur Leitungsführung einschließlich der Öffnung von Fliesenflächen, Trockenbaukonstruktionen sowie ggf. die Nutzung eines geeigneten Schachtes mit Durchführung in das Kellergeschoss wurden bereits berücksichtigt und sind Bestandteil der Kalkulation. Diese Voraussetzungen werden bauseitig als gegeben angenommen.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>nur wenn A04 = DG und D01 = Nein</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ende Positionsteil</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2374,243 +2356,239 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Objektdaten</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>O01</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Objektart</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>EFH | 2FH | REH | RMH | MFH | Gewerbe</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Basis für KfW-Ableitung (siehe Blatt KfW).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Objektdaten</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>O02</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Baujahr des Objekts</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Info.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Objektdaten</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>O03</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Anzahl Wohneinheiten</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>nur wenn O01 = 2FH oder MFH</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Vorbelegung: 2 bei 2FH. EFH/REH/RMH automatisch 1 WE, Gewerbe ohne WE-Frage.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Objektdaten</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>O04</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>WEG (Wohnungseigentümergemeinschaft)?</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Info.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Objektdaten</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>O05</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Beheizte Fläche (m²)</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Bei Gewerbe Basis der KfW-Höchstkosten.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Objektdaten</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>O06</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Rechnungsanschrift identisch mit Ausführungsort?</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>monday-Adresse = Ausführungsort</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Objektdaten</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>O09</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Rechnungs-Name</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Freitext</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>nur wenn O06 = Nein</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>optional – leer = Name des Kunden</t>
         </is>
@@ -2698,130 +2676,130 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Objektdaten</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>O08</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Bemerkung zum Objekt</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Freitext groß</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Alte Anlage</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>A01</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Aktueller Energieträger</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Gas | Öl | Nachtspeicher | Sonstiges</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Alte Anlage</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>A02</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Baujahr der alten Heizung</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Steuert Vorbelegung Klima-Bonus (K02).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Alte Anlage</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Aktueller Verbrauch (kWh)</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Verbrauch unbekannt</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Bei Öl rechnet der Vertriebler Liter in kWh um.</t>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bei Öl rechnet der Vertriebler Liter in kWh um. Alternative „Verbrauch unbekannt“: Auslegung erfolgt über Fläche × Gebäudestandard (A17/A18).</t>
         </is>
       </c>
     </row>
@@ -2833,32 +2811,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Heizlast bekannt?</t>
+          <t>Beheizte Wohnfläche in m²</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn A03 = Verbrauch unbekannt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Entscheidet bei Bekanntsein über das Paket – A03 (kWh) bleibt Pflicht fürs Protokoll</t>
+          <t>Flächen-Auslegung (v11): Heizlast = Fläche × Faktor ÷ 1000</t>
         </is>
       </c>
     </row>
@@ -2870,433 +2844,435 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>A18</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Gebäudestandard</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>saniert – 40 W/m² | Altbau – 60 W/m² | Altbau unsaniert – 70 W/m²</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>nur wenn A03 = Verbrauch unbekannt</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Faktor der Flächen-Auslegung (v11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Alte Anlage</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Heizlast bekannt?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Entscheidet bei Bekanntsein über das Paket – A03 (kWh) bleibt Pflicht fürs Protokoll</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Alte Anlage</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>A15</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Heizlast in kW</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>nur wenn A14 = Ja</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Dezimalzahl, z. B. 8,4 – hat Vorrang vor der kWh-Zuordnung</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Alte Anlage</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>A04</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Lage des Heizraums</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>KG | EG | OG | DG | Sonstiges</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Alte Anlage</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Soll die Wärmepumpe auch ins DG?</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>nur wenn A04 = DG</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Dachzentralen-Block.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Alte Anlage</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>D02</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Sind im Keller alle notwendigen Anschlüsse vorhanden?</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>nur wenn D01 = Nein</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Alte Anlage</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>D03</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Sollen die notwendigen Anschlüsse im EG erfolgen?</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>In welcher Etage liegen die Anschlüsse (Heizung/Warmwasser)?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Gleiche Etage (KG) | Andere Etage (z. B. EG)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>nur wenn D02 = Nein</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>v11: Gleiche Etage → Pauschale 141; andere Etage → getrennte Meterabfragen D07/D08 (139/140)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Alte Anlage</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Können die Leitungen durch den Schacht verlegt werden und ist dieser frei?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn D02 = Nein</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>nur wenn D06 = Andere Etage (z. B. EG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Alte Anlage</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Können die Leitungen durch den Schacht verlegt werden und ist dieser frei?</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn D03 = Nein</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D07</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Rohrleitung Heizung in m</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>nur wenn D04 = Ja</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pos. 139 (Rohrleitungen Heizungsvorlauf/-rücklauf) × Meter</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Alte Anlage</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>D05</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Länge der zu verlegenden Leitungen</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Mengenmaske (2 Zahlenfelder)</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Heizung VL/RL (m) | Trinkwasser TWK/TWW/Zirkulation (m)</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Rohrleitung Warmwasser in m</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
         <is>
           <t>nur wenn D04 = Ja</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Meter je Leitungsart.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pos. 140 (Rohrleitungen Warmwasser/Zirkulation) × Meter</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Alte Anlage</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>A05</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Länge der Erdleitung (m)</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>nur wenn A04 = KG oder EG, oder (A04 = DG und D01 = Nein)</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Berechnet wird Eingabe − 3 m (nie unter 0).</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Alte Anlage</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>A06</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Länge der Fassadenleitung (m)</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>nur wenn A04 = OG, oder (A04 = DG und D01 = Ja)</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Volle Meterzahl.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Alte Anlage</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>A13</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Leitungslänge zwischen Hauseinführung und WP-Inneneinheit (m)?</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Anschlussleitung Inneneinheit; berechnet wird Eingabe − 5 m (nie unter 0).</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Alte Anlage</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>A07</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Öl-Tankentsorgung erforderlich?</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn A01 = Öl</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Alte Anlage</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>A08</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Art des Öltanks</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Stahl | Kunststoff | Unterirdisch</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn A07 = Ja</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Alte Anlage</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Wie groß ist der Tank?</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>bis 3.000 L | bis 4.000 L | bis 5.000 L | bis 6.000 L | bis 7.000 L | bis 8.000 L | bis 9.000 L | ab 9.000 L</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn A08 = Stahl oder Kunststoff</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3306,371 +3282,360 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Öl-Tankentsorgung erforderlich?</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>nur wenn A01 = Öl</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Alte Anlage</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>A08</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Art des Öltanks</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Stahl | Kunststoff | Unterirdisch</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>nur wenn A07 = Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Alte Anlage</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Wie groß ist der Tank?</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>bis 3.000 L | bis 4.000 L | bis 5.000 L | bis 6.000 L | bis 7.000 L | bis 8.000 L | bis 9.000 L | ab 9.000 L</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>nur wenn A08 = Stahl oder Kunststoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Alte Anlage</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A19</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tatsächliche Tankgröße in Litern</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>nur wenn A09 = ab 9.000 L</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>v11: fürs Protokoll und als Zusatz im Positionstext der Entsorgung</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Alte Anlage</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>A16</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Stemmarbeiten für einen Durchgang benötigt?</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>nur wenn A08 = Stahl oder Kunststoff</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Alte Anlage</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>A10</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Solarthermie vorhanden?</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Ja, soll übernommen werden | Ja, soll stillgelegt werden | Nein</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Alte Anlage</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>A11</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>PV-Anlage vorhanden?</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Ja | Nein | Ist geplant</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Info.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Alte Anlage</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>A12</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Bemerkung zur alten Anlage</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Freitext groß</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Neue Anlage</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>N01</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Art der Wärmepumpe</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Luft/Wasser | Luft/Luft | Sole/Wasser | Split | Sonstiges</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Neue Anlage</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>N02</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Warmwasser über die Wärmepumpe?</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>Steuert Paketvariante + Überschrift Block 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Neue Anlage</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>N03</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Größe des Warmwasserspeichers</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>bis 200 l | 300 l | mehr als 300 l</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>nur wenn N02 = Ja</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>AWM-Pakete haben 180-l-Speicher integriert.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Alte Anlage</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Bemerkung zur alten Anlage</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Freitext groß</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Neue Anlage</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>N08</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Farbe der Außeneinheit?</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>N01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Art der Wärmepumpe</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Weiß | Schwarz</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>nur wenn Klasse = 15 kW</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Serie CS8800i: Pos. 030 (weiß) / Pos. 031 (schwarz)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Luft/Wasser | Luft/Luft | Sole/Wasser | Split | Sonstiges</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Neue Anlage</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>N04</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Aufstellort der Wärmepumpe</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>N02</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Warmwasser über die Wärmepumpe?</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Boden | Garagendach | Sonstiges</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Steuert Paketvariante + Überschrift Block 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Neue Anlage</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>N05</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Durchführung durch Bitumen?</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>N03</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Größe des Warmwasserspeichers</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>nur wenn N04 = Garagendach</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Neue Anlage</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>N06</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Größe des Pufferspeichers</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>50 l | 100 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>nur wenn Klasse = 4 kW oder 6 kW oder 7 kW oder 10 kW oder 13 kW</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>bis 200 l | 300 l | mehr als 300 l</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>nur wenn N02 = Ja</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>AWM-Pakete haben 180-l-Speicher integriert.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3680,12 +3645,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>N07</t>
+          <t>N08</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Größe des Pufferspeichers</t>
+          <t>Farbe der Außeneinheit?</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3695,7 +3660,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>70 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
+          <t>Weiß | Schwarz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3705,61 +3670,56 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Serie CS8800i: 70 l = AWMB (integriert), sonst AWE + externer Puffer</t>
+          <t>Serie CS8800i: Pos. 030 (weiß) / Pos. 031 (schwarz)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Heizverteilung</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Wie viele Heizkreise?</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Neue Anlage</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>N04</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Aufstellort der Wärmepumpe</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>1 | 2 | 3 | mehr als 3</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Boden | Garagendach | Sonstiges</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>immer</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>Ein Heizkreis ist im WP-Paket enthalten.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Heizverteilung</t>
+          <t>Neue Anlage</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>N05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wärmemengenzähler erforderlich?</t>
+          <t>Durchführung durch Bitumen?</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3774,357 +3734,365 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>nur wenn O01 = 2FH oder MFH</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>bei mehr als einer Wohneinheit</t>
+          <t>nur wenn N04 = Garagendach</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Neue Anlage</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>N09</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Mobiler Kran erforderlich?</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>nur wenn N04 = Garagendach</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>v11: ersetzt die automatische Kran-EP-Position</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Neue Anlage</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Länge der Fassadenleitung (m)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>nur wenn N04 = Garagendach und A04 = KG oder EG oder Sonstiges, oder (N04 = Garagendach und A04 = DG und D01 = Nein)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>v11: Fassadenleitung bei Dachaufstellung (Pos. 134 × Meter); bei OG/DG-bleibt läuft sie weiter über A06</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Neue Anlage</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>N06</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Größe des Pufferspeichers</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>50 l | 100 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>nur wenn Klasse = 4 kW oder 6 kW oder 7 kW oder 10 kW oder 13 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Neue Anlage</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>N07</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Größe des Pufferspeichers</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>70 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>nur wenn Klasse = 15 kW</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Serie CS8800i: 70 l = AWMB (integriert), sonst AWE + externer Puffer</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Heizverteilung</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Wie viele Heizkreise?</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1 | 2 | 3 | mehr als 3</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Ein Heizkreis ist im WP-Paket enthalten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Heizverteilung</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Wärmemengenzähler erforderlich?</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>nur wenn O01 = 2FH oder MFH</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>bei mehr als einer Wohneinheit</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Heizverteilung</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>H09</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Anzahl Wärmemengenzähler</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>nur wenn H08 = Ja</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Heizverteilung</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>H02</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Verteilsystem</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Heizkörper | Fußbodenheizung | Heizkörper und Fußbodenheizung | Sonstiges</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Heizverteilung</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>H03</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Heizkörpertausch erforderlich?</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>nur wenn H02 = Heizkörper oder beides</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Heizverteilung</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>H04</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Anzahl Heizkörper je Größe (S/M/L/XL)</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Mengenmaske</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>S | M | L | XL</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>nur wenn H03 = Ja</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Leer/0 = entfällt.</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>Heizverteilung</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>H05</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>FBH-Heizkreisverteiler einregulierbar?</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn H02 = Fußbodenheizung oder beides</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Heizverteilung</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>H06</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Anzahl Heizkreisverteiler</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn H05 = Nein</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Heizverteilung</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>H07</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Gruppen je Heizkreisverteiler {n}</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Wiederholfeld</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn H05 = Nein</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>Ein Feld pro Verteiler aus H06.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>Elektro/ZV</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Lage der Zählerverteilung</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>KG | EG | OG | DG | Sonstiges</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>Info (außer Sonstiges).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>Elektro/ZV</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>E02</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Muss die Zählerverteilung erneuert werden?</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Elektro/ZV</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Wie viele Felder?</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>2-Feld | 3-Feld | 4-Feld und mehr</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>nur wenn E02 = Ja</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Elektro/ZV</t>
+          <t>Heizverteilung</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>H05</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Unterverteilung erforderlich?</t>
+          <t>FBH-Heizkreisverteiler einregulierbar?</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4139,307 +4107,280 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>nur wenn E02 = Nein</t>
+          <t>nur wenn H02 = Fußbodenheizung oder beides</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Heizverteilung</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H06</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Anzahl Heizkreisverteiler</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>nur wenn H05 = Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Heizverteilung</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>H07</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Gruppen je Heizkreisverteiler {n}</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Wiederholfeld</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>nur wenn H05 = Nein</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ein Feld pro Verteiler aus H06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Elektro/ZV</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Lage der Zählerverteilung</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>KG | EG | OG | DG | Sonstiges</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Info (außer Sonstiges).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Elektro/ZV</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Muss die Zählerverteilung erneuert werden?</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Elektro/ZV</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Wie viele Felder?</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2-Feld | 3-Feld | 4-Feld und mehr</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>nur wenn E02 = Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Elektro/ZV</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Unterverteilung erforderlich?</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>nur wenn E02 = Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Elektro/ZV</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>E05</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>MID-Zwischenzähler erforderlich?</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>nur wenn E04 = Ja</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Friondo</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>P01</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Friondo HEMS gewünscht?</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>immer</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>Friondo</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>iMSys inkl. Smart Meter gewünscht?</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>Löst Vollmacht-Seite aus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Friondo</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Friondo SpotDynamic gewünscht?</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>Löst Vollmacht-Seite aus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Förderung</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>K01</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Bewohnt der Eigentümer eine Wohneinheit selbst?</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>nur wenn O01 = 2FH oder MFH</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>EFH/REH/RMH: automatisch Ja. Gewerbe: automatisch Nein.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>Förderung</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>K02</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Welche Heizung wird ersetzt? (Klima-Bonus)</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>Öl-, Kohle-, Gasetagen- oder Nachtspeicherheizung, funktionstüchtig | Gas- oder Biomasseheizung, mind. 20 Jahre, funktionstüchtig | Andere / jüngere Heizung / Neubau</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>nur bei Selbstnutzung</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>Vorbelegt aus A01 + A02, änderbar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>Förderung</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>K03</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>Zu versteuerndes Haushaltsjahreseinkommen (€)</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>Betragseingabe</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>nur bei Selbstnutzung</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>Leer oder über 50.000 € = kein Bonus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>Förderung</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>K04</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>Minderjähriges Kind im Haushalt?</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>nur wenn K03 ausgefüllt</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>10.000 € Abzug vom Einkommen.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Einschätzung</t>
+          <t>Friondo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Einschätzung des Kunden</t>
+          <t>iMSys inkl. Smart Meter gewünscht?</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4449,7 +4390,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>heiß | warm | kalt</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4459,37 +4400,254 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
+          <t>Löst Vollmacht-Seite aus.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>Friondo</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Friondo SpotDynamic gewünscht?</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Löst Vollmacht-Seite aus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Förderung</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>K01</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Bewohnt der Eigentümer eine Wohneinheit selbst?</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>nur wenn O01 = 2FH oder MFH</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>EFH/REH/RMH: automatisch Ja. Gewerbe: automatisch Nein.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Förderung</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>K02</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Welche Heizung wird ersetzt? (Klima-Bonus)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Öl-, Kohle-, Gasetagen- oder Nachtspeicherheizung, funktionstüchtig | Gas- oder Biomasseheizung, mind. 20 Jahre, funktionstüchtig | Andere / jüngere Heizung / Neubau</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>nur bei Selbstnutzung</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Vorbelegt aus A01 + A02, änderbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Förderung</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>K03</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Zu versteuerndes Haushaltsjahreseinkommen (€)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Betragseingabe</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>nur bei Selbstnutzung</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Leer oder über 50.000 € = kein Bonus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Förderung</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>K04</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Minderjähriges Kind im Haushalt?</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>nur wenn K03 ausgefüllt</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>10.000 € Abzug vom Einkommen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>Einschätzung</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Einschätzung des Kunden</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>heiß | warm | kalt</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Einschätzung</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Wiedervorlage am</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>optional – leer lassen, wenn keine Wiedervorlage nötig</t>
         </is>
@@ -4506,7 +4664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4538,192 +4696,184 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>A01</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Gas</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>weiter – Klima-Vorbelegung siehe Blatt KfW</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>A01</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Öl</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>weiter – Öl-Zweig (A07–A09) aktiv; K02 vorbelegt Option 1</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A01</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Nachtspeicher</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: aktuelle Heizung nicht konfigurierbar</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Katalog läuft weiter.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>A01</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Sonstiges</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: aktuelle Heizung nicht konfigurierbar</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>0 – 8.000 kWh</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Leistungsklasse 4 kW merken</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Paket lt. Paketmatrix</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>8.001 – 13.999 kWh</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Leistungsklasse 6 kW merken</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>14.000 – 19.999 kWh</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Leistungsklasse 7 kW merken</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>20.000 – 25.999 kWh</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Leistungsklasse 10 kW merken</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>26.000 – 31.000 kWh</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Leistungsklasse 13 kW merken</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>31.001 – 37.000 kWh</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Leistungsklasse 15 kW merken (Serie CS8800i)</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4743,1773 +4893,1733 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A04</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>KG oder EG</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>A05 (Erdleitung) folgt</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A04</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>OG</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>A06 (Fassadenleitung) folgt</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A04</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>DG</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Dachzentralen-Block (D01–D05) folgt; Artikel: Pos. 163 ×1</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Pos. 163 (Rückbau/Stilllegung Abgasanlage Dachzentrale) immer, wenn alte Anlage im DG</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A04</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Sonstiges</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: Lage des Heizraums zzt. nicht konfigurierbar</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A05</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Meterzahl</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Artikel: Pos. 102 × (Eingabe − 3), nie unter 0</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>3 m im Fundament enthalten; Eingabe 8 → 5 m berechnet. Bei Ergebnis 0: keine Position.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A06</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Meterzahl</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Artikel: Pos. 134 × Eingabe</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>volle Meterzahl</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A13</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Meterzahl</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Artikel: Pos. 103 × (Eingabe − 5), nie unter 0</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>5 m sind in Pos. 006 (Montagematerial) enthalten; Eingabe 8 → 3 m berechnet. Ergebnis 0 = keine Position.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>– (Anlage bleibt im DG; A06 Fassadenleitung wird gestellt)</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>D02 folgt; A05 Erdleitung wird gestellt (neuer Heizraum unten)</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Annahme: Aufstellung unten → Erdleitung</t>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Artikel: Z25 ×1 – D02 folgt; A05 Erdleitung wird gestellt (neuer Heizraum unten)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Z25 = Vermerk Heizungsumverlegung 0,00 € (v11, ersetzt den Vermerke-Blatt-Eintrag); nach Zulieferung 4 auf TAIFUN-Pos. 124 umstellen</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>D02</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>D02</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>D03 folgt</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>D06 folgt</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>D03</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Gleiche Etage (KG)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 141 ×1 (Montage-/Installationsarbeiten, Anschlüsse gleiche Etage)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>v11: Pauschale wie bisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Andere Etage (z. B. EG)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>D04 folgt</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>v11: NICHT 141, sondern Meterabfragen D07/D08</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 141 ×1 (Montage-/Installationsarbeiten Anschlüsse EG)</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>D03</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>D07/D08 folgen</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>D04 folgt</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Leitungsführung Dachzentrale nicht konfigurierbar (Schacht nicht nutzbar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>D07</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Meterzahl</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 139 × Eingabe</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>139 = Rohrleitungen Heizungsvorlauf und Rücklauf (laut Artikeltext, v11 dokumentiert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Meterzahl</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 140 × Eingabe</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>140 = Rohrleitungen Warmwasser und Zirkulation (laut Artikeltext, v11 dokumentiert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>D05 folgt</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>A08 folgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>AMPEL: individuell – Grund: Leitungsführung Dachzentrale nicht konfigurierbar (Schacht nicht nutzbar)</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>D05</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Heizung VL/RL (m)</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 139 × Eingabe</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>D05</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Trinkwasser TWK/TWW/Zirkulation (m)</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 140 × Eingabe</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>A07</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A08</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Stahl oder Kunststoff</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>A09 folgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A08</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unterirdisch</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 107 ×1 (Größenfrage entfällt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kunststoff, bis 3.000 L</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Artikel: Z01 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kunststoff, bis 4.000 L</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Artikel: Z02 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Kunststoff, bis 5.000 L</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Artikel: Z03 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Kunststoff, bis 6.000 L</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Artikel: Z04 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Kunststoff, bis 7.000 L</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Artikel: Z05 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Kunststoff, bis 8.000 L</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Artikel: Z06 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Kunststoff, bis 9.000 L</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Artikel: Z07 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Stahl, bis 3.000 L</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Artikel: Z08 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Stahl, bis 4.000 L</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Artikel: Z09 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Stahl, bis 5.000 L</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Artikel: Z10 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Stahl, bis 6.000 L</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Artikel: Z11 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Stahl, bis 7.000 L</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Artikel: Z12 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Stahl, bis 8.000 L</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Artikel: Z13 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Stahl, bis 9.000 L</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Artikel: Z14 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ab 9.000 L</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Größe des Öl-Tanks nicht konfigurierbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ja, soll übernommen werden</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Warmwasser lt. Paketmatrix-Übersteuerung: AWE-Variante + bivalenter 390-l-Solarspeicher (Engine, keine eigene Artikel-Anweisung); N03 entfällt</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Solarthermie-Übernahme (v9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ja, soll stillgelegt werden</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Artikel: Z24 ×1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Rückbau im Heizungsraum, 0,00 € (v9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>N01</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Luft/Wasser</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>weiter</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>N01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Luft/Luft / Sole/Wasser / Split / Sonstiges</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Wärmepumpen-Art nicht konfigurierbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>N02</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>A08 folgt</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>A07</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Paketvariante 'mit Warmwasser'; Überschrift Block 1 Variante 2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>N03 folgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>N02</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Paketvariante 'ohne Warmwasser' (AWE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>N03</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>bis 200 l</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AWM-Paket lt. Paketmatrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>N03</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>300 l</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AWE-Paket lt. Paketmatrix (inkl. Pos. 065)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pos. 065 kommt AUSSCHLIESSLICH aus der Paketmatrix-Spalte WW 300 l – hier keine eigene Artikel-Anweisung</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>N03</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>mehr als 300 l</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: WW-Speichergröße zu groß</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>N04</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 010 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>N04</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Garagendach</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 132 ×1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>N05/N09/N10 folgen; mobiler Kran nur noch über N09 (v11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>N09</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 135 ×1 als EP</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>An-/Abfahrt mobiler Kran (v11: Frage statt Automatik)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>N09</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>A08</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Stahl oder Kunststoff</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>A09 folgt</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>A08</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Unterirdisch</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 107 ×1 (Größenfrage entfällt)</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Kunststoff, bis 3.000 L</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z01 ×1</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Kunststoff, bis 4.000 L</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z02 ×1</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Kunststoff, bis 5.000 L</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z03 ×1</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Kunststoff, bis 6.000 L</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z04 ×1</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Kunststoff, bis 7.000 L</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z05 ×1</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Kunststoff, bis 8.000 L</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z06 ×1</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Kunststoff, bis 9.000 L</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z07 ×1</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Stahl, bis 3.000 L</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z08 ×1</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Stahl, bis 4.000 L</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z09 ×1</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Stahl, bis 5.000 L</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z10 ×1</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Stahl, bis 6.000 L</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z11 ×1</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Stahl, bis 7.000 L</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z12 ×1</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Stahl, bis 8.000 L</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z13 ×1</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Stahl, bis 9.000 L</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z14 ×1</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>ab 9.000 L</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>AMPEL: individuell – Grund: Größe des Öl-Tanks nicht konfigurierbar</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>A10</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Ja, soll übernommen werden</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Warmwasser lt. Paketmatrix-Übersteuerung: AWE-Variante + bivalenter 390-l-Solarspeicher (Engine, keine eigene Artikel-Anweisung); N03 entfällt</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Solarthermie-Übernahme (v9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>A10</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Ja, soll stillgelegt werden</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Z24 ×1</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>Rückbau im Heizungsraum, 0,00 € (v9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>A10</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="D62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Meterzahl</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 134 × Eingabe</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Fassadenleitung bei Dachaufstellung, volle Meterzahl (v11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>N04</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sonstiges</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Aufstellort zzt. nicht konfigurierbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>N05</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 133 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>N05</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>N01</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>Luft/Wasser</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>weiter</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>N01</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Luft/Luft / Sole/Wasser / Split / Sonstiges</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>AMPEL: individuell – Grund: Wärmepumpen-Art nicht konfigurierbar</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>N02</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>N06</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>100 l / 200 l</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Artikel: Z16 / Z17 ×1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>50 l: KEIN Artikel – der 50-l-Puffer (BST 50 Ehp) ist Bestandteil aller 3800er-Pakete 045–054 (v11, AN-C-261082)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>N06</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>300 l / 500 l</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 098 / Pos. 099 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>N06</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>mehr als 500 l</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Größe des Pufferspeichers nicht konfigurierbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>– (im WP-Paket enthalten)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 090 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 090 ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>mehr als 3</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Anzahl der Heizkreise nicht konfigurierbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Heizkörper</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>H03/H04 folgen</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Fußbodenheizung</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>H05–H07 folgen</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Heizkörper und Fußbodenheizung</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>beide Blöcke nacheinander</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Sonstiges</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Verteilsystem nicht konfigurierbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Paketvariante 'mit Warmwasser'; Überschrift Block 1 Variante 2</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>N03 folgt</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>N02</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>H04 folgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
         <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Paketvariante 'ohne Warmwasser' (AWE)</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>N03</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>bis 200 l</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>AWM-Paket lt. Paketmatrix</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>N03</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>300 l</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>AWE-Paket lt. Paketmatrix (inkl. Pos. 065)</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Pos. 065 kommt AUSSCHLIESSLICH aus der Paketmatrix-Spalte WW 300 l – hier keine eigene Artikel-Anweisung</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>N03</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>mehr als 300 l</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>AMPEL: individuell – Grund: WW-Speichergröße zu groß</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>N04</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 010 ×1</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>N04</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Garagendach</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 132 ×1 + Pos. 135 ×1 als EP</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>N05 folgt</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>N04</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>H04</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Anzahl S / M / L / XL</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Artikel: Z18 / Pos. 130 / Z19 / Pos. 131 × Anzahl</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>zusätzlich Pos. 129 × Gesamtanzahl</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>H05</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>H05</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>H06 + H07 folgen</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>H06</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Anzahl</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 108 × Anzahl Verteiler</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>H07</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>bis 4 / 5–8 / 9–14 Gruppen</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Artikel: Z20 / Pos. 109 / Z21 ×1 je Verteiler</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>gleiche Größen zusammenfassen</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>H07</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>über 14 Gruppen</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Gruppenanzahl Heizkreisverteiler nicht konfigurierbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>KG / EG / OG / DG</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>– (nur Protokoll)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
         <is>
           <t>Sonstiges</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>AMPEL: individuell – Grund: Aufstellort zzt. nicht konfigurierbar</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>N05</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: ZV-Lage nicht konfigurierbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 133 ×1</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>N05</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>E03 folgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
         <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>N06</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>100 l / 200 l</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Z16 / Z17 ×1</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>50 l: KEIN Artikel – der 50-l-Puffer (BST 50 Ehp) ist Bestandteil aller 3800er-Pakete 045–054 (v11, AN-C-261082)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>N06</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>300 l / 500 l</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 098 / Pos. 099 ×1</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>N06</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>mehr als 500 l</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>AMPEL: individuell – Grund: Größe des Pufferspeichers nicht konfigurierbar</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>– (im WP-Paket enthalten)</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 090 ×1</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 090 ×2</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>mehr als 3</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>AMPEL: individuell – Grund: Anzahl der Heizkreise nicht konfigurierbar</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>H02</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>Heizkörper</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>H03/H04 folgen</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>H02</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>Fußbodenheizung</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>H05–H07 folgen</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>H02</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Heizkörper und Fußbodenheizung</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>beide Blöcke nacheinander</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>H02</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>Sonstiges</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>AMPEL: individuell – Grund: Verteilsystem nicht konfigurierbar</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>H03</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>E04/E05 folgen (Unterverteilung)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2-Feld</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 104 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>3-Feld</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Artikel: Z22 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>4-Feld und mehr</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Zählerverteilung nicht konfigurierbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>H04 folgt</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>H03</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>H04</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Anzahl S / M / L / XL</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Z18 / Pos. 130 / Z19 / Pos. 131 × Anzahl</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>zusätzlich Pos. 129 × Gesamtanzahl</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>H05</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 015 ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>H05</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>H06 + H07 folgen</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>H06</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>Anzahl</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 108 × Anzahl Verteiler</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>H07</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>bis 4 / 5–8 / 9–14 Gruppen</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z20 / Pos. 109 / Z21 ×1 je Verteiler</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>gleiche Größen zusammenfassen</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>H07</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>über 14 Gruppen</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>AMPEL: individuell – Grund: Gruppenanzahl Heizkreisverteiler nicht konfigurierbar</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>KG / EG / OG / DG</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>– (nur Protokoll)</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>Sonstiges</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>AMPEL: individuell – Grund: ZV-Lage nicht konfigurierbar</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>E02</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 016 ×1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>aktiviert Vollmacht-Seite</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>E03 folgt</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>E02</t>
-        </is>
-      </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>E04/E05 folgen (Unterverteilung)</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>2-Feld</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 104 ×1</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>3-Feld</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Z22 ×1</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>4-Feld und mehr</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>AMPEL: individuell – Grund: Zählerverteilung nicht konfigurierbar</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>P01</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 015 ×1</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 016 ×1</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 017 ×1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
         <is>
           <t>aktiviert Vollmacht-Seite</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 017 ×1</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>aktiviert Vollmacht-Seite</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>Gruppen-Trigger</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>mind. ein Ja bei P01–P03</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Artikel: Pos. 014 ×1 direkt davor</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>599 € einmalig</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>Grundpaket</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>Pos. 003, 005, 006, 007 (EP), 008, 009, 011, 012, 013</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>Einsortierung lt. Angebotsaufbau</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>O01–O08 / K01–K04</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Objekt-/Förderangaben</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>keine Artikel – KfW-Ableitung lt. Blatt KfW</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>Ampel-Auswertung</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>mind. ein AMPEL-Treffer</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>Erfassung = 'Individuell' (orange) mit Grundliste; sonst 'Konfigurierbar' (grün)</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>Innendienst-Liste</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>Grundpaket</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>A15 folgt – Heizlast hat Vorrang vor der kWh-Zuordnung</t>
+          <t>Pos. 003, 005, 006, 007 (EP), 008, 009, 011, 012, 013</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Einsortierung lt. Angebotsaufbau</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>O01–O08 / K01–K04</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Objekt-/Förderangaben</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>– (Paket weiter über A03/kWh)</t>
+          <t>keine Artikel – KfW-Ableitung lt. Blatt KfW</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>Ampel-Auswertung</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>bis 15,9</t>
+          <t>mind. ein AMPEL-Treffer</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Leistungsklasse lt. Paketmatrix-Spalte „Heizlast“ merken (Vorrang vor A03)</t>
+          <t>Erfassung = 'Individuell' (orange) mit Grundliste; sonst 'Konfigurierbar' (grün)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Innendienst-Liste</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>16,0 – 18,5</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Leistungsklasse 15 kW merken (Serie CS8800i, Vorrang vor A03)</t>
+          <t>A15 folgt – Heizlast hat Vorrang vor der kWh-Zuordnung</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ab 18,6</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AMPEL: individuell – Grund: Leistungsklasse zu hoch</t>
+          <t>– (Paket weiter über A03/kWh)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>bis 15,9</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 126 ×1</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Stemmarbeiten für einen Durchgang (Öl-Zweig)</t>
+          <t>Leistungsklasse lt. Paketmatrix-Spalte „Heizlast“ merken (Vorrang vor A03)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>16,0 – 18,5</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Leistungsklasse 15 kW merken (Serie CS8800i, Vorrang vor A03)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>ab 18,6</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>H09 folgt</t>
+          <t>AMPEL: individuell – Grund: Leistungsklasse zu hoch</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Artikel: Pos. 126 ×1</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Stemmarbeiten für einen Durchgang (Öl-Zweig)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>H09</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Anzahl</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 096 × Anzahl (kein EP)</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Wärmemengenzähler als normale Position</t>
+          <t>–</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6519,19 +6629,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 152 ×1; E05 folgt</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Unterverteilung</t>
+          <t>H09 folgt</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6548,166 +6653,161 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>H09</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Anzahl</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Artikel: Z23 ×1</t>
+          <t>Artikel: Pos. 096 × Anzahl (kein EP)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>MID-Zwischenzähler</t>
+          <t>Wärmemengenzähler als normale Position</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Artikel: Pos. 152 ×1; E05 folgt</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Unterverteilung</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>heiß / warm / kalt</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Startwerte der Angebotsverfolgung – keine Artikel</t>
+          <t>–</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>N08</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Weiß</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 030 ×1</t>
+          <t>Artikel: Z23 ×1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Außeneinheit AW 15 O-T (Serie CS8800i)</t>
+          <t>MID-Zwischenzähler</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>N08</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Schwarz</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 031 ×1</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Außeneinheit AW 15 O-TB (Serie CS8800i)</t>
+          <t>–</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>N07</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>70 l</t>
+          <t>heiß / warm / kalt</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 055 ×1</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>AWMB-Inneneinheit mit integriertem 70-l-Puffer</t>
+          <t>Startwerte der Angebotsverfolgung – keine Artikel</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>N07</t>
+          <t>N08</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>200 l</t>
+          <t>Weiß</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 056 ×1 + Z17 ×1</t>
+          <t>Artikel: Pos. 030 ×1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>AWE-Inneneinheit + externer Puffer</t>
+          <t>Außeneinheit AW 15 O-T (Serie CS8800i)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>N07</t>
+          <t>N08</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>300 l</t>
+          <t>Schwarz</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 056 ×1 + Pos. 098 ×1</t>
+          <t>Artikel: Pos. 031 ×1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>AWE-Inneneinheit + externer Puffer</t>
+          <t>Außeneinheit AW 15 O-TB (Serie CS8800i)</t>
         </is>
       </c>
     </row>
@@ -6719,17 +6819,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>500 l</t>
+          <t>70 l</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 056 ×1 + Pos. 099 ×1</t>
+          <t>Artikel: Pos. 055 ×1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>AWE-Inneneinheit + externer Puffer</t>
+          <t>AWMB-Inneneinheit mit integriertem 70-l-Puffer</t>
         </is>
       </c>
     </row>
@@ -6741,10 +6841,76 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>200 l</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 056 ×1 + Z17 ×1</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AWE-Inneneinheit + externer Puffer</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>N07</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>300 l</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 056 ×1 + Pos. 098 ×1</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>AWE-Inneneinheit + externer Puffer</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>N07</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>500 l</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 056 ×1 + Pos. 099 ×1</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>AWE-Inneneinheit + externer Puffer</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>N07</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
           <t>mehr als 500 l</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: Größe des Pufferspeichers nicht konfigurierbar</t>
         </is>
@@ -7006,7 +7172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7682,6 +7848,34 @@
       <c r="F25" t="inlineStr">
         <is>
           <t>Technischer Hinweis: Im Angebot enthalten ist ausschließlich der Rückbau der Solarthermieanlage im Heizungsraum, einschließlich Aufputzleitungen, Solarthermie-Speicher und Solarstation, inkl. fachgerechter Entsorgung. Die vorhandene Solarthermieflüssigkeit wird abgelassen, die Anlage entleert und das Medium fachgerecht entsorgt. Nicht enthalten sind die dachseitigen Komponenten sowie die Leitungsführung außerhalb des Heizungsraums ab dem Übergabepunkt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Z25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Vermerk Heizungsumverlegung</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>pauschal</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vermerk zur Heizungsumverlegung
+Im Rahmen des vorliegenden Angebots ist vorgesehen, die bestehende Heizungsanlage vom Dachgeschoss in den Keller zu verlegen. Die dafür notwendigen Arbeiten sind in den aufgeführten Positionen enthalten.
+(Vorläufiger Wortlaut – wird nach Vorlage des TAIFUN-Musters, Position 124, ersetzt.)</t>
         </is>
       </c>
     </row>
@@ -7867,7 +8061,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Pos. 005 · 006 · 007 (EP) · 008 · Fassadenleitung (A06) · Anschlussleitung Inneneinheit (Pos. 103 aus A13) · Dachzentralen-Leitungen (Pos. 139/140 aus D05, Pos. 141 aus D03) · Heizkreise (H01) · Wärmemengenzähler: Pos. 096 × Anzahl (H09)</t>
+          <t>Pos. 005 · 006 · 007 (EP) · 008 · Fassadenleitung (A06/N10) · Anschlussleitung Inneneinheit (Pos. 103 aus A13) · Dachzentralen-Leitungen (Pos. 139/140 aus D07/D08, Pos. 141 aus D06) · Heizkreise (H01) · Wärmemengenzähler: Pos. 096 × Anzahl (H09)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -7933,7 +8127,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Pos. 009 · Öltank-Entsorgung (Z01–Z14 / Pos. 107) · Pos. 163 (bei A04 = DG) · ggf. Stemmarbeiten Pos. 126 · Solarthermie-Rückbau Z24</t>
+          <t>Pos. 009 · Öltank-Entsorgung (Z01–Z14 / Pos. 107) · Pos. 163 (bei A04 = DG) · ggf. Stemmarbeiten Pos. 126 · Solarthermie-Rückbau Z24 · Z25 (Vermerk Heizungsumverlegung, D01 = Nein)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -7972,7 +8166,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>(ohne Überschrift)</t>
+          <t>Elektroarbeiten</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -2306,7 +2306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2683,49 +2683,49 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>O08</t>
+          <t>O13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bemerkung zum Objekt</t>
+          <t>Abweichende Lieferanschrift (optional, z. B. Contracting)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Freitext groß</t>
+          <t>Freitext</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>immer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>leer lassen, wenn die Lieferung an den Ausführungsort geht (v11); erscheint als eigene Zeile im Angebots-PDF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alte Anlage</t>
+          <t>Objektdaten</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>O08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aktueller Energieträger</t>
+          <t>Bemerkung zum Objekt</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Gas | Öl | Nachtspeicher | Sonstiges</t>
+          <t>Freitext groß</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2742,27 +2742,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Baujahr der alten Heizung</t>
+          <t>Aktueller Energieträger</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Gas | Öl | Nachtspeicher | Sonstiges</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>immer</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Steuert Vorbelegung Klima-Bonus (K02).</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aktueller Verbrauch (kWh)</t>
+          <t>Baujahr der alten Heizung</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2787,11 +2787,6 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Verbrauch unbekannt</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>immer</t>
@@ -2799,7 +2794,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bei Öl rechnet der Vertriebler Liter in kWh um. Alternative „Verbrauch unbekannt“: Auslegung erfolgt über Fläche × Gebäudestandard (A17/A18).</t>
+          <t>Steuert Vorbelegung Klima-Bonus (K02).</t>
         </is>
       </c>
     </row>
@@ -2811,12 +2806,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Beheizte Wohnfläche in m²</t>
+          <t>Aktueller Verbrauch (kWh)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2824,15 +2819,19 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Verbrauch unbekannt</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>nur wenn A03 = Verbrauch unbekannt</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Flächen-Auslegung (v11): Heizlast = Fläche × Faktor ÷ 1000</t>
+          <t>Bei Öl rechnet der Vertriebler Liter in kWh um. Alternative „Verbrauch unbekannt“: Auslegung erfolgt über Fläche × Gebäudestandard (A17/A18).</t>
         </is>
       </c>
     </row>
@@ -2844,22 +2843,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gebäudestandard</t>
+          <t>Beheizte Wohnfläche in m²</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>saniert – 40 W/m² | Altbau – 60 W/m² | Altbau unsaniert – 70 W/m²</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2869,7 +2863,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Faktor der Flächen-Auslegung (v11)</t>
+          <t>Flächen-Auslegung (v11): Heizlast = Fläche × Faktor ÷ 1000</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2875,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Heizlast bekannt?</t>
+          <t>Gebäudestandard</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2896,17 +2890,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>saniert – 40 W/m² | Altbau – 60 W/m² | Altbau unsaniert – 70 W/m²</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn A03 = Verbrauch unbekannt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Entscheidet bei Bekanntsein über das Paket – A03 (kWh) bleibt Pflicht fürs Protokoll</t>
+          <t>Faktor der Flächen-Auslegung (v11)</t>
         </is>
       </c>
     </row>
@@ -2918,27 +2912,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Heizlast in kW</t>
+          <t>Heizlast bekannt?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>nur wenn A14 = Ja</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dezimalzahl, z. B. 8,4 – hat Vorrang vor der kWh-Zuordnung</t>
+          <t>Entscheidet bei Bekanntsein über das Paket – A03 (kWh) bleibt Pflicht fürs Protokoll</t>
         </is>
       </c>
     </row>
@@ -2950,27 +2949,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lage des Heizraums</t>
+          <t>Heizlast in kW</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>KG | EG | OG | DG | Sonstiges</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn A14 = Ja</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dezimalzahl, z. B. 8,4 – hat Vorrang vor der kWh-Zuordnung</t>
         </is>
       </c>
     </row>
@@ -2982,12 +2981,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Soll die Wärmepumpe auch ins DG?</t>
+          <t>Lage des Heizraums</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2997,17 +2996,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>KG | EG | OG | DG | Sonstiges</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>nur wenn A04 = DG</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dachzentralen-Block.</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
@@ -3019,12 +3013,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sind im Keller alle notwendigen Anschlüsse vorhanden?</t>
+          <t>Soll die Wärmepumpe auch ins DG?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3039,7 +3033,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>nur wenn D01 = Nein</t>
+          <t>nur wenn A04 = DG</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dachzentralen-Block.</t>
         </is>
       </c>
     </row>
@@ -3051,12 +3050,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>D06</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>In welcher Etage liegen die Anschlüsse (Heizung/Warmwasser)?</t>
+          <t>Sind im Keller alle notwendigen Anschlüsse vorhanden?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3066,17 +3065,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gleiche Etage (KG) | Andere Etage (z. B. EG)</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>nur wenn D02 = Nein</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>v11: Gleiche Etage → Pauschale 141; andere Etage → getrennte Meterabfragen D07/D08 (139/140)</t>
+          <t>nur wenn D01 = Nein</t>
         </is>
       </c>
     </row>
@@ -3088,12 +3082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Können die Leitungen durch den Schacht verlegt werden und ist dieser frei?</t>
+          <t>In welcher Etage liegen die Anschlüsse (Heizung/Warmwasser)?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3103,12 +3097,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Gleiche Etage (KG) | Andere Etage (z. B. EG)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>nur wenn D06 = Andere Etage (z. B. EG)</t>
+          <t>nur wenn D02 = Nein</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>v11: Gleiche Etage → Pauschale 141; andere Etage → getrennte Meterabfragen D07/D08 (139/140)</t>
         </is>
       </c>
     </row>
@@ -3120,28 +3119,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D07</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rohrleitung Heizung in m</t>
+          <t>Können die Leitungen durch den Schacht verlegt werden und ist dieser frei?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>nur wenn D04 = Ja</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Pos. 139 (Rohrleitungen Heizungsvorlauf/-rücklauf) × Meter</t>
+          <t>nur wenn D06 = Andere Etage (z. B. EG)</t>
         </is>
       </c>
     </row>
@@ -3153,12 +3151,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rohrleitung Warmwasser in m</t>
+          <t>Rohrleitung Heizung in m</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3166,7 +3164,6 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>nur wenn D04 = Ja</t>
@@ -3174,7 +3171,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pos. 140 (Rohrleitungen Warmwasser/Zirkulation) × Meter</t>
+          <t>Pos. 139 (Rohrleitungen Heizungsvorlauf/-rücklauf) × Meter</t>
         </is>
       </c>
     </row>
@@ -3186,12 +3183,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>D08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Länge der Erdleitung (m)</t>
+          <t>Rohrleitung Warmwasser in m</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3201,12 +3198,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>nur wenn A04 = KG oder EG, oder (A04 = DG und D01 = Nein)</t>
+          <t>nur wenn D04 = Ja</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Berechnet wird Eingabe − 3 m (nie unter 0).</t>
+          <t>Pos. 140 (Rohrleitungen Warmwasser/Zirkulation) × Meter</t>
         </is>
       </c>
     </row>
@@ -3218,12 +3215,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Länge der Fassadenleitung (m)</t>
+          <t>Länge der Erdleitung (m)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3233,12 +3230,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>nur wenn A04 = OG, oder (A04 = DG und D01 = Ja)</t>
+          <t>nur wenn A04 = KG oder EG, oder (A04 = DG und D01 = Nein)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Volle Meterzahl.</t>
+          <t>Berechnet wird Eingabe − 3 m (nie unter 0).</t>
         </is>
       </c>
     </row>
@@ -3250,12 +3247,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A13</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Leitungslänge zwischen Hauseinführung und WP-Inneneinheit (m)?</t>
+          <t>Länge der Fassadenleitung (m)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3265,12 +3262,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn A04 = OG, oder (A04 = DG und D01 = Ja)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anschlussleitung Inneneinheit; berechnet wird Eingabe − 5 m (nie unter 0).</t>
+          <t>Volle Meterzahl.</t>
         </is>
       </c>
     </row>
@@ -3282,27 +3279,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Öl-Tankentsorgung erforderlich?</t>
+          <t>Leitungslänge zwischen Hauseinführung und WP-Inneneinheit (m)?</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>nur wenn A01 = Öl</t>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Anschlussleitung Inneneinheit; berechnet wird Eingabe − 5 m (nie unter 0).</t>
         </is>
       </c>
     </row>
@@ -3314,12 +3311,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Art des Öltanks</t>
+          <t>Öl-Tankentsorgung erforderlich?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3329,12 +3326,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stahl | Kunststoff | Unterirdisch</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>nur wenn A07 = Ja</t>
+          <t>nur wenn A01 = Öl</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3343,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A09</t>
+          <t>A08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wie groß ist der Tank?</t>
+          <t>Art des Öltanks</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3361,12 +3358,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>bis 3.000 L | bis 4.000 L | bis 5.000 L | bis 6.000 L | bis 7.000 L | bis 8.000 L | bis 9.000 L | ab 9.000 L</t>
+          <t>Stahl | Kunststoff | Unterirdisch</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>nur wenn A08 = Stahl oder Kunststoff</t>
+          <t>nur wenn A07 = Ja</t>
         </is>
       </c>
     </row>
@@ -3378,28 +3375,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A19</t>
+          <t>A09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tatsächliche Tankgröße in Litern</t>
+          <t>Wie groß ist der Tank?</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>bis 3.000 L | bis 4.000 L | bis 5.000 L | bis 6.000 L | bis 7.000 L | bis 8.000 L | bis 9.000 L | ab 9.000 L</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>nur wenn A09 = ab 9.000 L</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>v11: fürs Protokoll und als Zusatz im Positionstext der Entsorgung</t>
+          <t>nur wenn A08 = Stahl oder Kunststoff</t>
         </is>
       </c>
     </row>
@@ -3411,27 +3407,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Stemmarbeiten für einen Durchgang benötigt?</t>
+          <t>Tatsächliche Tankgröße in Litern</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>nur wenn A08 = Stahl oder Kunststoff</t>
+          <t>nur wenn A09 = ab 9.000 L</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>v11: fürs Protokoll und als Zusatz im Positionstext der Entsorgung</t>
         </is>
       </c>
     </row>
@@ -3443,12 +3439,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Solarthermie vorhanden?</t>
+          <t>Stemmarbeiten für einen Durchgang benötigt?</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3458,12 +3454,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ja, soll übernommen werden | Ja, soll stillgelegt werden | Nein</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn A08 = Stahl oder Kunststoff</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3471,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PV-Anlage vorhanden?</t>
+          <t>Solarthermie vorhanden?</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3490,17 +3486,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ja | Nein | Ist geplant</t>
+          <t>Ja, soll übernommen werden | Ja, soll stillgelegt werden | Nein</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>immer</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Info.</t>
         </is>
       </c>
     </row>
@@ -3512,49 +3503,54 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bemerkung zur alten Anlage</t>
+          <t>PV-Anlage vorhanden?</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Freitext groß</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Ja | Nein | Ist geplant</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>immer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Info.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Neue Anlage</t>
+          <t>Alte Anlage</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>N01</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Art der Wärmepumpe</t>
+          <t>Bemerkung zur alten Anlage</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Luft/Wasser | Luft/Luft | Sole/Wasser | Split | Sonstiges</t>
+          <t>Freitext groß</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3571,12 +3567,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>N02</t>
+          <t>N01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Warmwasser über die Wärmepumpe?</t>
+          <t>Art der Wärmepumpe</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3586,17 +3582,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Luft/Wasser | Luft/Luft | Sole/Wasser | Split | Sonstiges</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>immer</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Steuert Paketvariante + Überschrift Block 1.</t>
         </is>
       </c>
     </row>
@@ -3608,12 +3599,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>N03</t>
+          <t>N02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Größe des Warmwasserspeichers</t>
+          <t>Warmwasser über die Wärmepumpe?</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3623,17 +3614,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>bis 200 l | 300 l | mehr als 300 l</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>nur wenn N02 = Ja</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>AWM-Pakete haben 180-l-Speicher integriert.</t>
+          <t>Steuert Paketvariante + Überschrift Block 1.</t>
         </is>
       </c>
     </row>
@@ -3645,12 +3636,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>N08</t>
+          <t>N03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Farbe der Außeneinheit?</t>
+          <t>Größe des Warmwasserspeichers</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3660,17 +3651,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Weiß | Schwarz</t>
+          <t>bis 200 l | 300 l | mehr als 300 l</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>nur wenn Klasse = 15 kW</t>
+          <t>nur wenn N02 = Ja</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Serie CS8800i: Pos. 030 (weiß) / Pos. 031 (schwarz)</t>
+          <t>AWM-Pakete haben 180-l-Speicher integriert.</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3673,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>N04</t>
+          <t>N08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Aufstellort der Wärmepumpe</t>
+          <t>Farbe der Außeneinheit?</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3697,12 +3688,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Boden | Garagendach | Sonstiges</t>
+          <t>Weiß | Schwarz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn Klasse = 15 kW</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Serie CS8800i: Pos. 030 (weiß) / Pos. 031 (schwarz)</t>
         </is>
       </c>
     </row>
@@ -3714,12 +3710,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>N05</t>
+          <t>N04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Durchführung durch Bitumen?</t>
+          <t>Aufstellort der Wärmepumpe</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3729,12 +3725,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Boden | Garagendach | Sonstiges</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>nur wenn N04 = Garagendach</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
@@ -3746,12 +3742,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>N09</t>
+          <t>N05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mobiler Kran erforderlich?</t>
+          <t>Durchführung durch Bitumen?</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3767,11 +3763,6 @@
       <c r="F44" t="inlineStr">
         <is>
           <t>nur wenn N04 = Garagendach</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>v11: ersetzt die automatische Kran-EP-Position</t>
         </is>
       </c>
     </row>
@@ -3783,28 +3774,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Länge der Fassadenleitung (m)</t>
+          <t>Mobiler Kran erforderlich?</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>nur wenn N04 = Garagendach und A04 = KG oder EG oder Sonstiges, oder (N04 = Garagendach und A04 = DG und D01 = Nein)</t>
+          <t>nur wenn N04 = Garagendach</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>v11: Fassadenleitung bei Dachaufstellung (Pos. 134 × Meter); bei OG/DG-bleibt läuft sie weiter über A06</t>
+          <t>v11: ersetzt die automatische Kran-EP-Position</t>
         </is>
       </c>
     </row>
@@ -3816,27 +3811,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>N06</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Größe des Pufferspeichers</t>
+          <t>Länge der Fassadenleitung (m)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>50 l | 100 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>nur wenn Klasse = 4 kW oder 6 kW oder 7 kW oder 10 kW oder 13 kW</t>
+          <t>nur wenn N04 = Garagendach und A04 = KG oder EG oder Sonstiges, oder (N04 = Garagendach und A04 = DG und D01 = Nein)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>v11: Fassadenleitung bei Dachaufstellung (Pos. 134 × Meter); bei OG/DG-bleibt läuft sie weiter über A06</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3843,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>N07</t>
+          <t>N06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3863,34 +3858,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>70 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
+          <t>50 l | 100 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>nur wenn Klasse = 15 kW</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Serie CS8800i: 70 l = AWMB (integriert), sonst AWE + externer Puffer</t>
+          <t>nur wenn Klasse = 4 kW oder 6 kW oder 7 kW oder 10 kW oder 13 kW</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Heizverteilung</t>
+          <t>Neue Anlage</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>N07</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wie viele Heizkreise?</t>
+          <t>Größe des Pufferspeichers</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3900,17 +3890,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1 | 2 | 3 | mehr als 3</t>
+          <t>70 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn Klasse = 15 kW</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ein Heizkreis ist im WP-Paket enthalten.</t>
+          <t>Serie CS8800i: 70 l = AWMB (integriert), sonst AWE + externer Puffer</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3912,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wärmemengenzähler erforderlich?</t>
+          <t>Wie viele Heizkreise?</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3937,17 +3927,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>1 | 2 | 3 | mehr als 3</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>nur wenn O01 = 2FH oder MFH</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>bei mehr als einer Wohneinheit</t>
+          <t>Ein Heizkreis ist im WP-Paket enthalten.</t>
         </is>
       </c>
     </row>
@@ -3959,22 +3949,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H09</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Anzahl Wärmemengenzähler</t>
+          <t>Wärmemengenzähler erforderlich?</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>nur wenn H08 = Ja</t>
+          <t>nur wenn O01 = 2FH oder MFH</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>bei mehr als einer Wohneinheit</t>
         </is>
       </c>
     </row>
@@ -3986,27 +3986,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>H09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Verteilsystem</t>
+          <t>Anzahl Wärmemengenzähler</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Heizkörper | Fußbodenheizung | Heizkörper und Fußbodenheizung | Sonstiges</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn H08 = Ja</t>
         </is>
       </c>
     </row>
@@ -4018,12 +4013,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Heizkörpertausch erforderlich?</t>
+          <t>Verteilsystem</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4033,12 +4028,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Heizkörper | Fußbodenheizung | Heizkörper und Fußbodenheizung | Sonstiges</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>nur wenn H02 = Heizkörper oder beides</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
@@ -4050,32 +4045,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>H04</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Anzahl Heizkörper je Größe (S/M/L/XL)</t>
+          <t>Heizkörpertausch erforderlich?</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mengenmaske</t>
+          <t>Auswahl</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>S | M | L | XL</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>nur wenn H03 = Ja</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Leer/0 = entfällt.</t>
+          <t>nur wenn H02 = Heizkörper oder beides</t>
         </is>
       </c>
     </row>
@@ -4087,27 +4077,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H05</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FBH-Heizkreisverteiler einregulierbar?</t>
+          <t>Anzahl Heizkörper je Größe (S/M/L/XL)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Auswahl</t>
+          <t>Mengenmaske</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>S | M | L | XL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>nur wenn H02 = Fußbodenheizung oder beides</t>
+          <t>nur wenn H03 = Ja</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Leer/0 = entfällt.</t>
         </is>
       </c>
     </row>
@@ -4119,22 +4114,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H06</t>
+          <t>H05</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Anzahl Heizkreisverteiler</t>
+          <t>FBH-Heizkreisverteiler einregulierbar?</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>nur wenn H05 = Nein</t>
+          <t>nur wenn H02 = Fußbodenheizung oder beides</t>
         </is>
       </c>
     </row>
@@ -4146,64 +4146,54 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H07</t>
+          <t>H06</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gruppen je Heizkreisverteiler {n}</t>
+          <t>Anzahl Heizkreisverteiler</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wiederholfeld</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>nur wenn H05 = Nein</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Ein Feld pro Verteiler aus H06.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Elektro/ZV</t>
+          <t>Heizverteilung</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>H07</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lage der Zählerverteilung</t>
+          <t>Gruppen je Heizkreisverteiler {n}</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>KG | EG | OG | DG | Sonstiges</t>
+          <t>Wiederholfeld</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn H05 = Nein</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Info (außer Sonstiges).</t>
+          <t>Ein Feld pro Verteiler aus H06.</t>
         </is>
       </c>
     </row>
@@ -4215,12 +4205,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Muss die Zählerverteilung erneuert werden?</t>
+          <t>Lage der Zählerverteilung</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4230,12 +4220,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>KG | EG | OG | DG | Sonstiges</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>immer</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Info (außer Sonstiges).</t>
         </is>
       </c>
     </row>
@@ -4247,12 +4242,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wie viele Felder?</t>
+          <t>Muss die Zählerverteilung erneuert werden?</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4262,12 +4257,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2-Feld | 3-Feld | 4-Feld und mehr</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>nur wenn E02 = Ja</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
@@ -4279,12 +4274,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Unterverteilung erforderlich?</t>
+          <t>Wie viele Felder?</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4294,12 +4289,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>2-Feld | 3-Feld | 4-Feld und mehr</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>nur wenn E02 = Nein</t>
+          <t>nur wenn E02 = Ja</t>
         </is>
       </c>
     </row>
@@ -4311,12 +4306,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MID-Zwischenzähler erforderlich?</t>
+          <t>Unterverteilung erforderlich?</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4331,24 +4326,24 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>nur wenn E04 = Ja</t>
+          <t>nur wenn E02 = Nein</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Friondo</t>
+          <t>Elektro/ZV</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Friondo HEMS gewünscht?</t>
+          <t>MID-Zwischenzähler erforderlich?</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4363,7 +4358,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn E04 = Ja</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4370,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>iMSys inkl. Smart Meter gewünscht?</t>
+          <t>Friondo HEMS gewünscht?</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4396,11 +4391,6 @@
       <c r="F63" t="inlineStr">
         <is>
           <t>immer</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Löst Vollmacht-Seite aus.</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4402,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Friondo SpotDynamic gewünscht?</t>
+          <t>iMSys inkl. Smart Meter gewünscht?</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4444,17 +4434,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Förderung</t>
+          <t>Friondo</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>K01</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bewohnt der Eigentümer eine Wohneinheit selbst?</t>
+          <t>Friondo SpotDynamic gewünscht?</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4469,12 +4459,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>nur wenn O01 = 2FH oder MFH</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>EFH/REH/RMH: automatisch Ja. Gewerbe: automatisch Nein.</t>
+          <t>Löst Vollmacht-Seite aus.</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4476,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>K02</t>
+          <t>K01</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Welche Heizung wird ersetzt? (Klima-Bonus)</t>
+          <t>Bewohnt der Eigentümer eine Wohneinheit selbst?</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4501,17 +4491,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Öl-, Kohle-, Gasetagen- oder Nachtspeicherheizung, funktionstüchtig | Gas- oder Biomasseheizung, mind. 20 Jahre, funktionstüchtig | Andere / jüngere Heizung / Neubau</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>nur bei Selbstnutzung</t>
+          <t>nur wenn O01 = 2FH oder MFH</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Vorbelegt aus A01 + A02, änderbar.</t>
+          <t>EFH/REH/RMH: automatisch Ja. Gewerbe: automatisch Nein.</t>
         </is>
       </c>
     </row>
@@ -4523,17 +4513,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>K03</t>
+          <t>K02</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Zu versteuerndes Haushaltsjahreseinkommen (€)</t>
+          <t>Welche Heizung wird ersetzt? (Klima-Bonus)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Betragseingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Öl-, Kohle-, Gasetagen- oder Nachtspeicherheizung, funktionstüchtig | Gas- oder Biomasseheizung, mind. 20 Jahre, funktionstüchtig | Andere / jüngere Heizung / Neubau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4543,7 +4538,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leer oder über 50.000 € = kein Bonus.</t>
+          <t>Vorbelegt aus A01 + A02, änderbar.</t>
         </is>
       </c>
     </row>
@@ -4555,49 +4550,44 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>K04</t>
+          <t>K03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minderjähriges Kind im Haushalt?</t>
+          <t>Zu versteuerndes Haushaltsjahreseinkommen (€)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Betragseingabe</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>nur wenn K03 ausgefüllt</t>
+          <t>nur bei Selbstnutzung</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>10.000 € Abzug vom Einkommen.</t>
+          <t>Leer oder über 50.000 € = kein Bonus.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Einschätzung</t>
+          <t>Förderung</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>K04</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Einschätzung des Kunden</t>
+          <t>Minderjähriges Kind im Haushalt?</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4607,17 +4597,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>heiß | warm | kalt</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn K03 ausgefüllt</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
+          <t>10.000 € Abzug vom Einkommen.</t>
         </is>
       </c>
     </row>
@@ -4629,25 +4619,62 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Einschätzung des Kunden</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>heiß | warm | kalt</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Einschätzung</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Wiedervorlage am</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>optional – leer lassen, wenn keine Wiedervorlage nötig</t>
         </is>
@@ -5816,7 +5843,6 @@
           <t>–</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7172,7 +7198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7870,12 +7896,39 @@
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>Vermerk zur Heizungsumverlegung
 Im Rahmen des vorliegenden Angebots ist vorgesehen, die bestehende Heizungsanlage vom Dachgeschoss in den Keller zu verlegen. Die dafür notwendigen Arbeiten sind in den aufgeführten Positionen enthalten.
 (Vorläufiger Wortlaut – wird nach Vorlage des TAIFUN-Musters, Position 124, ersetzt.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Z26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Elektroarbeiten – im PV-Angebot enthalten</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>pauschal</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Die notwendigen Elektroarbeiten sind Bestandteil des separaten PV-Angebots und werden dort ausgewiesen. (v11: wird beim Einfügen automatisch als Alternativ-Position mit Verknüpfung „PV-Angebot“ gekennzeichnet)</t>
         </is>
       </c>
     </row>

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -8354,7 +8354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -8378,72 +8378,87 @@
           <t>Bemerkung</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Nicht bei Profil</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Friondo Unternehmenspräsentation.pdf</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Unternehmenspräsentation – geht mit jedem Angebot</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Broschüre Ratenkauf.pdf</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Zahlungsoptionen Barkauf/Finanzierung (Nachtext A) – jedes Angebot</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Enni, SWD</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Friondo HEMS.pdf</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>wenn P01 = Ja</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Friondo-HEMS-Broschüre</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Friondo SpotDynamic.pdf</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>wenn P03 = Ja</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>SpotDynamic-Broschüre (dynamischer Stromtarif)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enni, SWD</t>
         </is>
       </c>
     </row>
@@ -8467,15 +8482,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Bosch CS8800iAW.pdf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>wenn Pos. 030–031 im Angebot</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Gerätebroschüre Serie CS8800i (Datei folgt – Zulieferung 3; bis dahin greift die Datei-fehlt-Warnung)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>(weitere Zeilen ergänzen)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Regeln: 'immer' | 'wenn &lt;Frage&gt; = &lt;Antwort&gt;' | 'wenn Pos. &lt;Nr&gt; im Angebot'</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>PDFs in den Ordner anlagen/ legen</t>
         </is>

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -5925,17 +5925,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>100 l / 200 l</t>
+          <t>50 l / 100 l / 200 l</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Artikel: Z16 / Z17 ×1</t>
+          <t>Artikel: Z15 / Z16 / Z17 ×1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>50 l: KEIN Artikel – der 50-l-Puffer (BST 50 Ehp) ist Bestandteil aller 3800er-Pakete 045–054 (v11, AN-C-261082)</t>
+          <t>Entscheidung 23.09.2026: Puffer bleibt eigene Position; stattdessen wird die 50-l-Puffer-Zeile per Textregel aus den Pakettexten 045–054 entfernt</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -8036,6 +8036,23 @@
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Positionen 045–054</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Zeile 'Pufferspeicher BST 50' aus der Beschreibung entfernen</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>50-l-Puffer ist eigene Position (Z15) – Entscheidung 23.09.2026; greift bei jedem (Re-)Import</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8495,7 +8512,6 @@
           <t>Gerätebroschüre Serie CS8800i (Datei folgt – Zulieferung 3; bis dahin greift die Datei-fehlt-Warnung)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -7896,11 +7896,13 @@
       <c r="D26" t="n">
         <v>0</v>
       </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>Vermerk zur Heizungsumverlegung
-Im Rahmen des vorliegenden Angebots ist vorgesehen, die bestehende Heizungsanlage vom Dachgeschoss in den Keller zu verlegen. Die dafür notwendigen Arbeiten sind in den aufgeführten Positionen enthalten.
-(Vorläufiger Wortlaut – wird nach Vorlage des TAIFUN-Musters, Position 124, ersetzt.)</t>
+Im Rahmen des vorliegenden Angebots ist vorgesehen, die bestehende Heizungsanlage aus dem Dachgeschoss in das Kellergeschoss zu verlegen. Die finale Ausführung kann erst im Zuge der detaillierten Feinplanung verbindlich festgelegt werden. Voraussetzung hierfür ist die eindeutige Klärung der hydraulischen Anbindung im Kellergeschoss. Insbesondere müssen geeignete Anschlusspunkte für Heizungs-Vorlauf und -Rücklauf sowie für die Warmwasserversorgung und eine gegebenenfalls erforderliche Zirkulationsleitung vorhanden sein. Für die Kalkulation dieses Angebots wird davon ausgegangen, dass entsprechende Übergabepunkte im Kellergeschoss selbst oder alternativ im direkt darüberliegenden Geschoss vorhanden sind und für die Anbindung genutzt werden können. Die erforderlichen baulichen Maßnahmen zur Leitungsführung einschließlich der Öffnung von Fliesenflächen, Trockenbaukonstruktionen sowie ggf. die Nutzung eines geeigneten Schachtes mit Durchführung in das Kellergeschoss wurden bereits berücksichtigt und sind Bestandteil der Kalkulation. Diese Voraussetzungen werden bauseitig als gegeben angenommen.</t>
         </is>
       </c>
     </row>

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -19,6 +19,10 @@
     <sheet name="Fragen PV" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Fragen KL" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Vermerke" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="PV-Artikel" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Aktionen PV" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Angebotsaufbau PV" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="PV-Parameter" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +32,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +54,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -87,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -105,6 +112,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -572,6 +583,13 @@
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>• Blatt 'Anhänge': PDF-Dateien in den Ordner anlagen/ legen und hier mit Regel eintragen – sie werden beim E-Mail-Versand automatisch angehängt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>v13-PV: Blätter „Aktionen PV“ (mit Spalte Zusatzbedingung), „Angebotsaufbau PV“, „PV-Parameter“ und „PV-Artikel“ (GUID → PV-Nr.; Pinning für den Import der PV-Positionslisten aus Artikel-Preislisten/PV/). PV-Artikel heißen PV001 … und werden wie „Pos. 045“ referenziert.</t>
         </is>
       </c>
     </row>
@@ -586,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,17 +647,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Objektdaten</t>
+          <t>Belegung</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PO01</t>
+          <t>PB01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gebäudeart</t>
+          <t>Belegungsart</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -649,12 +667,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EFH | 2FH | REH | RMH | MFH | Gewerbe</t>
+          <t>Maximalbelegung | Bedarfsorientierte Belegung</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>immer</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Maximalbelegung = Modulanzahl lt. Dachbelegung · Bedarfsorientiert = aus den Verbrauchsangaben, gedeckelt auf die Maximalbelegung</t>
         </is>
       </c>
     </row>
@@ -666,17 +689,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PO02</t>
+          <t>PO01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Baujahr Haus</t>
+          <t>Gebäudeart</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>EFH | 2FH | REH | RMH | MFH | Gewerbe</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -693,27 +721,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PO03</t>
+          <t>PO02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Letzte Dachsanierung</t>
+          <t>Baujahr Haus</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Freitext</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>immer</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>leer lassen, wenn unbekannt</t>
         </is>
       </c>
     </row>
@@ -725,22 +748,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PO04</t>
+          <t>PO03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Stromverbrauch inkl. WP &amp; WB in kWh</t>
+          <t>Letzte Dachsanierung</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Freitext</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>immer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>leer lassen, wenn unbekannt</t>
         </is>
       </c>
     </row>
@@ -752,103 +780,113 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PO05</t>
+          <t>PO04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bemerkung</t>
+          <t>(alt) Stromverbrauch inkl. WP &amp; WB in kWh</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Freitext groß</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn PO04 ausgefüllt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nur Alt-Erfassungen vor v13 – ersetzt durch PO06–PO09</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DC-Dachmontage</t>
+          <t>Objektdaten</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PD01</t>
+          <t>PO06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dachart</t>
+          <t>Stromverbrauch des Haushalts in kWh</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Satteldach | Flachdach | Walmdach | Sonstige</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>immer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ohne Wärmepumpe und Wallbox</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DC-Dachmontage</t>
+          <t>Objektdaten</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PD02</t>
+          <t>PO07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dachziegel und Ortgang fotografiert?</t>
+          <t>Stromverbrauch Wärmepumpe in kWh</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Auswahl</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Aus WP-Erfassung ermitteln</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>immer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0 = keine Wärmepumpe. „Aus WP-Erfassung ermitteln“: Gas-/Ölverbrauch der WP-Erfassung dieses Vorgangs ÷ 3,5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DC-Dachmontage</t>
+          <t>Objektdaten</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PD03</t>
+          <t>PO08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gerüstart</t>
+          <t>Wallbox geplant oder vorhanden?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -858,7 +896,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fanggerüst | Vollgerüst | Sonstiges</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -870,17 +908,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DC-Dachmontage</t>
+          <t>Objektdaten</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PD04</t>
+          <t>PO09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dachrinnenhöhe in m</t>
+          <t>Stromverbrauch Wallbox in kWh</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -890,34 +928,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn PO08 = Ja</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DC-Dachmontage</t>
+          <t>Objektdaten</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PD05</t>
+          <t>PO05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Verschattung vorhanden?</t>
+          <t>Bemerkung</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Freitext groß</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -934,22 +967,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PD06</t>
+          <t>PD01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Anzahl Optimierer</t>
+          <t>Dachart</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Satteldach | Flachdach | Walmdach | Sonstige</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>nur wenn PD05 = Ja</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
@@ -961,12 +999,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PD07</t>
+          <t>PD11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montage auf mehreren Dachseiten?</t>
+          <t>Belegung (Flachdach)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -976,12 +1014,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Ost/West | Süd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn PD01 = Flachdach</t>
         </is>
       </c>
     </row>
@@ -993,12 +1031,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PD08</t>
+          <t>PD12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Leitungslänge DC-Kabelweg in m</t>
+          <t>Maximale Modulanzahl lt. Dachbelegungstool</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1009,6 +1047,11 @@
       <c r="F14" t="inlineStr">
         <is>
           <t>immer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Interim bis zum Dachbelegungstool – Pflicht (Deckel der Bedarfsauslegung)</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1063,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PD09</t>
+          <t>PD13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DC-kWp</t>
+          <t>davon quer verlegte Module</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1035,7 +1078,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn PD01 = Satteldach</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Interim bis zum Dachbelegungstool – leer = 0 (UK Satteldach Kreuz je quer verlegtem Modul)</t>
         </is>
       </c>
     </row>
@@ -1047,17 +1095,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PD10</t>
+          <t>PD02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bemerkung</t>
+          <t>Dachziegel und Ortgang fotografiert?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Freitext groß</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1069,17 +1122,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AC-Elektromontage</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PA01</t>
+          <t>PD03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lage ZV</t>
+          <t>Gerüstart</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1089,7 +1142,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KG | EG | OG | DG | Sonstiges</t>
+          <t>Fanggerüst | Vollgerüst | Sonstiges</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1101,27 +1154,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AC-Elektromontage</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PA02</t>
+          <t>PD04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Neue ZV erforderlich?</t>
+          <t>Dachrinnenhöhe in m</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1133,17 +1181,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AC-Elektromontage</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PA03</t>
+          <t>PD05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Anzahl Felder</t>
+          <t>Verschattung vorhanden?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1153,61 +1201,61 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1-Feld | 2-Feld | 3-Feld | 4-Feld | Sonstige</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>nur wenn PA02 = Ja</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AC-Elektromontage</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PA04</t>
+          <t>PD06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ertüchtigung bestehender ZV?</t>
+          <t>Anzahl Optimierer (Verschattung und Module mit abweichender Neigung, z. B. Gaube)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>nur wenn PA02 = Nein</t>
+          <t>nur wenn PD05 = Ja</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tigo-Optimierer je betroffenem Modul – bei Verschattung sowie bei Modulen mit abweichender Neigung (z. B. auf einer Gaube)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AC-Elektromontage</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PA05</t>
+          <t>PD07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Externes APZ-Feld erforderlich?</t>
+          <t>Montage auf mehreren Dachseiten?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1222,66 +1270,56 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>nur wenn PA04 = Ja</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AC-Elektromontage</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PA06</t>
+          <t>PD08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HAK-Leitung erneuern?</t>
+          <t>Leitungslänge DC-Kabelweg in m</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>nur wenn PA04 = Ja</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AC-Elektromontage</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PA07</t>
+          <t>PD09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Unterverteilung erforderlich?</t>
+          <t>DC-kWp</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1293,27 +1331,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AC-Elektromontage</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PA08</t>
+          <t>PD10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tiefenerder vorhanden?</t>
+          <t>Bemerkung</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Freitext groß</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1330,17 +1363,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PA09</t>
+          <t>PA01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Leistung Wechselrichter in kW</t>
+          <t>Lage ZV</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>KG | EG | OG | DG | Sonstiges</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1357,17 +1395,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PA10</t>
+          <t>PA02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kapazität Batteriespeicher in kWh</t>
+          <t>Neue ZV erforderlich?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1384,12 +1427,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PA11</t>
+          <t>PA03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Friondo HEMS gewünscht?</t>
+          <t>Anzahl Felder</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1399,12 +1442,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>1-Feld | 2-Feld | 3-Feld | 4-Feld | Sonstige</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn PA02 = Ja</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1459,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PA12</t>
+          <t>PA04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>iMSys inkl. Smart Meter gewünscht?</t>
+          <t>Ertüchtigung bestehender ZV?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1436,7 +1479,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn PA02 = Nein</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1491,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PA13</t>
+          <t>PA05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Friondo SpotDynamic gewünscht?</t>
+          <t>Externes APZ-Feld erforderlich?</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1468,7 +1511,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn PA04 = Ja</t>
         </is>
       </c>
     </row>
@@ -1480,39 +1523,44 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PA14</t>
+          <t>PA06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bemerkung</t>
+          <t>HAK-Leitung erneuern?</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Freitext groß</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn PA04 = Ja</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Einschätzung</t>
+          <t>AC-Elektromontage</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>PA07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Einschätzung des Kunden</t>
+          <t>Unterverteilung erforderlich?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1522,47 +1570,320 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>heiß | warm | kalt</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>immer</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PA15</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Zählerzusammenlegung erforderlich?</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PA08</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tiefenerder vorhanden?</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PA09</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Leistung Wechselrichter in kW</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PA10</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Kapazität Batteriespeicher in kWh</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PA11</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Friondo HEMS gewünscht?</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PA12</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>iMSys inkl. Smart Meter gewünscht?</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PA13</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Friondo SpotDynamic gewünscht?</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PA14</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Freitext groß</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Einschätzung</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Einschätzung des Kunden</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>heiß | warm | kalt</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Einschätzung</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Wiedervorlage am</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>optional – leer lassen, wenn keine Wiedervorlage nötig</t>
         </is>
@@ -2292,6 +2613,7212 @@
       <c r="C1" t="inlineStr">
         <is>
           <t>Platzierung</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H177"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>PV-Nr.</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Datei</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Pos. in Datei</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>GUID</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Bezeichnung (1. Zeile)</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>VK netto (€)</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>EK (€)</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PV001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{58703D9A-CD96-4700-8BF4-5BF2828A5B75}</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Solar Fabrik Mono S4 Halfcut |Trend Full Black</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>87.75</v>
+      </c>
+      <c r="G2" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PV002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{0B58BD05-F465-4FAD-94EB-E17D40C98012}</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SOLARWATT Panel vision M 5.5 black 465W</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>69.59999999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PV003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{C838CCA2-87BA-4DF1-A32B-EA9C54751A3F}</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TW Solar N-type Half-cell Monofacial Dual</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>69.59999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PV004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{5616F536-C1A3-4179-BF89-E29046C1921B}</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aiko 465Wp | Glas-Glas | All Black</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>95.51000000000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PV005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{AF141391-468E-4FD2-A4A2-CE140FBE02FB}</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aiko 480Wp | Glas-Folie | Schwarz und Weiß</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>76.33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PV006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{5EED0618-B2E7-4ACE-A569-7A7DF35FA5BD}</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aiko 485Wp | Glas-Glas | All Black</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>129.98</v>
+      </c>
+      <c r="G7" t="n">
+        <v>108.32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PV007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{E18E5013-826B-4C1D-A172-CC69B90E4872}</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aiko 500 Wp Glas-Folie/Schwarz-Weiß</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>154</v>
+      </c>
+      <c r="G8" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PV008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{6D3D5D59-D544-4109-A0AD-9DE16D81CF6C}</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>JA Solar 465Wp | Glas-Glas | Schwarz-Weiß</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>81.97</v>
+      </c>
+      <c r="G9" t="n">
+        <v>68.31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PV009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{836812D6-DE39-4B0E-8EF7-B319EA434A8E}</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BISOL 305 Wp Terracotta- Terracotta</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>227.64</v>
+      </c>
+      <c r="G10" t="n">
+        <v>189.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PV010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{76084C03-25FB-4070-899A-CF75227E439E}</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Tigo TS4-A-OTigo TS4-A-O MC4 700W Optimierer</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PV011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{83C31928-D8EA-4861-B02B-791629D47202}</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Solar/Erdungskabel je weiterer Meter</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>26</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PV012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{EB962BA8-BB77-4FB3-861A-AE726567D901}</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Erdarbeiten zwischen Modulfeld bis zum Hauseinführung Boden auf eine Tiefe von ca. 40 cm ausheben.</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PV013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{9C125FF5-F2CF-459A-BDED-1A0E557CE6C5}</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>UK Satteldach Kreuz je Modul</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>123</v>
+      </c>
+      <c r="G14" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PV014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{AFC8855C-773E-4F16-86B4-27C2317384E1}</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>UK Flachdach S od. O/W je Modul</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>111</v>
+      </c>
+      <c r="G15" t="n">
+        <v>80.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PV015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{1EA3219E-605F-45C5-97EA-FE7F54517832}</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>UK Trapezblech/Sandwichpaneele/Ziegelimitatblech je Modul</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>104</v>
+      </c>
+      <c r="G16" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PV016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{19BFD7D6-CDC4-44D1-BE3C-81870C48EB1E}</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>UK Zaun je Modul</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PV017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{6ECF6556-838D-4EE9-BA52-4BAE9D70B290}</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Demontage PV-Module</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PV018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{50264AB8-217F-4B7F-BC4A-D0546C412ED1}</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Demontage alte PV-Anlage bis 20 Module</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PV019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{9D9A121D-5529-489E-9BE4-6DA1E00847BB}</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Gerüst / Absturzsicherung individuell</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>35</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PV020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{B0A40090-7526-4D19-AD7F-CDB24E46E286}</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Lastenlift für Modultransport inkl. An- und Abfahrt</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>538.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PV021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{F6023C70-455E-445F-9946-6E80929873F6}</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Demontage Solarthermie-Anlage bis 4 Kollektoren</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>929</v>
+      </c>
+      <c r="G22" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PV022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>022</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{E7DFB5AD-24F9-4860-A787-C058A41F8ECE}</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SAT Anlage versetzen</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>395</v>
+      </c>
+      <c r="G23" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PV023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>023</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{A17E39B4-AABE-49CA-B2FD-FC47CB2E9403}</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>DC Überspannungsschutz Typ 2, 3 MPPT</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>379</v>
+      </c>
+      <c r="G24" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PV024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>024</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{11B919F1-0F5A-4477-B7A0-28F1A73F68EE}</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sungrow Hybrid System 05/100 SBH</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>5882.6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4602</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PV025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{B3AC00B9-45C9-43A6-A8D2-0A47F16AC42B}</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sungrow Hybrid System 06/100 SBH</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>5999.4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4538</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PV026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{82279AB1-140E-41F7-BE44-A0D170F7FD2E}</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sungrow Hybrid System 08/100 SBH</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>6128.2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4714</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PV027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{9B63BED2-0489-4504-AF20-F48A2EF12841}</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sungrow Hybrid System 10/100 SBH</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>6316.4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4628</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PV028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>028</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{7B69FE94-3258-44E4-8A67-D92997042CB7}</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sungrow Hybrid System 15/100 SBH</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>7425.6</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5712</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PV029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>029</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{2F00CC40-281E-4997-9D2D-6A62D06E7C2D}</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sungrow Hybrid System 20/100 SBH</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>7846.7</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5959</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PV030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>030</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{B45AC270-C2FF-4759-B2C6-108C2BCF82FE}</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sungrow SBH 5 kWh Batteriemodul</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2210.04</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PV031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>031</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{F164DE3F-7DBC-4376-968B-8E4E72E5963D}</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Zähler-Komplettschrank 1-Feld inkl. Anbindung</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1708.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PV032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>032</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{638675A4-ADD0-4BED-8B0C-EC35FD7EAAF1}</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Zähler-Komplettschrank 3-Feld inkl. Anbindung</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2994.6</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PV033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>033</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{FD72629E-5BF7-46AB-8D6B-A16C50C5B072}</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Hensel Sicherungsgehäuse 2x3xNH00 bis 250A</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>880</v>
+      </c>
+      <c r="G34" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PV034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>034</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{676E9B4C-8ED0-4626-A45B-F1D7D941ACE9}</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Psl. Leistungsposition Elektroinstallation Zuleitung Zählerverlegung Keller</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1045</v>
+      </c>
+      <c r="G35" t="n">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PV035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>035</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{A49FC9E3-EA47-43ED-962F-F2180090A918}</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Durchführung Elektro-Leitungen inkl. Kernbohrung und Brandschutzabschottung</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>274.48</v>
+      </c>
+      <c r="G36" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PV036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>036</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{7F60A3CA-A270-4DDC-B601-8F1AEAD326DE}</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Wandlermessschrank inkl. Netz- und Erzeugungsmessung</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>9839</v>
+      </c>
+      <c r="G37" t="n">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PV037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>037</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{6C95DFD1-C4C9-478C-8355-56CF47D5B223}</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Umbau Bestands-Elektroverteilung / NSHV für PV-Anlage</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>6150</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PV038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>038</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{51CAF4F3-1CD9-476A-8C4C-42E964E9F761}</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Kabeltrasse inkl. liefern und montieren</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="G39" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PV039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>039</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{370359DA-9B95-4DF3-8E4F-61E665EBEEA5}</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Netz- und Anlagenschutz (NA-Schutz) bis 86,3 kVA</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>3720</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PV040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>040</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{6CF63C3D-39BD-4ED4-A403-CE44040D43DB}</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Fernwirktechnik / Rundsteuerempfänger (RSE) zur Einspeisesteuerung beim Netzbetreibers</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>940</v>
+      </c>
+      <c r="G41" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PV041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>041</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{8C51DEBD-4A25-4A84-A626-0092552A5BB6}</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Redispatch-2.0- und Direktvermarktungsschnittstelle</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>7872.9</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4890</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PV042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>042</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{FACE899F-344E-4F55-ABDE-53EBD61123A8}</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Privater Unterzähler inkl. Anbindung</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>217</v>
+      </c>
+      <c r="G43" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PV043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>043</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{4DCAB2EC-25F5-4CF7-844C-ED5528DA4C8F}</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SLS Hauptschalter inkl. Installation und Montage. Dieser ist zwingend nach aktueller TAB des EVU notwendig</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="G44" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PV044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{E7B1B913-5D15-4BF8-B54E-AA859DCA9ACC}</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AC Überspannungsschutz inkl. Installation und Montage. Dieser ist zwingend nach aktueller TAB des EVU notwendig</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>267.2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PV045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>045</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{6BF1234A-D742-42D3-8DBE-88E89B590077}</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>5x16mm Hauptleitung von HAK bis ZV 10m zwecks Potentialausgleich inkl. Installation und Montage</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>236.6</v>
+      </c>
+      <c r="G46" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PV046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>046</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{F6A7F55B-7058-4603-8C8F-B13C78F34CF7}</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>5x25mm Hauptleitung von HAK bis ZV 10m zwecks Potentialausgleich inkl. Installation und Montage</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>416.6</v>
+      </c>
+      <c r="G47" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PV047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>047</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{2ACDC820-41BA-4B3B-AF76-B1E3E2D4CE85}</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>5x35mm Hauptleitung von HAK bis ZV 10m zwecks Potentialausgleich inkl. Installation und Montage</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>512</v>
+      </c>
+      <c r="G48" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PV048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>048</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{0B0417CE-1B4B-4B7F-A9F6-51F9D1D1554E}</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Hensel AP Automatengehäuse 2-reihig 24 Teilungseinheiten grau KV4548</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>293</v>
+      </c>
+      <c r="G49" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PV049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>049</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{C8D9FDB5-EA79-42EB-812A-C6C69A063C5F}</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Erdungsspieß</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>338</v>
+      </c>
+      <c r="G50" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PV050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>050</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{4D219A38-5B22-4513-A0B2-E907DF04955E}</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>APZ-Feld Aufrüstsatz extern inkl. Installation</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>262</v>
+      </c>
+      <c r="G51" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PV051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>051</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{46FBBC0F-F94F-49BC-9BEC-B5BF154B1AB1}</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Stundensatz Facharbeiter Elektrotechniker</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="G52" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PV052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>052</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{72B2ED71-E665-45AE-AFEC-76224772C8FC}</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Zählerzusammenlegung</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>448</v>
+      </c>
+      <c r="G53" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PV053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>053</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{CA9D908B-4F7F-44DE-944C-386D27BF327F}</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>eHZ-Adapterplatte</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>243</v>
+      </c>
+      <c r="G54" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PV054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{AF982B86-D581-4E95-BD33-6D4600E9C8C6}</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Koppelrelais §14a EnWG (EVU-Steuerung)</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>229</v>
+      </c>
+      <c r="G55" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PV055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>055</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{6959D872-2879-4266-842A-DF88B8E45F47}</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Demontage bestehendes AC-Systems</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PV056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>056</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{58D9BD8B-8F70-4E2A-9976-5468828A792C}</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Anschlussvorbereitung Ladestation mit Ladeanschlussleistung bis zu 11 KW</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1197.2</v>
+      </c>
+      <c r="G57" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PV057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>057</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{C584829D-9E9D-43CB-B950-4114F3FAC06B}</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Montage AC- Heizstab</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>315.9</v>
+      </c>
+      <c r="G58" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PV058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>058</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{AF052E1A-F604-4009-BCD5-3633CA347BFB}</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Mennekes AMTRON 4You 310 11 kW mit 7,5 m Ladekabel</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>983.54</v>
+      </c>
+      <c r="G59" t="n">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PV059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>059</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{6169A79C-1ABA-4DA3-B772-0BAB0A5EAF26}</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Mennekes AMTRON 4You 560 11 kW mit 7,5 m Ladekabel</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1390.55</v>
+      </c>
+      <c r="G60" t="n">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PV060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>060</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{FA921201-DD2C-4662-B94A-E1855E06FCC5}</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>my-PV AC-ELWA-2 stufenloser Heizstab 3,5 kW inkl. Installation und Konfiguration</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>978.3</v>
+      </c>
+      <c r="G61" t="n">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PV061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>061</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{A46EE42F-A41A-43E9-BC52-9B1E760D08EE}</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Friondo HEMS</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>949</v>
+      </c>
+      <c r="G62" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PV062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>062</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{ADC8A4A0-5E8A-48D3-8058-D1F065A8C8BC}</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Datenkabel CAT 7 1000 MHz oder RS485 Leitung inkl. anteilig Kanal, Rohr bzw. Druckschellen (Aufputz-Verlegung) und Anschluss für Wärmepumpe, Wechselrichter/Batteriespeicher und Wallbox</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G63" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PV063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>063</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{4AD474E1-85A2-481C-B2BA-DE841CCA8710}</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>TP-LINK TL-SG108S 8-PORT GIGABIT SWITCH METALLGEHÄUSE Switch 8</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="G64" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PV064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Ersatz Position PV</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{2966C36D-FCEB-4B1C-A50D-35AF5B5218C7}</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Voranmeldung "iMSys" und dynamischen Stromtarif "enni.flexstrom "</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PV065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{7D800B33-176D-4730-96C4-8AFEDABA372A}</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Sigenergy Energy Gateway 3Ph Ersatzstrom inkl. Installation</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1091.8</v>
+      </c>
+      <c r="G66" t="n">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PV066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{C65C14C5-89A9-4005-97D5-D25A76C818A8}</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Sigen EV DC Charging Module 12 kW 10m Cable CCS2 inkl. Installation</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>2367.12</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PV067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{F446CBD7-28E9-454C-B971-B4AA1FA68D88}</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Sigen EV DC Charging Module 25 kW 10m Cable CCS2 inkl. Installation</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>3126.31</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1860.9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PV068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{5C0685DE-C31A-4574-9CEE-969F90592B23}</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Sigen Mirco Inverter 1000W 2-in-1 inkl. Installation</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>198.77</v>
+      </c>
+      <c r="G69" t="n">
+        <v>129.54</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PV069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{D14DD365-D1AA-4929-9107-E7797C4792A9}</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>SigenStor Batterie 6.0</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>2626.97</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1903.6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PV070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{65BA58ED-47A5-48BC-BA13-537401A35E1A}</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>SigenStor Batterie 10.0</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>3326.96</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2410.84</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PV071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{AD7AA298-187A-4CA5-993C-8C21EB7117EE}</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System TP2 06/06</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>3980.06</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2842.9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PV072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{A6392A14-E057-4B8A-BE42-EB0E84A268CF}</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System TP2 06/10</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>4890.01</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3349.32</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PV073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{4FD0A877-621E-4A64-BD48-5035B2520EF4}</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System TP2 08/10</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>4945.2</v>
+      </c>
+      <c r="G74" t="n">
+        <v>3389.43</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PV074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{4EAD8BCF-D6B1-4320-8186-5A4C8F749B60}</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System TP2 08/12</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>6559.6</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4685.43</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PV075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{C2B10DED-A950-491F-8DF7-82F1C461AB33}</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System TP2 10/10</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>4818.46</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3441.76</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PV076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{EF6189DF-D209-47A6-BE38-1082AC343790}</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System TP2 10/12</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>6727.15</v>
+      </c>
+      <c r="G77" t="n">
+        <v>4737.43</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PV077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{641AC55D-30BF-452F-B3EE-C844D07D4F78}</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System TP2 10/16</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>7342.85</v>
+      </c>
+      <c r="G78" t="n">
+        <v>5244.89</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PV078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{0F40733C-61F4-436A-B734-81321C6E9DB1}</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System TP2 10/20</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>8169.12</v>
+      </c>
+      <c r="G79" t="n">
+        <v>5752.9</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PV079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{3BBF5E54-FFAF-41FE-98CA-16087332C8F6}</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System TP2 12/10</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>4846.27</v>
+      </c>
+      <c r="G80" t="n">
+        <v>3461.62</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PV080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{606AE1D1-FFEE-4DD1-92AD-274B53503C2E}</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System TP2 12/12</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>6658.4</v>
+      </c>
+      <c r="G81" t="n">
+        <v>4756</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PV081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{1E74D3A4-79FA-4361-A8C6-A54C2442E4CE}</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System TP2 12/16</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>7369.88</v>
+      </c>
+      <c r="G82" t="n">
+        <v>5264.2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PV082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{DA0BBFE2-42FF-49CF-A5C6-C6BF54FF66AD}</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System TP2 12/20</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>8249.5</v>
+      </c>
+      <c r="G83" t="n">
+        <v>4714</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PV083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{C3FCAC28-7B4F-4DD6-B50F-DC63C22E4A24}</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System SigenStor 10/10</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>5818.53</v>
+      </c>
+      <c r="G84" t="n">
+        <v>4126.62</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PV084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{F0D179E7-7155-4E56-8E08-B418D18ED881}</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System SigenStor 10/12</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>7645.89</v>
+      </c>
+      <c r="G85" t="n">
+        <v>5422.62</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PV085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>022</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{3EF8E9EC-ACC1-4BE9-8E13-3C528AE1E064}</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System SigenStor 10/16</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>8301.469999999999</v>
+      </c>
+      <c r="G86" t="n">
+        <v>5929.62</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PV086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>023</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{1107240A-6F11-403F-8525-A5F807E19FB2}</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System SigenStor 10/20</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>9013.549999999999</v>
+      </c>
+      <c r="G87" t="n">
+        <v>6637.32</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PV087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>024</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{40203154-2095-42D2-AEA2-3D8DAF7365DF}</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System SigenStor 12/12</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>8066.07</v>
+      </c>
+      <c r="G88" t="n">
+        <v>5720.62</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>PV088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{0F0BDF15-448F-46D4-A427-BF18F2D6B383}</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System SigenStor 12/16</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>8781.34</v>
+      </c>
+      <c r="G89" t="n">
+        <v>6227.9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>PV089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{160F5B6A-7DC5-4E74-9C69-67BDF41DF66E}</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System SigenStor 15/10</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>6559.32</v>
+      </c>
+      <c r="G90" t="n">
+        <v>4652</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>PV090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{EF88B8B3-E3B1-4323-913B-D7DBB68F0670}</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System SigenStor 15/12</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>8445.040000000001</v>
+      </c>
+      <c r="G91" t="n">
+        <v>5947.21</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>PV091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>028</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{87B2F31F-3CC3-49D0-9AE7-62F288784DBA}</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System SigenStor 15/16</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>9102.16</v>
+      </c>
+      <c r="G92" t="n">
+        <v>6455.43</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>PV092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>029</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{804FB2A8-4FDD-49B4-8763-80E845CB71B5}</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System SigenStor 17/16</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>9348.77</v>
+      </c>
+      <c r="G93" t="n">
+        <v>6583.64</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PV093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>030</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{E1AD2860-6C91-4764-BD4C-A575A90AACDF}</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System SigenStor 17/20</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>10140.53</v>
+      </c>
+      <c r="G94" t="n">
+        <v>7091.28</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>PV094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>031</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{1671380C-1D26-4BDA-AD16-5DC08287F907}</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System SigenStor 20/16</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>10227.83</v>
+      </c>
+      <c r="G95" t="n">
+        <v>7210.84</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>PV095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>032</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{0DC52261-3258-4F2F-883F-A52FC9A2BE76}</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System SigenStor 20/20</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>10527.83</v>
+      </c>
+      <c r="G96" t="n">
+        <v>7210.84</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>PV096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>033</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{F6B78AF5-0971-487A-BD72-C23389A4D978}</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System SigenStor 25/30</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>14679.47</v>
+      </c>
+      <c r="G97" t="n">
+        <v>9918.559999999999</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>PV097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>034</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{56124E0D-1319-495E-BA48-D9C50287E25C}</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System SigenStor 30/30</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>15059</v>
+      </c>
+      <c r="G98" t="n">
+        <v>9918.559999999999</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>PV098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>035</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{06B658D4-36D0-4224-B7C5-68A1F9E3BD3F}</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid Wechselrichter 50kW M1-HYA ohne Backup Port</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>3881.17</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2733.22</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>PV099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>036</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{7B058F5F-34D6-48CC-8C3D-76E08108C432}</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid Wechselrichter 50kW M1-HYB mit Backup Port</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>6455.26</v>
+      </c>
+      <c r="G100" t="n">
+        <v>4610.9</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>PV100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>037</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{ED034BE7-8CD0-40C8-A461-00AF7E90C4B9}</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Sigenergy String Wechselrichter 50kW M1 ohne Backup Port</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>3198.13</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2175.6</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>PV101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>038</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{E91BC364-C028-445B-9FA3-CB1A3A4CD9AA}</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid Wechselrichter 60kW M1-HYA ohne Backup Port</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>4041.21</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2845.92</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>PV102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>039</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{F4A04725-7804-4F6F-BE5B-D71C6CA846E4}</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid Wechselrichter 60kW M1-HYB mit Backup Port</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>6813.35</v>
+      </c>
+      <c r="G103" t="n">
+        <v>4866.68</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>PV103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>040</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{39AED609-517F-4A44-A7A4-AFF7C404BEEF}</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Sigenergy String Wechselrichter 60kW M1 ohne Backup Port</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>3318.09</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2288.34</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PV104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>041</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{A1034CFB-7009-4C81-9708-86BFE58226B1}</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid Wechselrichter 80kW M1-HYA ohne Backup Port</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>5281.12</v>
+      </c>
+      <c r="G105" t="n">
+        <v>3719.1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>PV105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>042</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>{C8F5ABB1-F3FB-4585-B525-73EFC730B0D1}</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid Wechselrichter 80kW M1-HYB mit Backup Port</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>7709.27</v>
+      </c>
+      <c r="G106" t="n">
+        <v>5506.62</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>PV106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>043</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>{EBDAC9DA-268A-4018-BFAC-4533C9ECBAFB}</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Sigenergy String Wechselrichter 80kW M1 ohne Backup Port</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>4401.63</v>
+      </c>
+      <c r="G107" t="n">
+        <v>3099.74</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>PV107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>{DDD902D4-5B1F-4104-AD63-807705BA4F8A}</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid Wechselrichter 100kW M1-HYA ohne Backup Port</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>5681.9</v>
+      </c>
+      <c r="G108" t="n">
+        <v>4001.34</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>PV108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>045</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{F66BD354-64C6-415F-83F7-C97BADD18551}</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid Wechselrichter 100kW M1-HYB mit Backup Port</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>8426.82</v>
+      </c>
+      <c r="G109" t="n">
+        <v>6019.16</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>PV109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>046</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{417DBC6B-EAB6-47B3-BE01-70A03A0F4C42}</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Sigenergy String Wechselrichter 100kW M1 ohne Backup Port</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>4641.44</v>
+      </c>
+      <c r="G110" t="n">
+        <v>3245.76</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>PV110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>047</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{ADDBBFD0-13B8-4AC5-8B90-13498322FB38}</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid Wechselrichter 110kW M1-HYA ohne Backup Port</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>5841.94</v>
+      </c>
+      <c r="G111" t="n">
+        <v>4114.04</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>PV111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>048</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{260A3DB5-A5C6-4988-8357-73EC915D31B4}</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid Wechselrichter 110kW M1-HYB mit Backup Port</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>8606.559999999999</v>
+      </c>
+      <c r="G112" t="n">
+        <v>6147.54</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>PV112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>049</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{E1017E02-7CB6-4CDE-B267-66F88B2AF65C}</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Sigenergy String Wechselrichter 110kW M1 ohne Backup Port</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>4767.21</v>
+      </c>
+      <c r="G113" t="n">
+        <v>3381</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>PV113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>050</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{B169081C-5A14-48AE-9CA6-2B962C13D728}</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid Wechselrichter 125kW M1-HYA ohne Backup Port</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>8606.559999999999</v>
+      </c>
+      <c r="G114" t="n">
+        <v>4339.44</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>PV114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>051</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{8FCA038E-7A92-4130-8F8A-0E50D715BCE4}</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Sigenergy String Wechselrichter 125kW M1 ohne Backup Port</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>5157.15</v>
+      </c>
+      <c r="G115" t="n">
+        <v>3606.4</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>PV115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>052</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{B580D32C-B969-4147-BE8A-5B9CBAADF4FA}</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Sigenergy Power Sensor 300A CT</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>262.79</v>
+      </c>
+      <c r="G116" t="n">
+        <v>169.54</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>PV116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>053</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{33C9E52E-CF4D-4EB3-B636-F83FDDD25815}</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Sigenergy SigenStack Batteriemanagement BC M2-1C-BST</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>5909.99</v>
+      </c>
+      <c r="G117" t="n">
+        <v>4282.6</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>PV117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{42E16D2C-281B-4C89-93C9-8A930B4B8846}</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Sigenergy SigenStack BC-Kabel 4M</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>244.14</v>
+      </c>
+      <c r="G118" t="n">
+        <v>169.54</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>PV118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>055</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{682CA683-BA94-49C7-B037-0A89C542F51C}</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Sigenergy SigenStack Cover</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>244.14</v>
+      </c>
+      <c r="G119" t="n">
+        <v>169.54</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>PV119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>056</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{F920CE13-52D6-40B1-B994-60A6204AEAE1}</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Sigenergy SigenStack Base MAIN-1C</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>911.9</v>
+      </c>
+      <c r="G120" t="n">
+        <v>620.34</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>PV120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>057</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{A4889A66-CC4B-4EE4-9CDE-DC89CA2BE5B7}</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Sigenergy SigenStack Base SUB-1C</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>911.9</v>
+      </c>
+      <c r="G121" t="n">
+        <v>620.34</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>PV121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>058</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{48704B4C-F452-4AD1-9463-671201D73C9F}</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Sigenergy SigenStack 12,06kWh</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>2579.18</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1803.62</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>PV122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{3217ADBC-023A-4D49-8D80-56E59119CEA9}</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Zähler-Komplettschrank 1-Feld inkl. Anbindung</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>1708.5</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>PV123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{26E407AA-60CD-41CD-82FB-E622288D57F4}</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Zähler-Komplettschrank 2-Feld inkl. Anbindung</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>2320</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>PV124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{C3F3A849-AC2A-4187-8940-0E66731722D2}</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Zähler-Komplettschrank 3-Feld inkl. Anbindung</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>2994.6</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>PV125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{B354F171-EE41-47F3-AEB4-085662DA37F8}</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Wandlermessschrank inkl. Netz- und Erzeugungsmessung</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>9839</v>
+      </c>
+      <c r="G126" t="n">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PV126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{4ECEDD1F-64EE-42B0-B4D2-6739C73328A0}</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Zählerzusammenlegung</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>548</v>
+      </c>
+      <c r="G127" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>PV127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>{65997A3D-DE4B-47A2-84CC-00D73D1D5C64}</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>TECGET Feuchtraumverteiler, IP 65, 24 TE 2-reihig, mit Tür, Gehäuse + Tür PC</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>293</v>
+      </c>
+      <c r="G128" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>PV128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>{EF687803-31D3-4735-A5B3-E41C62956427}</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>TECGET Feuchtraumverteiler, IP 65, 36 TE 3-reihig, mit Tür, Gehäuse + Tür PC</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>343</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>PV129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>{B2C7EC70-6196-4A17-964B-D2564AC160DD}</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>TECGET Feuchtraumverteiler, IP 65, 48 TE 4-reihig, mit Tür, Gehäuse + Tür PC</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>383</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>PV130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>{E838B9BB-77FB-4DBB-9C11-87E8CDD21891}</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Hager VA12CN AP Kleinverteiler 1-reihig 12 PLE mit Tür, bis 63A</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>115</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>PV131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>{5B4B3DC2-2D58-4B91-A969-E57A0F36E2EC}</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Hager VA24CN AP Kleinverteiler 2-reihig 24 PLE mit Tür, bis 63A</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>195</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>PV132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>{F7ED81AF-C3FA-4CE1-A6B5-0C6D58B61E8B}</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Hager VA36CN AP Kleinverteiler 3-reihig 36 PLE mit Tür, bis 63A</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>275</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>PV133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>{2FA60813-8638-458C-9493-26DAFBF76EC0}</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Hager VA48CN AP Kleinverteiler 4-reihig 48 PLE mit Tür, bis 63A</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>355</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>PV134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>{D9717020-AEDF-43DF-823E-2220DF27DD47}</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>SLS Hauptschalter inkl. Installation und Montage</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>220.8</v>
+      </c>
+      <c r="G135" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>PV135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>{14EC21E0-8773-4231-9D00-9E08D5ABD77F}</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AC Überspannungsschutz inkl. Installation und Montage</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>298</v>
+      </c>
+      <c r="G136" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>PV136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>{95ADDC47-7266-401C-ADB9-463625DD93F0}</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>APZ-Feld Aufrüstsatz extern inkl. Installation</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>326.8</v>
+      </c>
+      <c r="G137" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>PV137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>{EFD6B514-2B06-494D-AEE7-D180B1F8EF3F}</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Koppelrelais §14a EnWG (EVU-Steuerung)</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>229</v>
+      </c>
+      <c r="G138" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>PV138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>{B02A0F96-8E9B-45C4-B0D3-5D7F1228A678}</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-V Material-Set Elektro u.a Klemmen, Verdrahtung, Aderenthülsen</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>356</v>
+      </c>
+      <c r="G139" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>PV139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>{4B76D278-4730-44D2-B546-E163725BC83F}</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>eHZ-Adapterplatte</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>243</v>
+      </c>
+      <c r="G140" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>PV140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>{539C79EE-989F-4D50-A317-0C364EB524FD}</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>5x16mm Hauptleitung von HAK bis ZV 10m zwecks Potentialausgleich inkl. Installation und Montage</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>280</v>
+      </c>
+      <c r="G141" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>PV141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>{5EF219D0-DFBF-4EC7-B06D-1057CD0061D0}</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>5x16mm Hauptleitung von HAK bis ZV 10m zwecks Potentialausgleich inkl. Installation und Montage</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>236.6</v>
+      </c>
+      <c r="G142" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>PV142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>{70DF6624-3887-494D-8971-6DD45292BD77}</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>5x25mm Hauptleitung von HAK bis ZV 10m zwecks Potentialausgleich inkl. Installation und Montage</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>416.6</v>
+      </c>
+      <c r="G143" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>PV143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>022</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>{9C480957-0E27-4CD2-989A-BE49F286715A}</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>5x35mm Hauptleitung von HAK bis ZV 10m zwecks Potentialausgleich inkl. Installation und Montage</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>512</v>
+      </c>
+      <c r="G144" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>PV144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>023</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>{926B4589-7746-4693-85AE-B09469F91B19}</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Zähler-WP Tarif inkl. Anbindung Modul 2</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>1098.4</v>
+      </c>
+      <c r="G145" t="n">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>PV145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>024</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>{A1FFB9EE-228D-496A-A434-6C4AD3D7FBDF}</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Netzanmeldung beim EVU für Wärmepumpenzähler nach §14a EnWG inkl. Verdrahtung</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>330</v>
+      </c>
+      <c r="G146" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>PV146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>{F676DC93-3060-48C3-9AC4-219F38B02DEC}</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Fernwirktechnik / Rundsteuerempfänger (RSE) zur Einspeisesteuerung beim Netzbetreibers</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>940</v>
+      </c>
+      <c r="G147" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>PV147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>026</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>{135453BC-39E7-41E5-9D4C-B945998B7A0C}</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Hensel Sicherungsgehäuse 2x3xNH00 bis 250A 5p Mi 6426</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>880</v>
+      </c>
+      <c r="G148" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>PV148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>{7B82BCAE-C7C5-4D34-986E-4A43343CC8C5}</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Erdungsspieß</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>338</v>
+      </c>
+      <c r="G149" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>PV149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>028</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>{6F1783BB-C235-4029-8118-441CD3F59BC8}</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Privater Unterzähler inkl. Anbindung</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>217</v>
+      </c>
+      <c r="G150" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>PV150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>029</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>{334C7D9B-928D-4CDD-B564-163242196D2E}</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Hager ADS920D FI-LS 3P+N 6kA B-16A 30mA A QC</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>91.36</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>PV151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>030</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>{C641C9AB-58B8-4D3F-A25D-D2FAD37C150F}</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Hager ADS920D FI-LS 3P+N 6kA B-20A 30mA A QC</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>96.14</v>
+      </c>
+      <c r="G152" t="n">
+        <v>66.3</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>PV152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>031</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>{3203A0A3-F390-415B-B804-293BE02DA600}</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Kabeltrasse inkl. liefern und montieren</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="G153" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>PV153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>032</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>{A8E6E4D4-9DB0-4A6D-9E69-CA074242E017}</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Fahrtkostenpauschale Zone 1, bestehend aus:</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G154" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>PV154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>033</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>{C1068B18-1CFD-4C90-A290-093DB0F9F2BB}</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Service &amp; Handlingpauschale</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G155" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>PV155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>034</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>{8EB5151B-8586-4822-9D16-9813D32E18D0}</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Arbeitslohn Friondo -Tarifgruppe E</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>89</v>
+      </c>
+      <c r="G156" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>PV156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>035</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>{F9EF0D11-DA0C-43BE-A8CC-AF9125D92545}</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Datenkabel CAT 7 1000 MHz oder RS485 Leitung inkl. anteilig Kanal, Rohr bzw. Druckschellen (Aufputz-Verlegung) und Anschluss für Wärmepumpe, Wechselrichter/Batteriespeicher und Wallbox</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G157" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>PV157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>036</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>{6DFFE7A4-6B0E-41C6-9FE9-08E05B068C67}</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>TP-LINK TL-SG108S 8-PORT GIGABIT SWITCH METALLGEHÄUSE Switch 8</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G158" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>PV158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>037</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>{8E131077-8CDD-4B99-9586-CF5B8C5A883C}</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>my-PV AC-ELWA-2 stufenloser Heizstab 3,5 kW inkl. Installation und Konfiguration</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>978.3</v>
+      </c>
+      <c r="G159" t="n">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>PV159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Elektro Allgemein</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>038</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>{1570E514-199F-4CFC-8702-8649EDE102C6}</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Anschlussvorbereitung Ladestation mit Ladeanschlussleistung bis zu 11 KW</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>1397.2</v>
+      </c>
+      <c r="G160" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>PV160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>{2120790A-218A-4DB8-91F1-945CC050A7EB}</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Solar Fabrik Mono S4 Halfcut |Trend Full Black</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>87.75</v>
+      </c>
+      <c r="G161" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>PV161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>{DBD2D0F9-34E3-4B20-B053-8622FBF16580}</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Solar/Erdungskabel Set je String</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>192</v>
+      </c>
+      <c r="G162" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>PV162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>{3DE96C8B-5D15-4513-AECF-BDDC1EFCDF35}</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>UK Satteldach je Modul</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>99</v>
+      </c>
+      <c r="G163" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>PV163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>{52A30880-B2B9-445A-B43F-32B3F2658427}</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Montage je Modul, DC-Verkabelung bis zum Wechselrichter</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>118</v>
+      </c>
+      <c r="G164" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>PV164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>{BC292EA5-3F31-40F3-8B0A-7BF7F99EBA1A}</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Gerüst / Absturzsicherung</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>735</v>
+      </c>
+      <c r="G165" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>PV165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>{0BC919CF-93D3-4A60-BB48-7923F428B1B1}</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System TP2 08/10</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>4945.2</v>
+      </c>
+      <c r="G166" t="n">
+        <v>3389.43</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>PV166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>{D520456C-20FD-40E5-B0A2-48F3FE0CAA0F}</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Sigenergy Energy Gateway 3Ph Ersatzstrom inkl. Installation</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>980</v>
+      </c>
+      <c r="G167" t="n">
+        <v>637</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>PV167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>{3776FEC4-2134-4874-807D-D57EF75FA117}</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Elektroarbeiten AC ab Wechselrichter</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>2228</v>
+      </c>
+      <c r="G168" t="n">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>PV168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>{BDAA07E2-2D18-41DC-A15B-96114EE0648B}</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Zähler-Komplettschrank 2-Feld inkl. Anbindung</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>2320</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>PV169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>{AD6B2C41-D97B-485E-914F-5924B9036F85}</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>DC Überspannungsschutz Typ 2, 2 MPPT</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>292</v>
+      </c>
+      <c r="G170" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>PV170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>{C39B7F9E-29AA-4AA5-95A0-EE01D9F3EF3D}</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Planung, Netzanmeldung und Inbetriebnahme</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>495</v>
+      </c>
+      <c r="G171" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>PV171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>{36C0CF86-C2F1-4405-A13D-8ABB1C5FF7F5}</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>An,- Abfahrt,- Müllentsorgung</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>150</v>
+      </c>
+      <c r="G172" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>PV172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>{999F804C-AB61-465D-BC89-C0C80784E65D}</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Friondo "fit for future"</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>599</v>
+      </c>
+      <c r="G173" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>PV173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>{C0090565-62B3-481F-8E46-81D1650EFAF5}</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Friondo HEMS</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>PV174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>{CBFBE25D-6728-4D79-8C94-BEB7C2B0F430}</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Friondo "iMSys"</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>PV175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>{AF001A5C-089C-4FAD-9B32-356DD0B36562}</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Friondo "SpotDynamic"</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>PV176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Musterangebot PV</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>{199A52D9-E3F5-4AC0-AA79-DA783C9127AC}</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>abzgl. Rabatt</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Frage</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Antwort / Bedingung</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Aktion</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Zusatzbedingung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>PB01</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Maximalbelegung</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Modulanzahl = Maximalbelegung (PD12)</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Auslegung siehe PV-Parameter</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>PB01</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Bedarfsorientierte Belegung</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Modulanzahl = aufrunden((Haushalt × 1,3 + WP × 1,5 + Wallbox) ÷ 960 ÷ 0,455), gedeckelt auf PD12</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Deckel wird im Protokoll und in der Auslegungszeile vermerkt</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>PD01</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Satteldach</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: PV162 × (Module − quer) + PV013 × quer</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>UK Satteldach je Modul; quer verlegte Module (PD13) als UK Satteldach Kreuz</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>PD01</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Walmdach</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: PV162 × (Module − quer)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>[ANNAHME] Walmdach wie Satteldach (ohne Quer-Abfrage)</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>PD01</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Flachdach</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Unterkonstruktion lt. PD11</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>PD01</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Sonstige</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Dachart nicht konfigurierbar</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>PD11</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Ost/West / Süd</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: PV014 × Modulanzahl</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Eine Position „UK Flachdach S od. O/W je Modul“ für beide Ausrichtungen</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>PD03</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Fanggerüst</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: PV164 ×1</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Gerüst / Absturzsicherung</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>PD03</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Vollgerüst / Sonstiges</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Gerüstart nicht konfigurierbar (Vollgerüst/Sonstiges)</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>PD05</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>PD06 folgt</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>PD05</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>PD06</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Anzahl</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: PV010 × Eingabe</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Tigo TS4 Optimierer (0 = keine Position)</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>PD07</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>2 belegte Dachseiten → mind. 2 Strings</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>PD07</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>1 Dachseite</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>PA03 folgt</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>PA04 folgt</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>1-Feld / 2-Feld / 3-Feld</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: PV122 / PV123 / PV124 ×1</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Zähler-Komplettschrank aus der Liste „Elektro Allgemein“</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>4-Feld / Sonstige</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Zählerschrank nicht konfigurierbar (4-Feld/Sonstige)</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>4-Feld: keine Position in den PV-Listen</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Ertüchtigung bestehender ZV – Positionen noch nicht hinterlegt</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>[OFFEN] Positionen für Ertüchtigung/APZ/HAK-Leitung (PA05/PA06) noch festzulegen</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>PA07</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: PV132 ×1</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Hager VA36CN AP Kleinverteiler 3-reihig 36 PLE – nur ohne neue ZV</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>nur wenn PA02 = Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>PA07</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>PA15</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: PV052 ×1</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Zählerzusammenlegung (Liste „Ersatz Position PV“)</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>PA15</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>PA08</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>PA08</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: PV049 ×1</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Erdungsspieß</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>PA11</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 015 ×1</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Friondo HEMS (analog WP P01)</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>PA12</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 016 ×1</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>iMSys – aktiviert Vollmacht-Seite</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PA13</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 017 ×1</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>SpotDynamic – aktiviert Vollmacht-Seite</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Gruppen-Trigger</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>mind. ein Ja bei PA11–PA13</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 014 ×1</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Friondo „fit for future“ 599 € (Profile Enni/SWD wie WP)</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Grundpaket</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: PV001 × Modulanzahl · PV161 × Strings · PV163 × Modulanzahl · PV065 (EP) ×1 · PV167 ×1 · PV170 ×1 · PV171 ×1</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Module · Solar/Erdungskabel-Set je String · Montage je Modul · Energy Gateway (EP) · Elektroarbeiten AC · Planung/Netzanmeldung · An-/Abfahrt</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Strings</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>bis 2</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: PV169 ×1</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>DC-Überspannungsschutz Typ 2, 2 MPPT</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Strings</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>3 – 3</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: PV023 ×1</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>DC-Überspannungsschutz Typ 2, 3 MPPT</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Strings</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>4 – 4</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: PV169 ×2</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>2 × Typ 2, 2 MPPT</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Strings</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>über 4</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: DC-Überspannungsschutz für mehr als 4 Strings nicht konfigurierbar</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>WR/Speicher</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>lt. Auslegung</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Sigenergy-Kombination aus dem Artikelstamm: WR-Stufe ≥ kWp ÷ 1,2 (TP2 6–12 kW, SigenStor 15–30 kW), Speicher = nächste Stufe ≥ PA10</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>[ANNAHME] – kein Treffer → AMPEL „WR/Speicher-Kombination nicht im Sortiment“</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Überschrift im Angebot</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Inhalt</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Wann</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>DYNAMISCH: 'Komplettpaket {kWp} kWp PV-Anlage inkl. PV-Module, Wechselrichter, Unterkonstruktion, Speicher und Montage zum Festpreis'</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>PV001 Module · WR/Speicher (Sigenergy lt. Auslegung) · PV010 Optimierer · PV161 Set je String · PV162 / PV013 / PV014 Unterkonstruktion · PV163 Montage · PV164 Gerüst · PV065 Energy Gateway (EP) · PV167 Elektroarbeiten AC · PV122 / PV123 / PV124 Zählerschrank · PV132 Unterverteilung · PV052 Zählerzusammenlegung · PV049 Erdungsspieß · PV169 / PV023 DC-Überspannungsschutz · PV170 Planung · PV171 An-/Abfahrt · Auslegungszeile (0,00 €)</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>(ohne Überschrift)</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Pos. 014 (Gruppen-Trigger) + gewählte 015 / 016 / 017</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>nur bei Friondo-Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Summenblock</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Netto · Umsatzsteuer 0 % (§ 12 Abs. 3 UStG) · Gesamt-Betrag = Netto · − Rabatt · = Endbetrag</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>kein KfW-/Förderblock</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Nachtexte</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Profil-Textblock PV: Nullsteuersatz-Hinweis · Zahlungsoptionen · „Ihre Beispielrechnung“ · Installationsvoraussetzungen · Unterschrift; Vollmacht nur bei PA12/PA13</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>siehe Parametrierung → Textblöcke</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Wert</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Einheit</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Modulleistung</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>kWp</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Solar Fabrik Mono S4 455 W</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Modul-Leerlaufspannung</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Voc je Modul</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Max. Stringspannung</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>→ max. Module je String = abrunden(1.000 ÷ 36,19) = 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Faktor Haushalt</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Bedarfsauslegung: Haushalt × Faktor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Faktor Wärmepumpe</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Bedarfsauslegung: WP-Strom × Faktor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Spezifischer Ertrag</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>960</v>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>kWh/kWp</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Bedarf ÷ Ertrag = kWp; Jahresertrag der Beispielrechnung</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>JAZ-Umrechnung Gas/Öl → Strom</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>WP-Strom = Gas-/Ölverbrauch (WP-Erfassung, A03) ÷ 3,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>WR-Faktor (kWp ÷ WR-Leistung)</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>[ANNAHME] benötigte WR-Leistung = kWp ÷ 1,2 → kleinste verfügbare Stufe darüber</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>WR-Stufen TP2</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>6; 8; 10; 12</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Sigenergy Hybrid System TP2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>WR-Stufen SigenStor</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>15; 17; 20; 25; 30</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Sigenergy SigenStor ab 15 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Max. WR-Leistung</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>darüber AMPEL (individuell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Eigenverbrauchsquote PV</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>[ANNAHME] Unternehmenspräsentation – Basisquote PV</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Eigenverbrauch Zuschlag Speicher</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>%-Punkte</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>[ANNAHME] additiv, wenn ein Speicher im Angebot ist</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Eigenverbrauch Zuschlag HEMS</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>%-Punkte</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>[ANNAHME] additiv, wenn Friondo HEMS (Pos. 015) im Angebot ist</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Strompreis</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>€/kWh</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Beispielrechnung – Ersparnis Eigenverbrauch</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Einspeisevergütung</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>€/kWh</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Beispielrechnung – Vergütung Einspeisung</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Hinweis nach Modulposition</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>*Die angebotenen PV-Modultypen stehen unter Vorbehalt der aktuellen Markt- und Lieferverfügbarkeit. Aufgrund der weltweiten Liefer- und Marktsituation behalten wir uns vor, in Rücksprache mit dem Kunden technisch und qualitativ gleichwertige Module anderer Hersteller bzw. Modultypen zu liefern und zu verbauen.</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>aus dem Musterangebot – wird an die Modulposition angehängt</t>
         </is>
       </c>
     </row>

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -15900,7 +15900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -16045,15 +16045,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>(Sigenergy-/Modul-Datenblatt – Zulieferung)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>wenn Sparte = PV</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>v13-PV: Datei nach Lieferung in anlagen/ legen und diese Zeile mit dem Dateinamen füllen (Klammern entfernen) – geht dann mit jedem PV-Angebot mit</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>(weitere Zeilen ergänzen)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Regeln: 'immer' | 'wenn &lt;Frage&gt; = &lt;Antwort&gt;' | 'wenn Pos. &lt;Nr&gt; im Angebot'</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>PDFs in den Ordner anlagen/ legen</t>
         </is>

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -16,13 +16,14 @@
     <sheet name="Angebotsaufbau" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Anhänge" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="KfW" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Fragen PV" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Fragen KL" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Vermerke" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="PV-Artikel" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Aktionen PV" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Angebotsaufbau PV" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="PV-Parameter" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="BAFA-Anlagen" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Fragen PV" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Fragen KL" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Vermerke" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="PV-Artikel" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Aktionen PV" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Angebotsaufbau PV" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="PV-Parameter" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +59,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +79,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EAF1F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -118,6 +128,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -590,6 +601,18 @@
       <c r="A16" t="inlineStr">
         <is>
           <t>v13-PV: Blätter „Aktionen PV“ (mit Spalte Zusatzbedingung), „Angebotsaufbau PV“, „PV-Parameter“ und „PV-Artikel“ (GUID → PV-Nr.; Pinning für den Import der PV-Positionslisten aus Artikel-Preislisten/PV/). PV-Artikel heißen PV001 … und werden wie „Pos. 045“ referenziert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BAFA-Anlagen</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>v19: Zuordnung WP-Paket (045–054) bzw. Klasse 15 + Inneneinheit (15+055 / 15+056) → BAFA-Anlagennummer, Gerätebezeichnung, Nennwärmeleistung für das BzA-Datenblatt; Schlüssel vorrat:… = Stammdaten ohne Konfigurator-Anbindung (Auswahl bei TAIFUN-Angeboten).</t>
         </is>
       </c>
     </row>
@@ -604,41 +627,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Seite</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Fragetext</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Typ</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Antwortmöglichkeiten</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Anzeigen wenn</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Schlüssel</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>BAFA-Anlagennummer</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Hersteller</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Gerätebezeichnung</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Nennwärmeleistung kW</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Kältemittel</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Netzdienlichkeit</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>E/E-Anzeige</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Hinweis</t>
         </is>
@@ -647,1245 +691,533 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Belegung</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PB01</t>
+          <t>16019273</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Belegungsart</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Maximalbelegung | Bedarfsorientierte Belegung</t>
-        </is>
+          <t>Compress CS3800iAW 4 OM-S (CS3800iAW 4 O-S + AWMi)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>R290</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Maximalbelegung = Modulanzahl lt. Dachbelegung · Bedarfsorientiert = aus den Verbrauchsangaben, gedeckelt auf die Maximalbelegung</t>
-        </is>
-      </c>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Objektdaten</t>
+          <t>046</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PO01</t>
+          <t>16019274</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gebäudeart</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>EFH | 2FH | REH | RMH | MFH | Gewerbe</t>
-        </is>
+          <t>Compress CS3800iAW 6 OM-S (CS3800iAW 6 O-S + AWMi)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>immer</t>
-        </is>
-      </c>
+          <t>R290</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Objektdaten</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PO02</t>
+          <t>16019275</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Baujahr Haus</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
-        </is>
+          <t>Compress CS3800iAW 7 OM-S (CS3800iAW 7 O-S + AWMi)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>immer</t>
-        </is>
-      </c>
+          <t>R290</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Objektdaten</t>
+          <t>048</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PO03</t>
+          <t>16019892</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Letzte Dachsanierung</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Freitext</t>
-        </is>
+          <t>Compress CS3800iAW 10 OM-T (CS3800iAW O-T + AWMi)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>R290</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>leer lassen, wenn unbekannt</t>
-        </is>
-      </c>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Objektdaten</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PO04</t>
+          <t>16019894</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(alt) Stromverbrauch inkl. WP &amp; WB in kWh</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
-        </is>
+          <t>Compress CS3800iAW 13 OM-T (CS3800iAW 13 O-T + AWMi)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>12.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>nur wenn PO04 ausgefüllt</t>
+          <t>R290</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nur Alt-Erfassungen vor v13 – ersetzt durch PO06–PO09</t>
-        </is>
-      </c>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Objektdaten</t>
+          <t>050</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PO06</t>
+          <t>16019269</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Stromverbrauch des Haushalts in kWh</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
-        </is>
+          <t>Compress CS3800iAW 4 OE-S (CS3800iAW 4 O-S + AWEi)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>R290</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ohne Wärmepumpe und Wallbox</t>
-        </is>
-      </c>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Objektdaten</t>
+          <t>051</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PO07</t>
+          <t>16019271</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stromverbrauch Wärmepumpe in kWh</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Aus WP-Erfassung ermitteln</t>
-        </is>
+          <t>Compress CS3800iAW 6 OE-S (CS3800iAW 6 O-S + AWEi)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>R290</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0 = keine Wärmepumpe. „Aus WP-Erfassung ermitteln“: Gas-/Ölverbrauch der WP-Erfassung dieses Vorgangs ÷ 3,5</t>
-        </is>
-      </c>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Objektdaten</t>
+          <t>052</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PO08</t>
+          <t>16019272</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wallbox geplant oder vorhanden?</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
+          <t>Compress CS3800iAW 7 OE-S (CS3800iAW 7 O-S + AWEi)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>immer</t>
-        </is>
-      </c>
+          <t>R290</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Objektdaten</t>
+          <t>053</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PO09</t>
+          <t>16019891</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Stromverbrauch Wallbox in kWh</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
-        </is>
+          <t>Compress CS3800iAW 10 OE-T (CS3800iAW 10 O-T + AWEi)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>nur wenn PO08 = Ja</t>
-        </is>
-      </c>
+          <t>R290</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Objektdaten</t>
+          <t>054</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PO05</t>
+          <t>16019893</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bemerkung</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Freitext groß</t>
-        </is>
+          <t>Compress CS3800iAW 13 OE-T (CS3800iAW 13 O-T + AWEi)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>12.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>immer</t>
-        </is>
-      </c>
+          <t>R290</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DC-Dachmontage</t>
+          <t>15+055</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PD01</t>
+          <t>16019200</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dachart</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Satteldach | Flachdach | Walmdach | Sonstige</t>
-        </is>
+          <t>Compress CS8800iAW 15 OMBD-T (B) (CS8800iAW 15 O-T (B) + AWMBi D)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>15</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>R290</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PRÜFPUNKT: Zusatz „(B)“ – gilt vorerst für weiße (030) und schwarze (031) Außeneinheit; eigene Nummer der weißen klären</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DC-Dachmontage</t>
+          <t>15+056</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PD11</t>
+          <t>16019199</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belegung (Flachdach)</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Ost/West | Süd</t>
-        </is>
+          <t>Compress CS8800iAW 15 OED-T (B) (CS8800iAW 15 O-T (B) + AWEi D)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>15</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>nur wenn PD01 = Flachdach</t>
+          <t>R290</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PRÜFPUNKT: Zusatz „(B)“ – gilt vorerst für weiße (030) und schwarze (031) Außeneinheit; eigene Nummer der weißen klären</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DC-Dachmontage</t>
+          <t>vorrat:hybrox21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PD12</t>
+          <t>16017387</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Maximale Modulanzahl lt. Dachbelegungstool</t>
+          <t>ait-deutschland GmbH</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Interim bis zum Dachbelegungstool – Pflicht (Deckel der Bedarfsauslegung)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DC-Dachmontage</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PD13</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>davon quer verlegte Module</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>nur wenn PD01 = Satteldach</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Interim bis zum Dachbelegungstool – leer = 0 (UK Satteldach Kreuz je quer verlegtem Modul)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>DC-Dachmontage</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PD02</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Dachziegel und Ortgang fotografiert?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>DC-Dachmontage</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PD03</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Gerüstart</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Fanggerüst | Vollgerüst | Sonstiges</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>DC-Dachmontage</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PD04</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Dachrinnenhöhe in m</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>DC-Dachmontage</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>PD05</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Verschattung vorhanden?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>DC-Dachmontage</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>PD06</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Anzahl Optimierer (Verschattung und Module mit abweichender Neigung, z. B. Gaube)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>nur wenn PD05 = Ja</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Tigo-Optimierer je betroffenem Modul – bei Verschattung sowie bei Modulen mit abweichender Neigung (z. B. auf einer Gaube)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>DC-Dachmontage</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>PD07</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Montage auf mehreren Dachseiten?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DC-Dachmontage</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>PD08</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Leitungslänge DC-Kabelweg in m</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DC-Dachmontage</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>PD09</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DC-kWp</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>DC-Dachmontage</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>PD10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Bemerkung</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Freitext groß</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AC-Elektromontage</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>PA01</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Lage ZV</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>KG | EG | OG | DG | Sonstiges</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AC-Elektromontage</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>PA02</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Neue ZV erforderlich?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AC-Elektromontage</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>PA03</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Anzahl Felder</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>1-Feld | 2-Feld | 3-Feld | 4-Feld | Sonstige</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>nur wenn PA02 = Ja</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AC-Elektromontage</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>PA04</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ertüchtigung bestehender ZV?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>nur wenn PA02 = Nein</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>AC-Elektromontage</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>PA05</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Externes APZ-Feld erforderlich?</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>nur wenn PA04 = Ja</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>AC-Elektromontage</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>PA06</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>HAK-Leitung erneuern?</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>nur wenn PA04 = Ja</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>AC-Elektromontage</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PA07</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Unterverteilung erforderlich?</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>AC-Elektromontage</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>PA15</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Zählerzusammenlegung erforderlich?</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AC-Elektromontage</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>PA08</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Tiefenerder vorhanden?</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AC-Elektromontage</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>PA09</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Leistung Wechselrichter in kW</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>AC-Elektromontage</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>PA10</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Kapazität Batteriespeicher in kWh</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>AC-Elektromontage</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>PA11</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Friondo HEMS gewünscht?</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>AC-Elektromontage</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>PA12</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>iMSys inkl. Smart Meter gewünscht?</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>AC-Elektromontage</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>PA13</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Friondo SpotDynamic gewünscht?</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>AC-Elektromontage</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>PA14</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Bemerkung</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Freitext groß</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Einschätzung</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Einschätzung des Kunden</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>heiß | warm | kalt</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Einschätzung</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>S02</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Wiedervorlage am</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>optional – leer lassen, wenn keine Wiedervorlage nötig</t>
+          <t>alpha innotec Hybrox 21</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>21</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Vorrat – geplante Klassenerweiterung (Komponenten/Preise offen)</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1943,17 +1275,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Objekt &amp; Anlage</t>
+          <t>Belegung</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KO01</t>
+          <t>PB01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gebäudeart</t>
+          <t>Belegungsart</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1963,34 +1295,44 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EFH | 2FH | REH | RMH | MFH | Gewerbe</t>
+          <t>Maximalbelegung | Bedarfsorientierte Belegung</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>immer</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Maximalbelegung = Modulanzahl lt. Dachbelegung · Bedarfsorientiert = aus den Verbrauchsangaben, gedeckelt auf die Maximalbelegung</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Objekt &amp; Anlage</t>
+          <t>Objektdaten</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KO02</t>
+          <t>PO01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Baujahr Haus</t>
+          <t>Gebäudeart</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>EFH | 2FH | REH | RMH | MFH | Gewerbe</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2002,27 +1344,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Objekt &amp; Anlage</t>
+          <t>Objektdaten</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KO03</t>
+          <t>PO02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kunde ist Eigentümer?</t>
+          <t>Baujahr Haus</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Ja | Nein, Zustimmung des Eigentümers liegt vor | Nein, Zustimmung noch nicht vorhanden</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2034,49 +1371,49 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Objekt &amp; Anlage</t>
+          <t>Objektdaten</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KO04</t>
+          <t>PO03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Anzahl Außengeräte</t>
+          <t>Letzte Dachsanierung</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1 | 2 | 3</t>
+          <t>Freitext</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>immer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>leer lassen, wenn unbekannt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Objekt &amp; Anlage</t>
+          <t>Objektdaten</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KO05</t>
+          <t>PO04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Anzahl zu klimatisierender Räume</t>
+          <t>(alt) Stromverbrauch inkl. WP &amp; WB in kWh</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2086,93 +1423,98 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn PO04 ausgefüllt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>öffnet je Raum einen eigenen Fragenblock</t>
+          <t>Nur Alt-Erfassungen vor v13 – ersetzt durch PO06–PO09</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Räume</t>
+          <t>Objektdaten</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KR01</t>
+          <t>PO06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raumbezeichnung</t>
+          <t>Stromverbrauch des Haushalts in kWh</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Freitext</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>je Raum (KO05)</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>z. B. Wohnzimmer</t>
+          <t>ohne Wärmepumpe und Wallbox</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Räume</t>
+          <t>Objektdaten</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KR02</t>
+          <t>PO07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lage des Raums</t>
+          <t>Stromverbrauch Wärmepumpe in kWh</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Auswahl</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Keller/Souterrain | Erdgeschoss | 1. OG | 2. OG | 3. OG+ | Dachgeschoss</t>
+          <t>Aus WP-Erfassung ermitteln</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>je Raum (KO05)</t>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0 = keine Wärmepumpe. „Aus WP-Erfassung ermitteln“: Gas-/Ölverbrauch der WP-Erfassung dieses Vorgangs ÷ 3,5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Räume</t>
+          <t>Objektdaten</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KR03</t>
+          <t>PO08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hauptzweck</t>
+          <t>Wallbox geplant oder vorhanden?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2182,93 +1524,83 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>hauptsächlich kühlen | kühlen und in der Übergangszeit heizen | regelmäßig heizen und kühlen</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>je Raum (KO05)</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Räume</t>
+          <t>Objektdaten</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KR04</t>
+          <t>PO09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Montageort Innengerät</t>
+          <t>Stromverbrauch Wallbox in kWh</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Außenwand | Innenwand | noch nicht bekannt</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>je Raum (KO05)</t>
+          <t>nur wenn PO08 = Ja</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Räume</t>
+          <t>Objektdaten</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KR05</t>
+          <t>PO05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Entfernung Innen- zu Außengerät</t>
+          <t>Bemerkung</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>bis 3 m | 3–5 m | 6–10 m | 11–15 m | über 16 m</t>
+          <t>Freitext groß</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>je Raum (KO05)</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Räume</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KR06</t>
+          <t>PD01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kondensatpumpe erforderlich?</t>
+          <t>Dachart</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2278,29 +1610,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Satteldach | Flachdach | Walmdach | Sonstige</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>je Raum (KO05)</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Räume</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KR07</t>
+          <t>PD11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Zuordnung zum Außengerät</t>
+          <t>Belegung (Flachdach)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2310,98 +1642,93 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1 | 2 | 3</t>
+          <t>Ost/West | Süd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>je Raum (KO05)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>es erscheinen nur so viele Optionen wie Außengeräte (KO04)</t>
+          <t>nur wenn PD01 = Flachdach</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Außengerät</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KA01</t>
+          <t>PD12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montageort Außengerät</t>
+          <t>Maximale Modulanzahl lt. Dachbelegungstool</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>auf dem Boden | an der Außenwand | auf einer Terrasse | auf einem Balkon | auf einem Flachdach | auf einem Schrägdach | noch unklar</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>immer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Interim bis zum Dachbelegungstool – Pflicht (Deckel der Bedarfsauslegung)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Außengerät</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KA02</t>
+          <t>PD13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Montagehöhe</t>
+          <t>davon quer verlegte Module</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>unter 2 m | 2–4 m | über 5 m</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn PD01 = Satteldach</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Interim bis zum Dachbelegungstool – leer = 0 (UK Satteldach Kreuz je quer verlegtem Modul)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Elektroinstallation</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KE01</t>
+          <t>PD02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Geeignete Stromversorgung nahe Außengerät?</t>
+          <t>Dachziegel und Ortgang fotografiert?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2411,7 +1738,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ja | Nein | Unklar</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2423,17 +1750,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Elektroinstallation</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KE02</t>
+          <t>PD03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Entfernung zum Sicherungskasten</t>
+          <t>Gerüstart</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2443,7 +1770,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0–5 m | 6–10 m | 11–15 m | über 16 m</t>
+          <t>Fanggerüst | Vollgerüst | Sonstiges</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2455,27 +1782,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Elektroinstallation</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KE03</t>
+          <t>PD04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Freie Sicherungsplätze vorhanden?</t>
+          <t>Dachrinnenhöhe in m</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2487,17 +1809,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zugänglichkeit</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KZ01</t>
+          <t>PD05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Erreichbarkeit der Montageorte</t>
+          <t>Verschattung vorhanden?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2507,7 +1829,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>vom Boden/Leiter | Gerüst erforderlich | Hubsteiger erforderlich</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2519,67 +1841,677 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Einschätzung</t>
+          <t>DC-Dachmontage</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>PD06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Einschätzung des Kunden</t>
+          <t>Anzahl Optimierer (Verschattung und Module mit abweichender Neigung, z. B. Gaube)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>heiß | warm | kalt</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn PD05 = Ja</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
+          <t>Tigo-Optimierer je betroffenem Modul – bei Verschattung sowie bei Modulen mit abweichender Neigung (z. B. auf einer Gaube)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>DC-Dachmontage</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PD07</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Montage auf mehreren Dachseiten?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DC-Dachmontage</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PD08</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Leitungslänge DC-Kabelweg in m</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DC-Dachmontage</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PD09</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DC-kWp</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DC-Dachmontage</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PD10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Freitext groß</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PA01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Lage ZV</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>KG | EG | OG | DG | Sonstiges</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Neue ZV erforderlich?</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Anzahl Felder</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1-Feld | 2-Feld | 3-Feld | 4-Feld | Sonstige</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>nur wenn PA02 = Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ertüchtigung bestehender ZV?</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>nur wenn PA02 = Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Externes APZ-Feld erforderlich?</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>nur wenn PA04 = Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HAK-Leitung erneuern?</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>nur wenn PA04 = Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PA07</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Unterverteilung erforderlich?</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PA15</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Zählerzusammenlegung erforderlich?</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PA08</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tiefenerder vorhanden?</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PA09</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Leistung Wechselrichter in kW</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PA10</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Kapazität Batteriespeicher in kWh</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PA11</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Friondo HEMS gewünscht?</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PA12</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>iMSys inkl. Smart Meter gewünscht?</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PA13</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Friondo SpotDynamic gewünscht?</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PA14</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Freitext groß</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Einschätzung</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Einschätzung des Kunden</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>heiß | warm | kalt</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Einschätzung</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Wiedervorlage am</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>optional – leer lassen, wenn keine Wiedervorlage nötig</t>
         </is>
@@ -2596,23 +2528,688 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Seite</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Bedingung</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Platzierung</t>
+          <t>Fragetext</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Antwortmöglichkeiten</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Anzeigen wenn</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Hinweis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Objekt &amp; Anlage</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KO01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Gebäudeart</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>EFH | 2FH | REH | RMH | MFH | Gewerbe</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Objekt &amp; Anlage</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KO02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Baujahr Haus</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Objekt &amp; Anlage</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KO03</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Kunde ist Eigentümer?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ja | Nein, Zustimmung des Eigentümers liegt vor | Nein, Zustimmung noch nicht vorhanden</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Objekt &amp; Anlage</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KO04</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Anzahl Außengeräte</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1 | 2 | 3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Objekt &amp; Anlage</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KO05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Anzahl zu klimatisierender Räume</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>öffnet je Raum einen eigenen Fragenblock</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Räume</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>KR01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Raumbezeichnung</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Freitext</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>je Raum (KO05)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>z. B. Wohnzimmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Räume</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KR02</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Lage des Raums</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Keller/Souterrain | Erdgeschoss | 1. OG | 2. OG | 3. OG+ | Dachgeschoss</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>je Raum (KO05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Räume</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KR03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Hauptzweck</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>hauptsächlich kühlen | kühlen und in der Übergangszeit heizen | regelmäßig heizen und kühlen</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>je Raum (KO05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Räume</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>KR04</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Montageort Innengerät</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Außenwand | Innenwand | noch nicht bekannt</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>je Raum (KO05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Räume</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KR05</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Entfernung Innen- zu Außengerät</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>bis 3 m | 3–5 m | 6–10 m | 11–15 m | über 16 m</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>je Raum (KO05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Räume</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KR06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Kondensatpumpe erforderlich?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>je Raum (KO05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Räume</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KR07</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Zuordnung zum Außengerät</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1 | 2 | 3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>je Raum (KO05)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>es erscheinen nur so viele Optionen wie Außengeräte (KO04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Außengerät</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KA01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Montageort Außengerät</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>auf dem Boden | an der Außenwand | auf einer Terrasse | auf einem Balkon | auf einem Flachdach | auf einem Schrägdach | noch unklar</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Außengerät</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KA02</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Montagehöhe</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>unter 2 m | 2–4 m | über 5 m</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Elektroinstallation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KE01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Geeignete Stromversorgung nahe Außengerät?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ja | Nein | Unklar</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Elektroinstallation</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KE02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Entfernung zum Sicherungskasten</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0–5 m | 6–10 m | 11–15 m | über 16 m</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Elektroinstallation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>KE03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Freie Sicherungsplätze vorhanden?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Zugänglichkeit</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>KZ01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Erreichbarkeit der Montageorte</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vom Boden/Leiter | Gerüst erforderlich | Hubsteiger erforderlich</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Einschätzung</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Einschätzung des Kunden</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>heiß | warm | kalt</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Einschätzung</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Wiedervorlage am</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>optional – leer lassen, wenn keine Wiedervorlage nötig</t>
         </is>
       </c>
     </row>
@@ -2622,6 +3219,37 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Bedingung</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Platzierung</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8505,7 +9133,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9329,7 +9957,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9455,7 +10083,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9833,7 +10461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10306,7 +10934,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Baujahr der alten Heizung</t>
+          <t>Inbetriebnahmejahr (Baujahr) der bestehenden Heizung</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -10321,7 +10949,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Steuert Vorbelegung Klima-Bonus (K02).</t>
+          <t>Steuert Vorbelegung Klima-Bonus (K02) und die Boni-Kategorie im BzA-Datenblatt (v19).</t>
         </is>
       </c>
     </row>
@@ -10333,12 +10961,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aktueller Verbrauch (kWh)</t>
+          <t>Nennleistung der bestehenden Heizung in kW</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10346,11 +10974,7 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Verbrauch unbekannt</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>immer</t>
@@ -10358,7 +10982,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bei Öl rechnet der Vertriebler Liter in kWh um. Alternative „Verbrauch unbekannt“: Auslegung erfolgt über Fläche × Gebäudestandard (A17/A18).</t>
+          <t>Typenschild der alten Heizung; BzA-Datenblatt (v19). Unbekannt → 0 eingeben (Datenblatt zeigt „fehlt“).</t>
         </is>
       </c>
     </row>
@@ -10370,12 +10994,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Beheizte Wohnfläche in m²</t>
+          <t>Aktueller Verbrauch (kWh)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10383,14 +11007,19 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Verbrauch unbekannt</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>nur wenn A03 = Verbrauch unbekannt</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Flächen-Auslegung (v11): Heizlast = Fläche × Faktor ÷ 1000</t>
+          <t>Bei Öl rechnet der Vertriebler Liter in kWh um. Alternative „Verbrauch unbekannt“: Auslegung erfolgt über Fläche × Gebäudestandard (A17/A18).</t>
         </is>
       </c>
     </row>
@@ -10402,22 +11031,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Gebäudestandard</t>
+          <t>Beheizte Wohnfläche in m²</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>saniert – 40 W/m² | Altbau – 60 W/m² | Altbau unsaniert – 70 W/m²</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -10427,7 +11051,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Faktor der Flächen-Auslegung (v11)</t>
+          <t>Flächen-Auslegung (v11): Heizlast = Fläche × Faktor ÷ 1000</t>
         </is>
       </c>
     </row>
@@ -10439,12 +11063,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Heizlast bekannt?</t>
+          <t>Gebäudestandard</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10454,17 +11078,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>saniert – 40 W/m² | Altbau – 60 W/m² | Altbau unsaniert – 70 W/m²</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn A03 = Verbrauch unbekannt</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Entscheidet bei Bekanntsein über das Paket – A03 (kWh) bleibt Pflicht fürs Protokoll</t>
+          <t>Faktor der Flächen-Auslegung (v11)</t>
         </is>
       </c>
     </row>
@@ -10476,27 +11100,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Heizlast in kW</t>
+          <t>Heizlast bekannt?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>nur wenn A14 = Ja</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dezimalzahl, z. B. 8,4 – hat Vorrang vor der kWh-Zuordnung</t>
+          <t>Entscheidet bei Bekanntsein über das Paket – A03 (kWh) bleibt Pflicht fürs Protokoll</t>
         </is>
       </c>
     </row>
@@ -10508,27 +11137,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lage des Heizraums</t>
+          <t>Heizlast in kW</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>KG | EG | OG | DG | Sonstiges</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn A14 = Ja</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dezimalzahl, z. B. 8,4 – hat Vorrang vor der kWh-Zuordnung</t>
         </is>
       </c>
     </row>
@@ -10540,12 +11169,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Soll die Wärmepumpe auch ins DG?</t>
+          <t>Lage des Heizraums</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -10555,17 +11184,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>KG | EG | OG | DG | Sonstiges</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>nur wenn A04 = DG</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Dachzentralen-Block.</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
@@ -10577,12 +11201,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sind im Keller alle notwendigen Anschlüsse vorhanden?</t>
+          <t>Soll die Wärmepumpe auch ins DG?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -10597,7 +11221,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>nur wenn D01 = Nein</t>
+          <t>nur wenn A04 = DG</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dachzentralen-Block.</t>
         </is>
       </c>
     </row>
@@ -10609,12 +11238,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>D06</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>In welcher Etage liegen die Anschlüsse (Heizung/Warmwasser)?</t>
+          <t>Sind im Keller alle notwendigen Anschlüsse vorhanden?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -10624,17 +11253,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gleiche Etage (KG) | Andere Etage (z. B. EG)</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>nur wenn D02 = Nein</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>v11: Gleiche Etage → Pauschale 141; andere Etage → getrennte Meterabfragen D07/D08 (139/140)</t>
+          <t>nur wenn D01 = Nein</t>
         </is>
       </c>
     </row>
@@ -10646,12 +11270,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Können die Leitungen durch den Schacht verlegt werden und ist dieser frei?</t>
+          <t>In welcher Etage liegen die Anschlüsse (Heizung/Warmwasser)?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -10661,12 +11285,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Gleiche Etage (KG) | Andere Etage (z. B. EG)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>nur wenn D06 = Andere Etage (z. B. EG)</t>
+          <t>nur wenn D02 = Nein</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>v11: Gleiche Etage → Pauschale 141; andere Etage → getrennte Meterabfragen D07/D08 (139/140)</t>
         </is>
       </c>
     </row>
@@ -10678,27 +11307,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D07</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rohrleitung Heizung in m</t>
+          <t>Können die Leitungen durch den Schacht verlegt werden und ist dieser frei?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>nur wenn D04 = Ja</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Pos. 139 (Rohrleitungen Heizungsvorlauf/-rücklauf) × Meter</t>
+          <t>nur wenn D06 = Andere Etage (z. B. EG)</t>
         </is>
       </c>
     </row>
@@ -10710,12 +11339,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D07</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rohrleitung Warmwasser in m</t>
+          <t>Rohrleitung Heizung in m</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -10730,7 +11359,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pos. 140 (Rohrleitungen Warmwasser/Zirkulation) × Meter</t>
+          <t>Pos. 139 (Rohrleitungen Heizungsvorlauf/-rücklauf) × Meter</t>
         </is>
       </c>
     </row>
@@ -10742,12 +11371,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>D08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Länge der Erdleitung (m)</t>
+          <t>Rohrleitung Warmwasser in m</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -10757,12 +11386,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>nur wenn A04 = KG oder EG, oder (A04 = DG und D01 = Nein)</t>
+          <t>nur wenn D04 = Ja</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Berechnet wird Eingabe − 3 m (nie unter 0).</t>
+          <t>Pos. 140 (Rohrleitungen Warmwasser/Zirkulation) × Meter</t>
         </is>
       </c>
     </row>
@@ -10774,12 +11403,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Länge der Fassadenleitung (m)</t>
+          <t>Länge der Erdleitung (m)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -10789,12 +11418,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>nur wenn A04 = OG, oder (A04 = DG und D01 = Ja)</t>
+          <t>nur wenn A04 = KG oder EG, oder (A04 = DG und D01 = Nein)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Volle Meterzahl.</t>
+          <t>Berechnet wird Eingabe − 3 m (nie unter 0).</t>
         </is>
       </c>
     </row>
@@ -10806,12 +11435,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A13</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Leitungslänge zwischen Hauseinführung und WP-Inneneinheit (m)?</t>
+          <t>Länge der Fassadenleitung (m)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -10821,12 +11450,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn A04 = OG, oder (A04 = DG und D01 = Ja)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anschlussleitung Inneneinheit; berechnet wird Eingabe − 5 m (nie unter 0).</t>
+          <t>Volle Meterzahl.</t>
         </is>
       </c>
     </row>
@@ -10838,27 +11467,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Öl-Tankentsorgung erforderlich?</t>
+          <t>Leitungslänge zwischen Hauseinführung und WP-Inneneinheit (m)?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>nur wenn A01 = Öl</t>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Anschlussleitung Inneneinheit; berechnet wird Eingabe − 5 m (nie unter 0).</t>
         </is>
       </c>
     </row>
@@ -10870,12 +11499,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Art des Öltanks</t>
+          <t>Öl-Tankentsorgung erforderlich?</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -10885,12 +11514,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stahl | Kunststoff | Unterirdisch</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>nur wenn A07 = Ja</t>
+          <t>nur wenn A01 = Öl</t>
         </is>
       </c>
     </row>
@@ -10902,12 +11531,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A09</t>
+          <t>A08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wie groß ist der Tank?</t>
+          <t>Art des Öltanks</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -10917,12 +11546,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>bis 3.000 L | bis 4.000 L | bis 5.000 L | bis 6.000 L | bis 7.000 L | bis 8.000 L | bis 9.000 L | ab 9.000 L</t>
+          <t>Stahl | Kunststoff | Unterirdisch</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>nur wenn A08 = Stahl oder Kunststoff</t>
+          <t>nur wenn A07 = Ja</t>
         </is>
       </c>
     </row>
@@ -10934,27 +11563,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A19</t>
+          <t>A09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tatsächliche Tankgröße in Litern</t>
+          <t>Wie groß ist der Tank?</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>bis 3.000 L | bis 4.000 L | bis 5.000 L | bis 6.000 L | bis 7.000 L | bis 8.000 L | bis 9.000 L | ab 9.000 L</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>nur wenn A09 = ab 9.000 L</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>v11: fürs Protokoll und als Zusatz im Positionstext der Entsorgung</t>
+          <t>nur wenn A08 = Stahl oder Kunststoff</t>
         </is>
       </c>
     </row>
@@ -10966,27 +11595,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Stemmarbeiten für einen Durchgang benötigt?</t>
+          <t>Tatsächliche Tankgröße in Litern</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>nur wenn A08 = Stahl oder Kunststoff</t>
+          <t>nur wenn A09 = ab 9.000 L</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>v11: fürs Protokoll und als Zusatz im Positionstext der Entsorgung</t>
         </is>
       </c>
     </row>
@@ -10998,12 +11627,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Solarthermie vorhanden?</t>
+          <t>Stemmarbeiten für einen Durchgang benötigt?</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -11013,12 +11642,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ja, soll übernommen werden | Ja, soll stillgelegt werden | Nein</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn A08 = Stahl oder Kunststoff</t>
         </is>
       </c>
     </row>
@@ -11030,12 +11659,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PV-Anlage vorhanden?</t>
+          <t>Solarthermie vorhanden?</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -11045,17 +11674,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ja | Nein | Ist geplant</t>
+          <t>Ja, soll übernommen werden | Ja, soll stillgelegt werden | Nein</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>immer</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Info.</t>
         </is>
       </c>
     </row>
@@ -11067,49 +11691,54 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bemerkung zur alten Anlage</t>
+          <t>PV-Anlage vorhanden?</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Freitext groß</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ja | Nein | Ist geplant</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>immer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Info.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Neue Anlage</t>
+          <t>Alte Anlage</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>N01</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Art der Wärmepumpe</t>
+          <t>Bemerkung zur alten Anlage</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Luft/Wasser | Luft/Luft | Sole/Wasser | Split | Sonstiges</t>
+          <t>Freitext groß</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -11126,12 +11755,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>N02</t>
+          <t>N01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Warmwasser über die Wärmepumpe?</t>
+          <t>Art der Wärmepumpe</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -11141,17 +11770,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Luft/Wasser | Luft/Luft | Sole/Wasser | Split | Sonstiges</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>immer</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Steuert Paketvariante + Überschrift Block 1.</t>
         </is>
       </c>
     </row>
@@ -11163,12 +11787,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>N03</t>
+          <t>N02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Größe des Warmwasserspeichers</t>
+          <t>Warmwasser über die Wärmepumpe?</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -11178,17 +11802,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>bis 200 l | 300 l | mehr als 300 l</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>nur wenn N02 = Ja</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AWM-Pakete haben 180-l-Speicher integriert.</t>
+          <t>Steuert Paketvariante + Überschrift Block 1.</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11824,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>N08</t>
+          <t>N03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Farbe der Außeneinheit?</t>
+          <t>Größe des Warmwasserspeichers</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -11215,17 +11839,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Weiß | Schwarz</t>
+          <t>bis 200 l | 300 l | mehr als 300 l</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>nur wenn Klasse = 15 kW</t>
+          <t>nur wenn N02 = Ja</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Serie CS8800i: Pos. 030 (weiß) / Pos. 031 (schwarz)</t>
+          <t>AWM-Pakete haben 180-l-Speicher integriert.</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11861,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>N04</t>
+          <t>N08</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Aufstellort der Wärmepumpe</t>
+          <t>Farbe der Außeneinheit?</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -11252,12 +11876,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Boden | Garagendach | Sonstiges</t>
+          <t>Weiß | Schwarz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn Klasse = 15 kW</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Serie CS8800i: Pos. 030 (weiß) / Pos. 031 (schwarz)</t>
         </is>
       </c>
     </row>
@@ -11269,12 +11898,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>N05</t>
+          <t>N04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Durchführung durch Bitumen?</t>
+          <t>Aufstellort der Wärmepumpe</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -11284,12 +11913,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Boden | Garagendach | Sonstiges</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>nur wenn N04 = Garagendach</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
@@ -11301,12 +11930,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>N09</t>
+          <t>N05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mobiler Kran erforderlich?</t>
+          <t>Durchführung durch Bitumen?</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -11322,11 +11951,6 @@
       <c r="F45" t="inlineStr">
         <is>
           <t>nur wenn N04 = Garagendach</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>v11: ersetzt die automatische Kran-EP-Position</t>
         </is>
       </c>
     </row>
@@ -11338,27 +11962,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Länge der Fassadenleitung (m)</t>
+          <t>Mobiler Kran erforderlich?</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>nur wenn N04 = Garagendach und A04 = KG oder EG oder Sonstiges, oder (N04 = Garagendach und A04 = DG und D01 = Nein)</t>
+          <t>nur wenn N04 = Garagendach</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>v11: Fassadenleitung bei Dachaufstellung (Pos. 134 × Meter); bei OG/DG-bleibt läuft sie weiter über A06</t>
+          <t>v11: ersetzt die automatische Kran-EP-Position</t>
         </is>
       </c>
     </row>
@@ -11370,27 +11999,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>N06</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Größe des Pufferspeichers</t>
+          <t>Länge der Fassadenleitung (m)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>50 l | 100 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>nur wenn Klasse = 4 kW oder 6 kW oder 7 kW oder 10 kW oder 13 kW</t>
+          <t>nur wenn N04 = Garagendach und A04 = KG oder EG oder Sonstiges, oder (N04 = Garagendach und A04 = DG und D01 = Nein)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>v11: Fassadenleitung bei Dachaufstellung (Pos. 134 × Meter); bei OG/DG-bleibt läuft sie weiter über A06</t>
         </is>
       </c>
     </row>
@@ -11402,7 +12031,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>N07</t>
+          <t>N06</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -11417,34 +12046,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>70 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
+          <t>50 l | 100 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>nur wenn Klasse = 15 kW</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Serie CS8800i: 70 l = AWMB (integriert), sonst AWE + externer Puffer</t>
+          <t>nur wenn Klasse = 4 kW oder 6 kW oder 7 kW oder 10 kW oder 13 kW</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Heizverteilung</t>
+          <t>Neue Anlage</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>N07</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wie viele Heizkreise?</t>
+          <t>Größe des Pufferspeichers</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -11454,34 +12078,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1 | 2 | 3 | mehr als 3</t>
+          <t>70 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn Klasse = 15 kW</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ein Heizkreis ist im WP-Paket enthalten.</t>
+          <t>Serie CS8800i: 70 l = AWMB (integriert), sonst AWE + externer Puffer</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Heizverteilung</t>
+          <t>Neue Anlage</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>N11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wärmemengenzähler erforderlich?</t>
+          <t>Contracting-Modell?</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -11496,12 +12120,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>nur wenn O01 = 2FH oder MFH</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>bei mehr als einer Wohneinheit</t>
+          <t>Vorbelegung Nein; BzA-Datenblatt „Contracting“ (v19).</t>
         </is>
       </c>
     </row>
@@ -11513,22 +12137,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H09</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Anzahl Wärmemengenzähler</t>
+          <t>Wie viele Heizkreise?</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1 | 2 | 3 | mehr als 3</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>nur wenn H08 = Ja</t>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ein Heizkreis ist im WP-Paket enthalten.</t>
         </is>
       </c>
     </row>
@@ -11540,12 +12174,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Verteilsystem</t>
+          <t>Wärmemengenzähler erforderlich?</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -11555,12 +12189,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Heizkörper | Fußbodenheizung | Heizkörper und Fußbodenheizung | Sonstiges</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn O01 = 2FH oder MFH</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>bei mehr als einer Wohneinheit</t>
         </is>
       </c>
     </row>
@@ -11572,27 +12211,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Heizkörpertausch erforderlich?</t>
+          <t>Anzahl Wärmemengenzähler</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>nur wenn H02 = Heizkörper oder beides</t>
+          <t>nur wenn H08 = Ja</t>
         </is>
       </c>
     </row>
@@ -11604,32 +12238,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H04</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Anzahl Heizkörper je Größe (S/M/L/XL)</t>
+          <t>Verteilsystem</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mengenmaske</t>
+          <t>Auswahl</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>S | M | L | XL</t>
+          <t>Heizkörper | Fußbodenheizung | Heizkörper und Fußbodenheizung | Sonstiges</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>nur wenn H03 = Ja</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Leer/0 = entfällt.</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
@@ -11641,12 +12270,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H05</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FBH-Heizkreisverteiler einregulierbar?</t>
+          <t>Heizkörpertausch erforderlich?</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11661,7 +12290,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>nur wenn H02 = Fußbodenheizung oder beides</t>
+          <t>nur wenn H02 = Heizkörper oder beides</t>
         </is>
       </c>
     </row>
@@ -11673,22 +12302,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H06</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Anzahl Heizkreisverteiler</t>
+          <t>Anzahl Heizkörper je Größe (S/M/L/XL)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Mengenmaske</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>S | M | L | XL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>nur wenn H05 = Nein</t>
+          <t>nur wenn H03 = Ja</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Leer/0 = entfällt.</t>
         </is>
       </c>
     </row>
@@ -11700,96 +12339,86 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>H07</t>
+          <t>H05</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gruppen je Heizkreisverteiler {n}</t>
+          <t>FBH-Heizkreisverteiler einregulierbar?</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wiederholfeld</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>nur wenn H05 = Nein</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Ein Feld pro Verteiler aus H06.</t>
+          <t>nur wenn H02 = Fußbodenheizung oder beides</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Elektro/ZV</t>
+          <t>Heizverteilung</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>H06</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lage der Zählerverteilung</t>
+          <t>Anzahl Heizkreisverteiler</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>KG | EG | OG | DG | Sonstiges</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Info (außer Sonstiges).</t>
+          <t>nur wenn H05 = Nein</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Elektro/ZV</t>
+          <t>Heizverteilung</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>H07</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Muss die Zählerverteilung erneuert werden?</t>
+          <t>Gruppen je Heizkreisverteiler {n}</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Wiederholfeld</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn H05 = Nein</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ein Feld pro Verteiler aus H06.</t>
         </is>
       </c>
     </row>
@@ -11801,12 +12430,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wie viele Felder?</t>
+          <t>Lage der Zählerverteilung</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -11816,12 +12445,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2-Feld | 3-Feld | 4-Feld und mehr</t>
+          <t>KG | EG | OG | DG | Sonstiges</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>nur wenn E02 = Ja</t>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Info (außer Sonstiges).</t>
         </is>
       </c>
     </row>
@@ -11833,12 +12467,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Unterverteilung erforderlich?</t>
+          <t>Muss die Zählerverteilung erneuert werden?</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -11853,7 +12487,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>nur wenn E02 = Nein</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
@@ -11865,12 +12499,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MID-Zwischenzähler erforderlich?</t>
+          <t>Wie viele Felder?</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -11880,29 +12514,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>2-Feld | 3-Feld | 4-Feld und mehr</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>nur wenn E04 = Ja</t>
+          <t>nur wenn E02 = Ja</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Friondo</t>
+          <t>Elektro/ZV</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Friondo HEMS gewünscht?</t>
+          <t>Unterverteilung erforderlich?</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -11917,24 +12551,24 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn E02 = Nein</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Friondo</t>
+          <t>Elektro/ZV</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>iMSys inkl. Smart Meter gewünscht?</t>
+          <t>MID-Zwischenzähler erforderlich?</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -11949,12 +12583,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Löst Vollmacht-Seite aus.</t>
+          <t>nur wenn E04 = Ja</t>
         </is>
       </c>
     </row>
@@ -11966,12 +12595,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Friondo SpotDynamic gewünscht?</t>
+          <t>Friondo HEMS gewünscht?</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -11987,28 +12616,23 @@
       <c r="F65" t="inlineStr">
         <is>
           <t>immer</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Löst Vollmacht-Seite aus.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Förderung</t>
+          <t>Friondo</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>K01</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bewohnt der Eigentümer eine Wohneinheit selbst?</t>
+          <t>iMSys inkl. Smart Meter gewünscht?</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -12023,29 +12647,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>nur wenn O01 = 2FH oder MFH</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>EFH/REH/RMH: automatisch Ja. Gewerbe: automatisch Nein.</t>
+          <t>Löst Vollmacht-Seite aus.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Förderung</t>
+          <t>Friondo</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>K02</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Welche Heizung wird ersetzt? (Klima-Bonus)</t>
+          <t>Friondo SpotDynamic gewünscht?</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -12055,17 +12679,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Öl-, Kohle-, Gasetagen- oder Nachtspeicherheizung, funktionstüchtig | Gas- oder Biomasseheizung, mind. 20 Jahre, funktionstüchtig | Andere / jüngere Heizung / Neubau</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>nur bei Selbstnutzung</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Vorbelegt aus A01 + A02, änderbar.</t>
+          <t>Löst Vollmacht-Seite aus.</t>
         </is>
       </c>
     </row>
@@ -12077,27 +12701,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>K03</t>
+          <t>K01</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Zu versteuerndes Haushaltsjahreseinkommen (€)</t>
+          <t>Bewohnt der Eigentümer eine Wohneinheit selbst?</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Betragseingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>nur bei Selbstnutzung</t>
+          <t>nur wenn O01 = 2FH oder MFH</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leer oder über 50.000 € = kein Bonus.</t>
+          <t>EFH/REH/RMH: automatisch Ja. Gewerbe: automatisch Nein.</t>
         </is>
       </c>
     </row>
@@ -12109,12 +12738,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>K04</t>
+          <t>K02</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minderjähriges Kind im Haushalt?</t>
+          <t>Welche Heizung wird ersetzt? (Klima-Bonus)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -12124,84 +12753,153 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Öl-, Kohle-, Gasetagen- oder Nachtspeicherheizung, funktionstüchtig | Gas- oder Biomasseheizung, mind. 20 Jahre, funktionstüchtig | Andere / jüngere Heizung / Neubau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>nur wenn K03 ausgefüllt</t>
+          <t>nur bei Selbstnutzung</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>10.000 € Abzug vom Einkommen.</t>
+          <t>Vorbelegt aus A01 + A02, änderbar.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Einschätzung</t>
+          <t>Förderung</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>K03</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Einschätzung des Kunden</t>
+          <t>Zu versteuerndes Haushaltsjahreseinkommen (€)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>heiß | warm | kalt</t>
+          <t>Betragseingabe</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur bei Selbstnutzung</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
+          <t>Leer oder über 50.000 € = kein Bonus.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>Förderung</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>K04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Minderjähriges Kind im Haushalt?</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>nur wenn K03 ausgefüllt</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>10.000 € Abzug vom Einkommen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>Einschätzung</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Einschätzung des Kunden</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>heiß | warm | kalt</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Einschätzung</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Wiedervorlage am</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>optional – leer lassen, wenn keine Wiedervorlage nötig</t>
         </is>

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -727,7 +727,6 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -768,7 +767,6 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -809,7 +807,6 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -850,7 +847,6 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -891,7 +887,6 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -932,7 +927,6 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -973,7 +967,6 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1014,7 +1007,6 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1055,7 +1047,6 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1096,7 +1087,6 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1139,7 +1129,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PRÜFPUNKT: Zusatz „(B)“ – gilt vorerst für weiße (030) und schwarze (031) Außeneinheit; eigene Nummer der weißen klären</t>
+          <t>gilt für weiße (Pos. 030) und schwarze (Pos. 031) Außeneinheit – keine eigene Nummer (bestätigt 30.09.2026)</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1174,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PRÜFPUNKT: Zusatz „(B)“ – gilt vorerst für weiße (030) und schwarze (031) Außeneinheit; eigene Nummer der weißen klären</t>
+          <t>gilt für weiße (Pos. 030) und schwarze (Pos. 031) Außeneinheit – keine eigene Nummer (bestätigt 30.09.2026)</t>
         </is>
       </c>
     </row>
@@ -1212,9 +1202,6 @@
       <c r="E14" t="n">
         <v>21</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Vorrat – geplante Klassenerweiterung (Komponenten/Preise offen)</t>
@@ -10974,7 +10961,6 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>immer</t>

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -9554,12 +9554,12 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>AMPEL: individuell – Grund: Ertüchtigung bestehender ZV – Positionen noch nicht hinterlegt</t>
+          <t>–</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>[OFFEN] Positionen für Ertüchtigung/APZ/HAK-Leitung (PA05/PA06) noch festzulegen</t>
+          <t>v22 (30.09.2026): Ja löst keine Positionen und keine Ampel aus – Antwort nur im Protokoll</t>
         </is>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -10076,7 +10076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>[ANNAHME] Unternehmenspräsentation – Basisquote PV</t>
+          <t>[ANNAHME] Unternehmenspräsentation – Basisquote PV – überholt durch Energiebilanz (v22), ungenutzt</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>[ANNAHME] additiv, wenn ein Speicher im Angebot ist</t>
+          <t>[ANNAHME] additiv, wenn ein Speicher im Angebot ist – überholt durch Energiebilanz (v22), ungenutzt</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>[ANNAHME] additiv, wenn Friondo HEMS (Pos. 015) im Angebot ist</t>
+          <t>[ANNAHME] additiv, wenn Friondo HEMS (Pos. 015) im Angebot ist – überholt durch Energiebilanz (v22), ungenutzt</t>
         </is>
       </c>
     </row>
@@ -10434,6 +10434,498 @@
       <c r="D18" s="8" t="inlineStr">
         <is>
           <t>aus dem Musterangebot – wird an die Modulposition angehängt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Strompreissteigerung</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>%/Jahr</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>v22 Wirtschaftlichkeit: Annahme Strompreisentwicklung</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Degradation</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>%/Jahr</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>v22: Leistungsabnahme der Module je Jahr</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Betriebskosten</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>€/Jahr</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>v22: Versicherung, Wartung, Zählergebühr (pauschal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Betrachtungszeitraum</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Jahre</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>v22: Laufzeit der Betrachtung</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Inbetriebnahme-Versatz</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Jahr</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>v22: Startjahr = Angebotsjahr + Versatz</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Direktanteil Haushalt</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>v22: Anteil des Haushaltsstroms, der direkt aus PV gedeckt wird</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Direktanteil Wärmepumpe</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>v22: Anteil des WP-Stroms direkt aus PV (ohne HEMS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Direktanteil Wallbox</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>v22 [ANNAHME]: Anteil des Wallbox-Stroms direkt aus PV</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>HEMS-Zuschlag Haushalt</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>%-Punkte</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>v22: Zuschlag auf den Direktanteil mit Friondo HEMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>HEMS-Zuschlag Wärmepumpe</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>%-Punkte</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>v22: Zuschlag auf den Direktanteil mit Friondo HEMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>HEMS-Zuschlag Wallbox</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>%-Punkte</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>v22 [ANNAHME]: Zuschlag auf den Direktanteil mit Friondo HEMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Speicher Vollzyklen</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>/Jahr</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>v22: nutzbare Vollzyklen des Speichers je Jahr</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Speicher Wirkungsgrad</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>v22: Round-trip-Wirkungsgrad des Speichers</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>SpotDynamic Bezugspreis</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>€/kWh</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>v22: Ø Netzbezugspreis mit Friondo SpotDynamic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Kosten-Airbag</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>€/kWh</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>v22: Obergrenze SpotDynamic (nur Text auf Seite 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Szenarien Strompreissteigerung</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>1; 3; 5</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>%/Jahr</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>v22: drei Säulen auf Seite 3 (vorsichtig · Ihre Rechnung · stark)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>CO₂-Faktor Netzstrom</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>380</v>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>g/kWh</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>v22: Umweltbundesamt, deutscher Strommix</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>CO₂ Auto</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>g/km</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>v22: Umrechnung in Autokilometer</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>CO₂ Baum</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>kg/Jahr</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>v22: CO₂-Bindung je Baum und Jahr</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Montagedauer-Text</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Montage in 1–2 Tagen</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>v22: Schritt 3 unter „So geht es weiter“ (Seite 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Monatsprofil PV</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>2,5; 4,5; 10; 11; 12,5; 13; 13; 11,5; 9,5; 7; 3,5; 2</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>% je Monat</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>v22 Saisonmodell: Anteil des Jahresertrags je Monat Jan–Dez (typische Verteilung Deutschland: Nov–Feb ≈ 12 %, Apr–Sep ≈ 70 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Monatsprofil Haushalt</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>9,5; 8,5; 8,8; 8; 7,7; 7,3; 7,5; 7,5; 7,7; 8,4; 9; 10,1</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>% je Monat</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>v22 Saisonmodell [ANNAHME]: Haushaltsstrom je Monat, angelehnt an BDEW-Lastprofil H0 (Winter höher, Sommer niedriger)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Monatsprofil Wärmepumpe</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>15,3; 13,7; 12,1; 8,1; 4,9; 2,7; 2,7; 2,7; 4,1; 8,1; 11,3; 14,5</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>% je Monat</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>v22 Saisonmodell: 80 % Heizung nach VDI-2067-Gradtagszahlen + 20 % Warmwasser gleichverteilt</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Monatsprofil Wallbox</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>8,33; 8,33; 8,33; 8,33; 8,33; 8,33; 8,33; 8,33; 8,33; 8,33; 8,33; 8,33</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>% je Monat</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>v22 Saisonmodell [ANNAHME]: Wallbox gleichverteilt</t>
         </is>
       </c>
     </row>

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -27408,7 +27408,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>(Bosch Climate Broschüre – Zulieferung)</t>
+          <t>Bosch Climate 3200i.pdf</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -27418,7 +27418,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>v24: Datei nach Lieferung in anlagen/ legen und diese Zeile auf den Dateinamen setzen</t>
+          <t>Gerätebroschüre Bosch Climate 3200i (v27)</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -13785,7 +13785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14285,12 +14285,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A20</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nennleistung der bestehenden Heizung in kW</t>
+          <t>Aktueller Verbrauch (kWh)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -14298,6 +14298,11 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Verbrauch unbekannt</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>immer</t>
@@ -14305,7 +14310,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Typenschild der alten Heizung; BzA-Datenblatt (v19). Unbekannt → 0 eingeben (Datenblatt zeigt „fehlt“).</t>
+          <t>Bei Öl rechnet der Vertriebler Liter in kWh um. Alternative „Verbrauch unbekannt“: Auslegung erfolgt über Fläche × Gebäudestandard (A17/A18).</t>
         </is>
       </c>
     </row>
@@ -14317,12 +14322,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Aktueller Verbrauch (kWh)</t>
+          <t>Beheizte Wohnfläche in m²</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -14330,19 +14335,14 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Verbrauch unbekannt</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn A03 = Verbrauch unbekannt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bei Öl rechnet der Vertriebler Liter in kWh um. Alternative „Verbrauch unbekannt“: Auslegung erfolgt über Fläche × Gebäudestandard (A17/A18).</t>
+          <t>Flächen-Auslegung (v11): Heizlast = Fläche × Faktor ÷ 1000</t>
         </is>
       </c>
     </row>
@@ -14354,17 +14354,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Beheizte Wohnfläche in m²</t>
+          <t>Gebäudestandard</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>saniert – 40 W/m² | Altbau – 60 W/m² | Altbau unsaniert – 70 W/m²</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -14374,7 +14379,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Flächen-Auslegung (v11): Heizlast = Fläche × Faktor ÷ 1000</t>
+          <t>Faktor der Flächen-Auslegung (v11)</t>
         </is>
       </c>
     </row>
@@ -14386,12 +14391,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gebäudestandard</t>
+          <t>Heizlast bekannt?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -14401,17 +14406,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>saniert – 40 W/m² | Altbau – 60 W/m² | Altbau unsaniert – 70 W/m²</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>nur wenn A03 = Verbrauch unbekannt</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Faktor der Flächen-Auslegung (v11)</t>
+          <t>Entscheidet bei Bekanntsein über das Paket – A03 (kWh) bleibt Pflicht fürs Protokoll</t>
         </is>
       </c>
     </row>
@@ -14423,32 +14428,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Heizlast bekannt?</t>
+          <t>Heizlast in kW</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn A14 = Ja</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Entscheidet bei Bekanntsein über das Paket – A03 (kWh) bleibt Pflicht fürs Protokoll</t>
+          <t>Dezimalzahl, z. B. 8,4 – hat Vorrang vor der kWh-Zuordnung</t>
         </is>
       </c>
     </row>
@@ -14460,27 +14460,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Heizlast in kW</t>
+          <t>Lage des Heizraums</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>KG | EG | OG | DG | Sonstiges</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>nur wenn A14 = Ja</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dezimalzahl, z. B. 8,4 – hat Vorrang vor der kWh-Zuordnung</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
@@ -14492,12 +14492,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lage des Heizraums</t>
+          <t>Soll die Wärmepumpe auch ins DG?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -14507,12 +14507,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KG | EG | OG | DG | Sonstiges</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn A04 = DG</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dachzentralen-Block.</t>
         </is>
       </c>
     </row>
@@ -14524,12 +14529,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Soll die Wärmepumpe auch ins DG?</t>
+          <t>Sind im Keller alle notwendigen Anschlüsse vorhanden?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -14544,12 +14549,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>nur wenn A04 = DG</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Dachzentralen-Block.</t>
+          <t>nur wenn D01 = Nein</t>
         </is>
       </c>
     </row>
@@ -14561,12 +14561,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sind im Keller alle notwendigen Anschlüsse vorhanden?</t>
+          <t>In welcher Etage liegen die Anschlüsse (Heizung/Warmwasser)?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -14576,12 +14576,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Gleiche Etage (KG) | Andere Etage (z. B. EG)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>nur wenn D01 = Nein</t>
+          <t>nur wenn D02 = Nein</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>v11: Gleiche Etage → Pauschale 141; andere Etage → getrennte Meterabfragen D07/D08 (139/140)</t>
         </is>
       </c>
     </row>
@@ -14593,12 +14598,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D06</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>In welcher Etage liegen die Anschlüsse (Heizung/Warmwasser)?</t>
+          <t>Können die Leitungen durch den Schacht verlegt werden und ist dieser frei?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -14608,17 +14613,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gleiche Etage (KG) | Andere Etage (z. B. EG)</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>nur wenn D02 = Nein</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>v11: Gleiche Etage → Pauschale 141; andere Etage → getrennte Meterabfragen D07/D08 (139/140)</t>
+          <t>nur wenn D06 = Andere Etage (z. B. EG)</t>
         </is>
       </c>
     </row>
@@ -14630,27 +14630,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Können die Leitungen durch den Schacht verlegt werden und ist dieser frei?</t>
+          <t>Rohrleitung Heizung in m</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>nur wenn D06 = Andere Etage (z. B. EG)</t>
+          <t>nur wenn D04 = Ja</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pos. 139 (Rohrleitungen Heizungsvorlauf/-rücklauf) × Meter</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>D07</t>
+          <t>D08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rohrleitung Heizung in m</t>
+          <t>Rohrleitung Warmwasser in m</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -14682,7 +14682,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pos. 139 (Rohrleitungen Heizungsvorlauf/-rücklauf) × Meter</t>
+          <t>Pos. 140 (Rohrleitungen Warmwasser/Zirkulation) × Meter</t>
         </is>
       </c>
     </row>
@@ -14694,12 +14694,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rohrleitung Warmwasser in m</t>
+          <t>Länge der Erdleitung (m)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -14709,12 +14709,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>nur wenn D04 = Ja</t>
+          <t>nur wenn A04 = KG oder EG, oder (A04 = DG und D01 = Nein)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pos. 140 (Rohrleitungen Warmwasser/Zirkulation) × Meter</t>
+          <t>Berechnet wird Eingabe − 3 m (nie unter 0).</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Länge der Erdleitung (m)</t>
+          <t>Länge der Fassadenleitung (m)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>nur wenn A04 = KG oder EG, oder (A04 = DG und D01 = Nein)</t>
+          <t>nur wenn A04 = OG, oder (A04 = DG und D01 = Ja)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Berechnet wird Eingabe − 3 m (nie unter 0).</t>
+          <t>Volle Meterzahl.</t>
         </is>
       </c>
     </row>
@@ -14758,12 +14758,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Länge der Fassadenleitung (m)</t>
+          <t>Leitungslänge zwischen Hauseinführung und WP-Inneneinheit (m)?</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -14773,12 +14773,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>nur wenn A04 = OG, oder (A04 = DG und D01 = Ja)</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Volle Meterzahl.</t>
+          <t>Anschlussleitung Inneneinheit; berechnet wird Eingabe − 5 m (nie unter 0).</t>
         </is>
       </c>
     </row>
@@ -14790,27 +14790,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A13</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Leitungslänge zwischen Hauseinführung und WP-Inneneinheit (m)?</t>
+          <t>Öl-Tankentsorgung erforderlich?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Anschlussleitung Inneneinheit; berechnet wird Eingabe − 5 m (nie unter 0).</t>
+          <t>nur wenn A01 = Öl</t>
         </is>
       </c>
     </row>
@@ -14822,12 +14822,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Öl-Tankentsorgung erforderlich?</t>
+          <t>Art des Öltanks</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -14837,12 +14837,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Stahl | Kunststoff | Unterirdisch</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>nur wenn A01 = Öl</t>
+          <t>nur wenn A07 = Ja</t>
         </is>
       </c>
     </row>
@@ -14854,12 +14854,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>A09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Art des Öltanks</t>
+          <t>Wie groß ist der Tank?</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -14869,12 +14869,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stahl | Kunststoff | Unterirdisch</t>
+          <t>bis 3.000 L | bis 4.000 L | bis 5.000 L | bis 6.000 L | bis 7.000 L | bis 8.000 L | bis 9.000 L | ab 9.000 L</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>nur wenn A07 = Ja</t>
+          <t>nur wenn A08 = Stahl oder Kunststoff</t>
         </is>
       </c>
     </row>
@@ -14886,27 +14886,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A09</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wie groß ist der Tank?</t>
+          <t>Tatsächliche Tankgröße in Litern</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>bis 3.000 L | bis 4.000 L | bis 5.000 L | bis 6.000 L | bis 7.000 L | bis 8.000 L | bis 9.000 L | ab 9.000 L</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>nur wenn A08 = Stahl oder Kunststoff</t>
+          <t>nur wenn A09 = ab 9.000 L</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>v11: fürs Protokoll und als Zusatz im Positionstext der Entsorgung</t>
         </is>
       </c>
     </row>
@@ -14918,27 +14918,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A19</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tatsächliche Tankgröße in Litern</t>
+          <t>Stemmarbeiten für einen Durchgang benötigt?</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>nur wenn A09 = ab 9.000 L</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>v11: fürs Protokoll und als Zusatz im Positionstext der Entsorgung</t>
+          <t>nur wenn A08 = Stahl oder Kunststoff</t>
         </is>
       </c>
     </row>
@@ -14950,12 +14950,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Stemmarbeiten für einen Durchgang benötigt?</t>
+          <t>Solarthermie vorhanden?</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -14965,12 +14965,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Ja, soll übernommen werden | Ja, soll stillgelegt werden | Nein</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>nur wenn A08 = Stahl oder Kunststoff</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
@@ -14982,12 +14982,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Solarthermie vorhanden?</t>
+          <t>PV-Anlage vorhanden?</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -14997,12 +14997,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ja, soll übernommen werden | Ja, soll stillgelegt werden | Nein</t>
+          <t>Ja | Nein | Ist geplant</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>immer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Info.</t>
         </is>
       </c>
     </row>
@@ -15014,54 +15019,49 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PV-Anlage vorhanden?</t>
+          <t>Bemerkung zur alten Anlage</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Ja | Nein | Ist geplant</t>
+          <t>Freitext groß</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>immer</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Info.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alte Anlage</t>
+          <t>Neue Anlage</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>N01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bemerkung zur alten Anlage</t>
+          <t>Art der Wärmepumpe</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Freitext groß</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Luft/Wasser | Luft/Luft | Sole/Wasser | Split | Sonstiges</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -15078,12 +15078,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>N01</t>
+          <t>N02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Art der Wärmepumpe</t>
+          <t>Warmwasser über die Wärmepumpe?</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -15093,12 +15093,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Luft/Wasser | Luft/Luft | Sole/Wasser | Split | Sonstiges</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>immer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Steuert Paketvariante + Überschrift Block 1.</t>
         </is>
       </c>
     </row>
@@ -15110,12 +15115,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>N02</t>
+          <t>N03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Warmwasser über die Wärmepumpe?</t>
+          <t>Größe des Warmwasserspeichers</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -15125,17 +15130,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>bis 200 l | 300 l | mehr als 300 l</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn N02 = Ja</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Steuert Paketvariante + Überschrift Block 1.</t>
+          <t>AWM-Pakete haben 180-l-Speicher integriert.</t>
         </is>
       </c>
     </row>
@@ -15147,12 +15152,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>N03</t>
+          <t>N08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Größe des Warmwasserspeichers</t>
+          <t>Farbe der Außeneinheit?</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -15162,17 +15167,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>bis 200 l | 300 l | mehr als 300 l</t>
+          <t>Weiß | Schwarz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>nur wenn N02 = Ja</t>
+          <t>nur wenn Klasse = 15 kW</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>AWM-Pakete haben 180-l-Speicher integriert.</t>
+          <t>Serie CS8800i: Pos. 030 (weiß) / Pos. 031 (schwarz)</t>
         </is>
       </c>
     </row>
@@ -15184,12 +15189,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>N08</t>
+          <t>N04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Farbe der Außeneinheit?</t>
+          <t>Aufstellort der Wärmepumpe</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -15199,17 +15204,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Weiß | Schwarz</t>
+          <t>Boden | Garagendach | Sonstiges</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>nur wenn Klasse = 15 kW</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Serie CS8800i: Pos. 030 (weiß) / Pos. 031 (schwarz)</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
@@ -15221,12 +15221,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>N04</t>
+          <t>N05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Aufstellort der Wärmepumpe</t>
+          <t>Durchführung durch Bitumen?</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -15236,12 +15236,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Boden | Garagendach | Sonstiges</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn N04 = Garagendach</t>
         </is>
       </c>
     </row>
@@ -15253,12 +15253,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>N05</t>
+          <t>N09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Durchführung durch Bitumen?</t>
+          <t>Mobiler Kran erforderlich?</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -15274,6 +15274,11 @@
       <c r="F45" t="inlineStr">
         <is>
           <t>nur wenn N04 = Garagendach</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>v11: ersetzt die automatische Kran-EP-Position</t>
         </is>
       </c>
     </row>
@@ -15285,32 +15290,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>N09</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mobiler Kran erforderlich?</t>
+          <t>Länge der Fassadenleitung (m)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>nur wenn N04 = Garagendach</t>
+          <t>nur wenn N04 = Garagendach und A04 = KG oder EG oder Sonstiges, oder (N04 = Garagendach und A04 = DG und D01 = Nein)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>v11: ersetzt die automatische Kran-EP-Position</t>
+          <t>v11: Fassadenleitung bei Dachaufstellung (Pos. 134 × Meter); bei OG/DG-bleibt läuft sie weiter über A06</t>
         </is>
       </c>
     </row>
@@ -15322,27 +15322,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Länge der Fassadenleitung (m)</t>
+          <t>Größe des Pufferspeichers</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>50 l | 100 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>nur wenn N04 = Garagendach und A04 = KG oder EG oder Sonstiges, oder (N04 = Garagendach und A04 = DG und D01 = Nein)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>v11: Fassadenleitung bei Dachaufstellung (Pos. 134 × Meter); bei OG/DG-bleibt läuft sie weiter über A06</t>
+          <t>nur wenn Klasse = 4 kW oder 6 kW oder 7 kW oder 10 kW oder 13 kW</t>
         </is>
       </c>
     </row>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>N06</t>
+          <t>N07</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -15369,12 +15369,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>50 l | 100 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
+          <t>70 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>nur wenn Klasse = 4 kW oder 6 kW oder 7 kW oder 10 kW oder 13 kW</t>
+          <t>nur wenn Klasse = 15 kW</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Serie CS8800i: 70 l = AWMB (integriert), sonst AWE + externer Puffer</t>
         </is>
       </c>
     </row>
@@ -15386,12 +15391,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>N07</t>
+          <t>N11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Größe des Pufferspeichers</t>
+          <t>Contracting-Modell?</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -15401,34 +15406,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>70 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>nur wenn Klasse = 15 kW</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Serie CS8800i: 70 l = AWMB (integriert), sonst AWE + externer Puffer</t>
+          <t>Vorbelegung Nein; BzA-Datenblatt „Contracting“ (v19).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Neue Anlage</t>
+          <t>Heizverteilung</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>N11</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Contracting-Modell?</t>
+          <t>Wie viele Heizkreise?</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -15438,7 +15443,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>1 | 2 | 3 | mehr als 3</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -15448,7 +15453,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Vorbelegung Nein; BzA-Datenblatt „Contracting“ (v19).</t>
+          <t>Ein Heizkreis ist im WP-Paket enthalten.</t>
         </is>
       </c>
     </row>
@@ -15460,12 +15465,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wie viele Heizkreise?</t>
+          <t>Wärmemengenzähler erforderlich?</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -15475,17 +15480,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1 | 2 | 3 | mehr als 3</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn O01 = 2FH oder MFH</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ein Heizkreis ist im WP-Paket enthalten.</t>
+          <t>bei mehr als einer Wohneinheit</t>
         </is>
       </c>
     </row>
@@ -15497,32 +15502,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>H09</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wärmemengenzähler erforderlich?</t>
+          <t>Anzahl Wärmemengenzähler</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>nur wenn O01 = 2FH oder MFH</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>bei mehr als einer Wohneinheit</t>
+          <t>nur wenn H08 = Ja</t>
         </is>
       </c>
     </row>
@@ -15534,22 +15529,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>H09</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Anzahl Wärmemengenzähler</t>
+          <t>Verteilsystem</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Heizkörper | Fußbodenheizung | Heizkörper und Fußbodenheizung | Sonstiges</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>nur wenn H08 = Ja</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
@@ -15561,12 +15561,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Verteilsystem</t>
+          <t>Heizkörpertausch erforderlich?</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Heizkörper | Fußbodenheizung | Heizkörper und Fußbodenheizung | Sonstiges</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn H02 = Heizkörper oder beides</t>
         </is>
       </c>
     </row>
@@ -15593,27 +15593,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Heizkörpertausch erforderlich?</t>
+          <t>Anzahl Heizkörper je Größe (S/M/L/XL)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Auswahl</t>
+          <t>Mengenmaske</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>S | M | L | XL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>nur wenn H02 = Heizkörper oder beides</t>
+          <t>nur wenn H03 = Ja</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Leer/0 = entfällt.</t>
         </is>
       </c>
     </row>
@@ -15625,32 +15630,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H04</t>
+          <t>H05</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Anzahl Heizkörper je Größe (S/M/L/XL)</t>
+          <t>FBH-Heizkreisverteiler einregulierbar?</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mengenmaske</t>
+          <t>Auswahl</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>S | M | L | XL</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>nur wenn H03 = Ja</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Leer/0 = entfällt.</t>
+          <t>nur wenn H02 = Fußbodenheizung oder beides</t>
         </is>
       </c>
     </row>
@@ -15662,27 +15662,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>H05</t>
+          <t>H06</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FBH-Heizkreisverteiler einregulierbar?</t>
+          <t>Anzahl Heizkreisverteiler</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
+          <t>Zahleneingabe</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>nur wenn H02 = Fußbodenheizung oder beides</t>
+          <t>nur wenn H05 = Nein</t>
         </is>
       </c>
     </row>
@@ -15694,54 +15689,64 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>H06</t>
+          <t>H07</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Anzahl Heizkreisverteiler</t>
+          <t>Gruppen je Heizkreisverteiler {n}</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
+          <t>Wiederholfeld</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>nur wenn H05 = Nein</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ein Feld pro Verteiler aus H06.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Heizverteilung</t>
+          <t>Elektro/ZV</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>H07</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Gruppen je Heizkreisverteiler {n}</t>
+          <t>Lage der Zählerverteilung</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Wiederholfeld</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>KG | EG | OG | DG | Sonstiges</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>nur wenn H05 = Nein</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ein Feld pro Verteiler aus H06.</t>
+          <t>Info (außer Sonstiges).</t>
         </is>
       </c>
     </row>
@@ -15753,12 +15758,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lage der Zählerverteilung</t>
+          <t>Muss die Zählerverteilung erneuert werden?</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -15768,17 +15773,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KG | EG | OG | DG | Sonstiges</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>immer</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Info (außer Sonstiges).</t>
         </is>
       </c>
     </row>
@@ -15790,12 +15790,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Muss die Zählerverteilung erneuert werden?</t>
+          <t>Wie viele Felder?</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -15805,12 +15805,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>2-Feld | 3-Feld | 4-Feld und mehr</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn E02 = Ja</t>
         </is>
       </c>
     </row>
@@ -15822,12 +15822,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wie viele Felder?</t>
+          <t>Unterverteilung erforderlich?</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2-Feld | 3-Feld | 4-Feld und mehr</t>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>nur wenn E02 = Ja</t>
+          <t>nur wenn E02 = Nein</t>
         </is>
       </c>
     </row>
@@ -15854,12 +15854,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Unterverteilung erforderlich?</t>
+          <t>MID-Zwischenzähler erforderlich?</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -15874,24 +15874,24 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>nur wenn E02 = Nein</t>
+          <t>nur wenn E04 = Ja</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Elektro/ZV</t>
+          <t>Friondo</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MID-Zwischenzähler erforderlich?</t>
+          <t>Friondo HEMS gewünscht?</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>nur wenn E04 = Ja</t>
+          <t>immer</t>
         </is>
       </c>
     </row>
@@ -15918,12 +15918,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Friondo HEMS gewünscht?</t>
+          <t>iMSys inkl. Smart Meter gewünscht?</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -15939,6 +15939,11 @@
       <c r="F65" t="inlineStr">
         <is>
           <t>immer</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Löst Vollmacht-Seite aus.</t>
         </is>
       </c>
     </row>
@@ -15950,12 +15955,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>iMSys inkl. Smart Meter gewünscht?</t>
+          <t>Friondo SpotDynamic gewünscht?</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -15982,17 +15987,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Friondo</t>
+          <t>Förderung</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>K01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Friondo SpotDynamic gewünscht?</t>
+          <t>Bewohnt der Eigentümer eine Wohneinheit selbst?</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -16007,12 +16012,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn O01 = 2FH oder MFH</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Löst Vollmacht-Seite aus.</t>
+          <t>EFH/REH/RMH: automatisch Ja. Gewerbe: automatisch Nein.</t>
         </is>
       </c>
     </row>
@@ -16024,12 +16029,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>K01</t>
+          <t>K02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bewohnt der Eigentümer eine Wohneinheit selbst?</t>
+          <t>Welche Heizung wird ersetzt? (Klima-Bonus)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -16039,17 +16044,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Öl-, Kohle-, Gasetagen- oder Nachtspeicherheizung, funktionstüchtig | Gas- oder Biomasseheizung, mind. 20 Jahre, funktionstüchtig | Andere / jüngere Heizung / Neubau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>nur wenn O01 = 2FH oder MFH</t>
+          <t>nur bei Selbstnutzung</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>EFH/REH/RMH: automatisch Ja. Gewerbe: automatisch Nein.</t>
+          <t>Vorbelegt aus A01 + A02, änderbar.</t>
         </is>
       </c>
     </row>
@@ -16061,22 +16066,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>K02</t>
+          <t>K03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Welche Heizung wird ersetzt? (Klima-Bonus)</t>
+          <t>Zu versteuerndes Haushaltsjahreseinkommen (€)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Öl-, Kohle-, Gasetagen- oder Nachtspeicherheizung, funktionstüchtig | Gas- oder Biomasseheizung, mind. 20 Jahre, funktionstüchtig | Andere / jüngere Heizung / Neubau</t>
+          <t>Betragseingabe</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -16086,7 +16086,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Vorbelegt aus A01 + A02, änderbar.</t>
+          <t>Leer oder über 50.000 € = kein Bonus.</t>
         </is>
       </c>
     </row>
@@ -16098,44 +16098,49 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>K03</t>
+          <t>K04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Zu versteuerndes Haushaltsjahreseinkommen (€)</t>
+          <t>Minderjähriges Kind im Haushalt?</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Betragseingabe</t>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>nur bei Selbstnutzung</t>
+          <t>nur wenn K03 ausgefüllt</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leer oder über 50.000 € = kein Bonus.</t>
+          <t>10.000 € Abzug vom Einkommen.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Förderung</t>
+          <t>Einschätzung</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>K04</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minderjähriges Kind im Haushalt?</t>
+          <t>Einschätzung des Kunden</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -16145,17 +16150,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>heiß | warm | kalt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>nur wenn K03 ausgefüllt</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>10.000 € Abzug vom Einkommen.</t>
+          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
         </is>
       </c>
     </row>
@@ -16167,22 +16172,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Einschätzung des Kunden</t>
+          <t>Wiedervorlage am</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>heiß | warm | kalt</t>
+          <t>Datum</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -16191,38 +16191,6 @@
         </is>
       </c>
       <c r="G72" t="inlineStr">
-        <is>
-          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Einschätzung</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>S02</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Wiedervorlage am</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
         <is>
           <t>optional – leer lassen, wenn keine Wiedervorlage nötig</t>
         </is>

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -31,6 +31,11 @@
     <sheet name="Aktionen KL" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="Angebotsaufbau KL" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="KL-Parameter" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Fragen WB" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="WB-Artikel" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Aktionen WB" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Angebotsaufbau WB" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="WB-Parameter" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -224,6 +229,81 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Angebotstool v34</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Agent W, Fassung v34-Nachtrag-15.10.2026-b</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Angebotstool v34</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Agent W, Fassung v34-Nachtrag-15.10.2026-b</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Angebotstool v34</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Agent W, Fassung v34-Nachtrag-15.10.2026-b</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Angebotstool v34</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Agent W, Fassung v34-Nachtrag-15.10.2026-b</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Angebotstool v34</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Agent W, Fassung v34-Nachtrag-15.10.2026-b</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -515,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -648,6 +728,20 @@
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Klima (v24) – Blätter: Fragen KL (28 Fragen; Raumfragen als Wiederholgruppe „je Raum (KO05)“, KR07 begrenzt über den Hinweis „… Optionen wie Außengeräte (KO04)“) · KL-Artikel (GUID → KL-Nr.; Pinning für den Import der Klima-Positionslisten aus Artikel-Preislisten/Klima/: KL001–KL048 = Ersatzangebot KL Pos. 001–048, KL049 = Musterangebot KL Pos. 006 Systemgarantie, KL050 = Rollgerüst ohne TAIFUN-GUID) · Paketmatrix KL · Kombinationen KL (Bosch Tab. 7) · Montagematrix KL · Aktionen KL (Schreibweisen wie Aktionen PV, zusätzlich „Hinweis: &lt;Text&gt;“ = fachlicher Hinweis ohne Position und ohne Ampel; Mengenwörter „Innengeräte“ = Σ Räume, „Außengeräte“ = KO04, „je Außengerät“ = × KO04, „je Raum“ = je Raum-Klon) · Angebotsaufbau KL · KL-Parameter. KL-Artikel heißen KL001 … KL050 und werden wie „PV001“ referenziert. Textregeln „Positionen KL020–KL025“, „Position KL013“ und „Positionen KL026–KL029“ greifen bei jedem Klima-Import; Anhang „wenn Sparte = KL“ (Bosch-Climate-Broschüre, Zulieferung).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Wallbox (v34): Wallbox-Konfigurator Mennekes AMTRON 4You (PLAN_V21, Phasen 178/179, Nachtrag 15.10.2026). Fragen: WB01 Wallbox (310 → WB001, 560 → WB002), WB02 Leitungsverlegung in Metern (bis leitung_inklusive_m = 10 m in der Anschlussvorbereitung WB003 enthalten; Mehrlänge = WB02 − 10 m, kaufmännisch auf ganze Meter gerundet, nie unter 0 → WB005 lfd. Meter × Mehrlänge), WB03 Erdarbeiten Ja/Nein mit WB04 Meter (→ WB006 × Meter, ganze Meter; 0/leer → Absende-Meldung „Erdarbeiten: Meter fehlen“; unabhängig von Wandmontage/Säule), WB05 Wandmontage oder Säule (Säule → WB007 Fundament und Standsäule 1 × psl.), WB07 Anzahl Durchbrüche (durchbrueche_inklusive = 2 in der Anschlussvorbereitung enthalten, darüber WB008 × (WB07 − 2), ganze Stück), WB08 Bemerkung (nur Protokoll; WB06 unbelegt). Immer im Angebot: WB003 Anschlussvorbereitung (psl.) und WB004 Netzanmeldung §14a EnWG (0,00 €). Keine AMPEL-Gründe – eine WB-Katalog-Erfassung ist immer grün; individuelle Fälle über die Freitext-Weiche (TAIFUN). Leitungslänge über 100 m = Warnung (keine Sperre). Angebot mit 19 % USt, ohne Förderblock, ohne Wirtschaftlichkeit, ohne Auslegungs-Position; Vollmacht (Nachtext D) bei WB immer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Wallbox (v34) – Blätter: Fragen WB (WB01–WB05, WB07, WB08, S01/S02 Einschätzung) · WB-Artikel (Anker für den Import: Datei „WB Angebot Excel 1“ + Position + Beschreibungsanfang – die GUIDs der TAIFUN-Exporte sind Angebots-GUIDs und je Export verschieden, die Spalte „GUID (zuletzt gesehen)“ wird vom Import nachgeführt; die Spalte Einheit überstimmt die Export-Einheit, z. B. WB007 psl. statt „m“) · Aktionen WB (Schreibweise wie Aktionen KL; Mengenwörter „× Mehrlänge“ nur bei WB02, „× WB04“ = Meter aus der Frage WB04, „× (WB07 − 2)“ = Durchbrüche über die enthaltenen) · Angebotsaufbau WB (Block 1 Wallbox · 2 Installation und Anschluss: WB003, WB008, WB005, WB006, WB007 · 3 Netzanmeldung) · WB-Parameter (leitung_inklusive_m, meterposition_leitung, erdarbeiten_position, fundament_position, durchbrueche_inklusive, durchbruch_position, wallbox_standard). Import: Artikel → Wallbox-Positionslisten importieren liest Artikel-Preislisten/Wallbox/WB Angebot Excel 1.xlsx (Blatt „Tabelle 1“, Positionen 001–008; die Textzeile ohne Position „Komplettpaket Wallbox inkl. Montage“ wird der Absatz am Ende des Vortexts); weitere xlsx-Dateien im Ordner werden nur auf Preiskonflikte geprüft (Ankerdatei gewinnt, Konflikt im Protokoll); _x000D_ und „?“-Platzhalter werden bereinigt. Anhänge-Regel „wenn Artikel WB001 im Angebot“ ist zusätzlich erlaubt (Datenblatt je Modell).</t>
         </is>
       </c>
     </row>
@@ -23470,6 +23564,1423 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Seite</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Fragetext</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Antwortmöglichkeiten</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Anzeigen wenn</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>Hinweis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Wallbox</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>WB01</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Welche Wallbox?</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Mennekes AMTRON 4You 310 – 11 kW, 7,5 m Ladekabel | Mennekes AMTRON 4You 560 – 11 kW, 7,5 m Ladekabel, MID-Zähler, App, OCPP</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>keine Vorbelegung – Modell gemeinsam mit dem Kunden festlegen (310 = Basis, 560 = mit MID-Zähler, App und OCPP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Wallbox</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>WB02</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Wie viel Meter Leitungsverlegung erforderlich?</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Vorbelegung 10 m (= in der Anschlussvorbereitung enthalten); Dezimalzahl mit Komma möglich, z. B. 12,5 – jeder Meter über 10 m wird als lfd. Meter NYY-J (WB005) berechnet, kaufmännisch auf ganze Meter gerundet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Wallbox</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>WB03</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Erdarbeiten erforderlich?</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Vorbelegung Nein [ANNAHME]; bei Ja folgt die Meterfrage WB04 – Erdarbeiten zwischen Wallbox und Hauseinführung (WB006 je Meter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Wallbox</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>WB04</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Erdarbeiten: wie viele Meter?</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>nur wenn WB03 = Ja</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Meter zwischen Wallbox und Hauseinführung (Boden ca. 40 cm tief ausheben, Kunststoffrohr und Leitungen verlegen); Dezimalzahl möglich, kaufmännisch auf ganze Meter gerundet – Pflicht bei Erdarbeiten</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Wallbox</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>WB05</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Wandmontage oder Säule?</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Wandmontage | Säule</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Vorbelegung Wandmontage [ANNAHME]; Säule = Fundament und Standsäule (WB007, 1 × psl.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Wallbox</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>WB07</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Wie viele Durchbrüche erforderlich?</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>2 Durchbrüche sind in der Anschlussvorbereitung enthalten; Vorbelegung 2 [ANNAHME] – jeder weitere Durchbruch wird als Bohrung/Durchbruch (WB008) berechnet (ganze Stück)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Wallbox</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>WB08</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Bemerkungen zur Ausführung (optional)</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Freitext groß</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>optional – nur im Protokoll, keine Auswirkung auf das Angebot (z. B. Montageort, Leitungsweg, Besonderheiten am Zählerschrank); WB06 ist unbelegt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Einschätzung</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Einschätzung des Kunden</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>heiß | warm | kalt</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Einschätzung</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Wiedervorlage am</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>optional – leer lassen, wenn keine Wiedervorlage nötig</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>WB-Nr.</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Datei</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Beschreibungsanfang</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>GUID (zuletzt gesehen)</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Einheit</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>WB001</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>WB Angebot Excel 1</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Mennekes AMTRON 4You 310 11 kW mit 7,5 m Ladekabel</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Wallbox 310 – über WB01; VK laut Export 938,50 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>WB002</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>WB Angebot Excel 1</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Mennekes AMTRON 4You 560 11 kW mit 7,5 m Ladekabel</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Wallbox 560 (MID-Zähler, App, OCPP) – über WB01; VK laut Export 1.390,55 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>WB003</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>WB Angebot Excel 1</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Anschlussvorbereitung Ladestation mit Ladeanschlussleistung bis zu 11 KW</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>psl.</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>immer; bis 10 m Leitung enthalten (WB-Parameter leitung_inklusive_m); VK 1.297,20 € (bestätigt R1, 15.10.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>WB004</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>WB Angebot Excel 1</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Netzanmeldung beim EVU nach §14a EnWG</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>psl.</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>immer; 0,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>WB005</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>WB Angebot Excel 1</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>lfd. meter NYY-J 5x10mm², separate Erdung 16mm² und Ethernet-Kabel CAT7 zwischen der Hauptverteilung und geplantem Ort der Ladestation liefern und verlegen</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>× Mehrlänge (WB02 − leitung_inklusive_m, ganze Meter); VK 49,34 €/m</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>WB006</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>WB Angebot Excel 1</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Erdarbeiten zwischen Wallbox bis zur Hauseinführung Boden auf eine Tiefe von ca. 40 cm ausheben.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>× WB04 (Meter Erdarbeiten, ganze Meter) bei WB03 = Ja; VK 123,50 €/m – ersetzt seit dem Nachtrag 15.10.2026 den Montagekanal (entfällt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>WB007</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>WB Angebot Excel 1</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Fundament und Standsäule für Wallbox MENNEKES AMTRON 4You Serie</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>psl.</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>× 1 bei WB05 = Säule; VK 1.020,00 € – der Export nennt Einheit „m“, im Tool 1 × psl. [ANNAHME, Rückfrage]; das Blatt überstimmt die Export-Einheit</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>WB008</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>WB Angebot Excel 1</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Zusätzliche erforderte Bohrung/Durchbrüche für den Leitungsdurchgang o.ä.</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>× (WB07 − 2) bei mehr als 2 Durchbrüchen (2 in der Anschlussvorbereitung enthalten, WB-Parameter durchbrueche_inklusive); VK 169,00 €</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Frage</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Antwort / Bedingung</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Aktion</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Zusatzbedingung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>WB01</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Mennekes AMTRON 4You 310 – 11 kW, 7,5 m Ladekabel</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: WB001 ×1</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Wallbox AMTRON 4You 310 (Block 1)</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>WB01</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Mennekes AMTRON 4You 560 – 11 kW, 7,5 m Ladekabel, MID-Zähler, App, OCPP</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: WB002 ×1</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Wallbox AMTRON 4You 560 (Block 1)</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Grundpaket</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: WB003 ×1</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Anschlussvorbereitung Ladestation – immer; bis 10 m Leitung enthalten (WB-Parameter leitung_inklusive_m)</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Grundpaket</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: WB004 ×1</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Netzanmeldung beim EVU nach §14a EnWG – immer, 0,00 € (Block 3)</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>WB02</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>bis 10</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Leitungsverlegung bis 10 m in der Anschlussvorbereitung enthalten – keine Meter-Position</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>WB02</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>über 10</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: WB005 × Mehrlänge</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Mehrlänge = WB02 − leitung_inklusive_m, kaufmännisch auf ganze Meter gerundet, nie unter 0 (app/wb_auslegung.py); „über 10“ = Wert des Parameters leitung_inklusive_m</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>WB03</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: WB006 × WB04</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Erdarbeiten je Meter aus WB04 (kaufmännisch ganze Meter [ANNAHME]); 0 oder leer → Absende-Meldung „Erdarbeiten: Meter fehlen“</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>WB03</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>keine Erdarbeiten</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>WB05</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Säule</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: WB007 ×1</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Fundament und Standsäule (1 × psl.)</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>WB05</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Wandmontage</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Wandmontage ist in der Anschlussvorbereitung enthalten</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>WB07</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>bis 2</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>bis 2 Durchbrüche in der Anschlussvorbereitung enthalten (WB-Parameter durchbrueche_inklusive)</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>WB07</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>über 2</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Artikel: WB008 × (WB07 − 2)</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>zusätzliche Bohrung/Durchbrüche = WB07 − 2, ganze Stück, nie unter 0 (Ergänzung 15.10.2026)</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>WB08</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>(Freitext)</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>nur Protokoll</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Überschrift im Angebot</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Inhalt</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Wann</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Wallbox</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>WB001 · WB002 Wallbox lt. WB01 (genau eine)</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Installation und Anschluss</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>WB003 Anschlussvorbereitung · WB008 Bohrung/Durchbrüche × (WB07 − 2) · WB005 lfd. Meter Leitung × Mehrlänge · WB006 Erdarbeiten × WB04 · WB007 Fundament und Standsäule (WB05 = Säule)</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Netzanmeldung</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>WB004 Netzanmeldung beim EVU nach §14a EnWG (0,00 €)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Summenblock</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Netto · Umsatzsteuer 19 % · Gesamt-Betrag · ggf. Rabatt · Endbetrag</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>kein KfW-/Förderblock, keine Wirtschaftlichkeit, keine Auslegungszeile (v34 Phase 180: Auslegung nur im Protokoll und intern im Editor)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Nachtexte</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Profil-Textblock WB</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Textblöcke „Friondo WB Standard / Enni / SWD / Sparkasse DU“ (Parametrierung → Textblöcke): Nachtext B Installationsvoraussetzungen + C Schlussseite ({zahlungsbedingungen}) + D Vollmacht (bei WB immer, Netzanmeldung §14a); kein Nachtext A, kein Förderblock, keine Wirtschaftlichkeit; Vortext mit Absatz „Komplettpaket Wallbox inkl. Montage“ aus der Textzeile der Excel</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Anhänge</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Mennekes AMTRON 4You Datenblatt (Zulieferung) · Unternehmenspräsentation · Ratenkauf-Broschüre</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Regel „wenn Sparte = WB“ (Blatt Anhänge); Datei nach anlagen/ legen; Ratenkauf nicht bei Enni/SWD (Spalte „Nicht bei Profil“)</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Protokoll</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Erfassungsprotokoll</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Seite „Auslegung“: Wallbox (Kurzname), Leitungsverlegung gesamt / davon enthalten / Mehrlänge, Erdarbeiten (Meter oder keine), Montage (Wandmontage oder Säule), Durchbrüche (gesamt, davon enthalten, zusätzlich); Bemerkung WB08; Einschätzung S01/S02</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Wert</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Einheit</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>leitung_inklusive_m</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>in der Anschlussvorbereitung (WB003) enthalten; Mehrlänge = WB02 − dieser Wert, kaufmännisch auf ganze Meter, nie unter 0; zugleich Vorbelegung von WB02 – bei Änderung auch die Schwelle „über 10“ im Blatt Aktionen WB anpassen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>meterposition_leitung</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>WB005</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>lfd. Meter NYY-J 5x10mm², Erdung 16 mm², CAT7 – je Meter Mehrlänge</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>erdarbeiten_position</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>WB006</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Erdarbeiten zwischen Wallbox und Hauseinführung – je Meter aus WB04 (bei WB03 = Ja)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>fundament_position</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>WB007</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Fundament und Standsäule – 1 × psl. bei WB05 = Säule</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>durchbrueche_inklusive</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>in der Anschlussvorbereitung (WB003) enthaltene Durchbrüche; zugleich Vorbelegung von WB07 – bei Änderung auch die Schwelle „über 2“ und den Abzug „(WB07 − 2)“ im Blatt Aktionen WB anpassen (Ergänzung 15.10.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>durchbruch_position</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>WB008</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Zusätzliche Bohrung/Durchbrüche – je Stück über durchbrueche_inklusive</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>wallbox_standard</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Vorbelegung WB01 (Option wörtlich) – leer = keine Vorbelegung [ANNAHME, Plan]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -27214,7 +28725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -27392,17 +28903,35 @@
       <c r="D9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Mennekes AMTRON 4You Datenblatt.pdf</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>wenn Sparte = WB</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>v34 Wallbox: Gerätedatenblatt Mennekes AMTRON 4You (Zulieferung – Datei fehlt noch, anhaenge.fehlende_dateien meldet sie); liefert Mennekes getrennte Datenblätter je Modell, zwei Zeilen mit „wenn Artikel WB001 im Angebot“ / „wenn Artikel WB002 im Angebot“ anlegen</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>(weitere Zeilen ergänzen)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Regeln: 'immer' | 'wenn &lt;Frage&gt; = &lt;Antwort&gt;' | 'wenn Pos. &lt;Nr&gt; im Angebot'</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>PDFs in den Ordner anlagen/ legen</t>
         </is>
